--- a/Equity/output/daily/SwingStocks_Thu_22nd Oct.xlsx
+++ b/Equity/output/daily/SwingStocks_Thu_22nd Oct.xlsx
@@ -14,10 +14,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW TO READ" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'PRIORITY'!$A$4:$V$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SWING PICKS'!$A$4:$AL$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'PRIORITY'!$A$4:$V$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'SWING PICKS'!$A$4:$AL$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'WATCHLIST'!$A$4:$AL$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ALL INDICATORS'!$A$4:$AO$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ALL INDICATORS'!$A$4:$AO$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V23"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -565,14 +565,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Universe: NSE_LISTED | NIFTY regime: BEAR | Generated: 21-Oct-2026 16:46 | Targets: +7% / +10% | *Qty sized for Rs 100,000 capital, 1% risk</t>
+          <t>Universe: NSE_LISTED | NIFTY regime: BEAR | Generated: 21-Oct-2026 19:34 | Targets: +7% / +10% | *Qty sized for Rs 100,000 capital, 1% risk</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>WARNING: Yahoo gave no fundamentals / results dates today, so those were NOT checked - look up each stock's results date yourself before buying.   Checks: BUY ZONE now | no Risk Flags | Fundamental not Mixed | Hist Hit 7% &gt;= 25 | one stock per sector | best Hist Hit 7% first | at most 3 stocks because NIFTY regime is BEAR.  At 9:15 buy only if the price is still inside Entry Low - Entry High; if it opens above, skip it.</t>
+          <t>WARNING: Yahoo gave no fundamentals / results dates today, so those were NOT checked - look up each stock's results date yourself before buying.   Checks: BUY ZONE now | no Risk Flags | Fundamental not Mixed | Hist Hit 7% &gt;= 25 | one stock per sector | best Hist Hit 7% first | at most 1 stock because NIFTY regime is BEAR.  At 9:15 buy only if the price is still inside Entry Low - Entry High; if it opens above, skip it.  EXIT: sell at Target 1 (6-month test: holding on for Target 2 made less money).</t>
         </is>
       </c>
     </row>
@@ -694,18 +694,22 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>MANOMAY</t>
+          <t>KARURVYSYA</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Manomay Tex India Limited</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr"/>
+          <t>Karur Vysya Bank Limited</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>EMA20 PULLBACK</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -714,40 +718,40 @@
         </is>
       </c>
       <c r="G5" s="8" t="n">
-        <v>57.14285714285714</v>
+        <v>50.64935064935064</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>242.7700042724609</v>
+        <v>359.6499938964844</v>
       </c>
       <c r="L5" s="9" t="n">
-        <v>238.1906049900909</v>
+        <v>356.0534939575195</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>243.9838542938232</v>
+        <v>363.2464938354492</v>
       </c>
       <c r="N5" s="9" t="n">
-        <v>226.989953994751</v>
+        <v>336.2727442932129</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>259.7639045715332</v>
+        <v>384.8254934692383</v>
       </c>
       <c r="P5" s="9" t="n">
-        <v>267.047004699707</v>
+        <v>395.6149932861329</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>15294.51026916504</v>
+        <v>15105.29974365234</v>
       </c>
       <c r="S5" s="6" t="inlineStr">
         <is>
@@ -757,7 +761,7 @@
       <c r="T5" s="6" t="inlineStr"/>
       <c r="U5" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | OBV rising | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 57% of similar setups</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | Volume 3.1x avg | OBV rising | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 51% of similar setups</t>
         </is>
       </c>
       <c r="V5" s="10" t="inlineStr">
@@ -766,241 +770,153 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>KARURVYSYA</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="inlineStr">
-        <is>
-          <t>Karur Vysya Bank Limited</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>OTHER PICKS LEFT OUT - and the check that failed</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="G9" s="12" t="inlineStr">
+        <is>
+          <t>Hist Hit 7%</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="inlineStr">
+        <is>
+          <t>Why Not Priority</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>SOUTHBANK</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>The South Indian Bank Limited</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>MOMENTUM</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>BUY ZONE</t>
         </is>
       </c>
-      <c r="G6" s="8" t="n">
-        <v>50.64935064935064</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>77</v>
-      </c>
-      <c r="I6" s="5" t="n">
-        <v>80</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="K6" s="9" t="n">
-        <v>359.6499938964844</v>
-      </c>
-      <c r="L6" s="9" t="n">
-        <v>356.0534939575195</v>
-      </c>
-      <c r="M6" s="9" t="n">
-        <v>363.2464938354492</v>
-      </c>
-      <c r="N6" s="9" t="n">
-        <v>336.2727442932129</v>
-      </c>
-      <c r="O6" s="9" t="n">
-        <v>384.8254934692383</v>
-      </c>
-      <c r="P6" s="9" t="n">
-        <v>395.6149932861329</v>
-      </c>
-      <c r="Q6" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="R6" s="5" t="n">
-        <v>15105.29974365234</v>
-      </c>
-      <c r="S6" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T6" s="6" t="inlineStr"/>
-      <c r="U6" s="7" t="inlineStr">
-        <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | Volume 3.1x avg | OBV rising | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 51% of similar setups</t>
-        </is>
-      </c>
-      <c r="V6" s="10" t="inlineStr">
-        <is>
-          <t>Open filings</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="G10" s="14" t="n">
+        <v>42.34234234234234</v>
+      </c>
+      <c r="H10" s="13" t="inlineStr">
+        <is>
+          <t>Risk flag: RSI&gt;70 (hot), Extended &gt;7% above EMA20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>PTCIL</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="inlineStr">
-        <is>
-          <t>PTC Industries Limited</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>Capital Goods</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
-        <is>
-          <t>TREND CONTINUATION</t>
-        </is>
-      </c>
-      <c r="F7" s="7" t="inlineStr">
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>MPHASIS</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>MphasiS Limited</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>BREAKOUT</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="inlineStr">
         <is>
           <t>BUY ZONE</t>
         </is>
       </c>
-      <c r="G7" s="8" t="n">
-        <v>41.77215189873418</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>79</v>
-      </c>
-      <c r="I7" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="J7" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" s="9" t="n">
-        <v>25115</v>
-      </c>
-      <c r="L7" s="9" t="n">
-        <v>24863.85</v>
-      </c>
-      <c r="M7" s="9" t="n">
-        <v>25366.15</v>
-      </c>
-      <c r="N7" s="9" t="n">
-        <v>23636.225</v>
-      </c>
-      <c r="O7" s="9" t="n">
-        <v>26873.05</v>
-      </c>
-      <c r="P7" s="9" t="n">
-        <v>27626.5</v>
-      </c>
-      <c r="Q7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="T7" s="6" t="inlineStr"/>
-      <c r="U7" s="7" t="inlineStr">
-        <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | Volume 2.0x avg | OBV rising | Near 52W high | Beating NIFTY 1M | Stock hit +7% in 15d 42% of similar setups</t>
-        </is>
-      </c>
-      <c r="V7" s="10" t="inlineStr">
-        <is>
-          <t>Open filings</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>OTHER PICKS LEFT OUT - and the check that failed</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>Rank</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>Company</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>Setup</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
-        <is>
-          <t>Hist Hit 7%</t>
-        </is>
-      </c>
-      <c r="H11" s="12" t="inlineStr">
-        <is>
-          <t>Why Not Priority</t>
+      <c r="G11" s="14" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="H11" s="13" t="inlineStr">
+        <is>
+          <t>Risk flag: RSI&gt;70 (hot), Extended &gt;7% above EMA20, Low hist. +7% hit-rate | Hist Hit 7% below 25</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>SOUTHBANK</t>
+          <t>PTCIL</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>The South Indian Bank Limited</t>
+          <t>PTC Industries Limited</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>Financial Services</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>TREND CONTINUATION</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
@@ -1009,36 +925,36 @@
         </is>
       </c>
       <c r="G12" s="14" t="n">
-        <v>42.34234234234234</v>
+        <v>41.77215189873418</v>
       </c>
       <c r="H12" s="13" t="inlineStr">
         <is>
-          <t>Same sector as KARURVYSYA (which has the better Hist Hit 7%)</t>
+          <t>Passed every check, but only the top 1 are listed on a BEAR day</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B13" s="13" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>SHYAMMETL</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>MphasiS Limited</t>
+          <t>Shyam Metalics and Energy Limited</t>
         </is>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Capital Goods</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>BREAKOUT</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="F13" s="13" t="inlineStr">
@@ -1047,377 +963,17 @@
         </is>
       </c>
       <c r="G13" s="14" t="n">
-        <v>3.333333333333333</v>
+        <v>26.92307692307692</v>
       </c>
       <c r="H13" s="13" t="inlineStr">
         <is>
-          <t>Risk flag: RSI&gt;70 (hot), Extended &gt;7% above EMA20, Low hist. +7% hit-rate | Hist Hit 7% below 25</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>SHYAMMETL</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Shyam Metalics and Energy Limited</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>Capital Goods</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>MOMENTUM</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="inlineStr">
-        <is>
-          <t>BUY ZONE</t>
-        </is>
-      </c>
-      <c r="G14" s="14" t="n">
-        <v>26.92307692307692</v>
-      </c>
-      <c r="H14" s="13" t="inlineStr">
-        <is>
           <t>Risk flag: Extended &gt;7% above EMA20</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B15" s="13" t="inlineStr">
-        <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="C15" s="13" t="inlineStr">
-        <is>
-          <t>Punjab National Bank</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="E15" s="13" t="inlineStr">
-        <is>
-          <t>TREND CONTINUATION</t>
-        </is>
-      </c>
-      <c r="F15" s="13" t="inlineStr">
-        <is>
-          <t>BUY ZONE</t>
-        </is>
-      </c>
-      <c r="G15" s="14" t="n">
-        <v>15.38461538461539</v>
-      </c>
-      <c r="H15" s="13" t="inlineStr">
-        <is>
-          <t>Hist Hit 7% below 25</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="n">
-        <v>7</v>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>MVGJL</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
-        <is>
-          <t>Manoj Vaibhav Gems N Jewellers Limited</t>
-        </is>
-      </c>
-      <c r="D16" s="13" t="inlineStr"/>
-      <c r="E16" s="13" t="inlineStr">
-        <is>
-          <t>TREND CONTINUATION</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="inlineStr">
-        <is>
-          <t>BUY ZONE</t>
-        </is>
-      </c>
-      <c r="G16" s="14" t="n">
-        <v>36.36363636363637</v>
-      </c>
-      <c r="H16" s="13" t="inlineStr">
-        <is>
-          <t>Passed every check, but only the top 3 are listed on a BEAR day</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="n">
-        <v>8</v>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>TIPSMUSIC</t>
-        </is>
-      </c>
-      <c r="C17" s="13" t="inlineStr">
-        <is>
-          <t>Tips Music Limited</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="inlineStr">
-        <is>
-          <t>Media Entertainment &amp; Publication</t>
-        </is>
-      </c>
-      <c r="E17" s="13" t="inlineStr">
-        <is>
-          <t>TREND CONTINUATION</t>
-        </is>
-      </c>
-      <c r="F17" s="13" t="inlineStr">
-        <is>
-          <t>BUY ZONE</t>
-        </is>
-      </c>
-      <c r="G17" s="14" t="n">
-        <v>53.33333333333334</v>
-      </c>
-      <c r="H17" s="13" t="inlineStr">
-        <is>
-          <t>Risk flag: Extended &gt;7% above EMA20, Volume below average</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="B18" s="13" t="inlineStr">
-        <is>
-          <t>MGEL</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>Mangalam Global Enterprise Limited</t>
-        </is>
-      </c>
-      <c r="D18" s="13" t="inlineStr"/>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>NEAR BREAKOUT</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="inlineStr">
-        <is>
-          <t>WAIT - trigger not hit (buy above 17.52)</t>
-        </is>
-      </c>
-      <c r="G18" s="14" t="n">
-        <v>47.72727272727273</v>
-      </c>
-      <c r="H18" s="13" t="inlineStr">
-        <is>
-          <t>Not in buy zone | Risk flag: Negative headline - check news</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B19" s="13" t="inlineStr">
-        <is>
-          <t>MASTEK</t>
-        </is>
-      </c>
-      <c r="C19" s="13" t="inlineStr">
-        <is>
-          <t>Mastek Limited</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="E19" s="13" t="inlineStr">
-        <is>
-          <t>MOMENTUM</t>
-        </is>
-      </c>
-      <c r="F19" s="13" t="inlineStr">
-        <is>
-          <t>BUY ZONE</t>
-        </is>
-      </c>
-      <c r="G19" s="14" t="n"/>
-      <c r="H19" s="13" t="inlineStr">
-        <is>
-          <t>Risk flag: Extended &gt;7% above EMA20 | Too few past cases to know Hist Hit 7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="n">
-        <v>11</v>
-      </c>
-      <c r="B20" s="13" t="inlineStr">
-        <is>
-          <t>AAREYDRUGS</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>Aarey Drugs &amp; Pharmaceuticals Limited</t>
-        </is>
-      </c>
-      <c r="D20" s="13" t="inlineStr"/>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>NEAR BREAKOUT</t>
-        </is>
-      </c>
-      <c r="F20" s="13" t="inlineStr">
-        <is>
-          <t>WAIT - trigger not hit (buy above 114.91)</t>
-        </is>
-      </c>
-      <c r="G20" s="14" t="n">
-        <v>68.25396825396825</v>
-      </c>
-      <c r="H20" s="13" t="inlineStr">
-        <is>
-          <t>Not in buy zone | Risk flag: Volume below average</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="n">
-        <v>13</v>
-      </c>
-      <c r="B21" s="13" t="inlineStr">
-        <is>
-          <t>HEXT</t>
-        </is>
-      </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>Hexaware Technologies Limited</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>BREAKOUT</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="inlineStr">
-        <is>
-          <t>BUY ZONE</t>
-        </is>
-      </c>
-      <c r="G21" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="13" t="inlineStr">
-        <is>
-          <t>Hist Hit 7% below 25</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="n">
-        <v>14</v>
-      </c>
-      <c r="B22" s="13" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>Coforge Limited</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>NEAR BREAKOUT</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="inlineStr">
-        <is>
-          <t>WAIT - trigger not hit (buy above 1971.97)</t>
-        </is>
-      </c>
-      <c r="G22" s="14" t="n">
-        <v>35.71428571428572</v>
-      </c>
-      <c r="H22" s="13" t="inlineStr">
-        <is>
-          <t>Not in buy zone | Risk flag: Weak trend (ADX&lt;20)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="13" t="n">
-        <v>15</v>
-      </c>
-      <c r="B23" s="13" t="inlineStr">
-        <is>
-          <t>SINGERIND</t>
-        </is>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
-        <is>
-          <t>Singer India Limited</t>
-        </is>
-      </c>
-      <c r="D23" s="13" t="inlineStr"/>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>MOMENTUM</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="inlineStr">
-        <is>
-          <t>BUY ZONE</t>
-        </is>
-      </c>
-      <c r="G23" s="14" t="n"/>
-      <c r="H23" s="13" t="inlineStr">
-        <is>
-          <t>Too few past cases to know Hist Hit 7%</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:V7"/>
-  <conditionalFormatting sqref="F5:F7">
+  <autoFilter ref="A4:V5"/>
+  <conditionalFormatting sqref="F5">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>LEFT(F5,3)="BUY"</formula>
     </cfRule>
@@ -1428,7 +984,7 @@
       <formula>OR(LEFT(F5,5)="AVOID",LEFT(F5,6)="REVIEW",LEFT(F5,4)="SKIP")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I5:I7">
+  <conditionalFormatting sqref="I5">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="50"/>
@@ -1442,8 +998,6 @@
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="V7" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1455,7 +1009,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL19"/>
+  <dimension ref="A1:AL9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1508,7 +1062,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Universe: NSE_LISTED | NIFTY regime: BEAR | Generated: 21-Oct-2026 16:46 | Targets: +7% / +10% | *Qty sized for Rs 100,000 capital, 1% risk</t>
+          <t>Universe: NSE_LISTED | NIFTY regime: BEAR | Generated: 21-Oct-2026 19:34 | Targets: +7% / +10% | *Qty sized for Rs 100,000 capital, 1% risk</t>
         </is>
       </c>
     </row>
@@ -1793,7 +1347,7 @@
         <v>75.6141110683601</v>
       </c>
       <c r="Z5" s="8" t="n">
-        <v>26.39500914229825</v>
+        <v>26.39500914229831</v>
       </c>
       <c r="AA5" s="8" t="n">
         <v>3.371168386562134</v>
@@ -1828,7 +1382,7 @@
       </c>
       <c r="AJ5" s="7" t="inlineStr">
         <is>
-          <t>RELAXED smallcap</t>
+          <t>RELAXED smallcap | RSI&gt;70 (hot) | Extended &gt;7% above EMA20</t>
         </is>
       </c>
       <c r="AK5" s="7" t="inlineStr">
@@ -2239,7 +1793,7 @@
       <c r="AJ8" s="7" t="inlineStr"/>
       <c r="AK8" s="7" t="inlineStr">
         <is>
-          <t>[15 Oct 2026] PTC Industries (NSEI:PTCIL) Stock Forecast &amp; Analyst Predictions - Simply Wall Street | [15 Oct 2026] PTCIL Share Price Today - PTC Industries on NSE/BSE - scanx.trade | [14 Oct 2026] PTC Industries (PTCIL.NS) Slips 2.06% to ₹24,975 as Support Zone Comes Into Focus - Composite Profile - https://www.siam.in/ | [15 Oct 2026] PTC Industries raises ₹1,800 crore to expand defence, aerospace manufacturing in Lucknow - The Times of India</t>
+          <t>[15 Oct 2026] PTC Industries (NSEI:PTCIL) Stock Forecast &amp; Analyst Predictions - Simply Wall Street | [15 Oct 2026] PTCIL Share Price Today - PTC Industries on NSE/BSE - scanx.trade | [19 Oct 2026] PTC Industries (PTCIL.NS) Rises 1.70% to ₹25,100 as Defence-Aerospace Stock Holds Above Key Support - Stop Hunt - https://www.siam.in/ | [15 Oct 2026] PTC Industries raises ₹1,800 crore to expand defence, aerospace manufacturing in Lucknow - The Times of India</t>
         </is>
       </c>
       <c r="AL8" s="10" t="inlineStr">
@@ -2298,10 +1852,10 @@
         <v>1207.555975341797</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>1122.375800251059</v>
+        <v>1122.375799990441</v>
       </c>
       <c r="N9" s="8" t="n">
-        <v>6.12447112998586</v>
+        <v>6.124471151783971</v>
       </c>
       <c r="O9" s="9" t="n">
         <v>1279.291973876953</v>
@@ -2310,10 +1864,10 @@
         <v>1315.159973144531</v>
       </c>
       <c r="Q9" s="8" t="n">
-        <v>1.142955832664065</v>
+        <v>1.142955828596076</v>
       </c>
       <c r="R9" s="8" t="n">
-        <v>1.632794046662946</v>
+        <v>1.632794040851534</v>
       </c>
       <c r="S9" s="5" t="n">
         <v>13</v>
@@ -2334,13 +1888,13 @@
         <v>1.67906950564853</v>
       </c>
       <c r="Y9" s="8" t="n">
-        <v>68.27988496543384</v>
+        <v>68.27988449590266</v>
       </c>
       <c r="Z9" s="8" t="n">
-        <v>24.83134818788051</v>
+        <v>24.83134681575903</v>
       </c>
       <c r="AA9" s="8" t="n">
-        <v>3.402483961103256</v>
+        <v>3.402483973213317</v>
       </c>
       <c r="AB9" s="8" t="n">
         <v>8.690906871448867</v>
@@ -2386,1335 +1940,9 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>PNB</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>Punjab National Bank</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
-        <is>
-          <t>TREND CONTINUATION</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>BUY ZONE</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>75</v>
-      </c>
-      <c r="H10" s="6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I10" s="9" t="n">
-        <v>122.5</v>
-      </c>
-      <c r="J10" s="9" t="n">
-        <v>122.5</v>
-      </c>
-      <c r="K10" s="9" t="n">
-        <v>121.275</v>
-      </c>
-      <c r="L10" s="9" t="n">
-        <v>123.725</v>
-      </c>
-      <c r="M10" s="9" t="n">
-        <v>116.5831426488481</v>
-      </c>
-      <c r="N10" s="8" t="n">
-        <v>4.830087633593356</v>
-      </c>
-      <c r="O10" s="9" t="n">
-        <v>131.075</v>
-      </c>
-      <c r="P10" s="9" t="n">
-        <v>134.75</v>
-      </c>
-      <c r="Q10" s="8" t="n">
-        <v>1.449249067721851</v>
-      </c>
-      <c r="R10" s="8" t="n">
-        <v>2.070355811031212</v>
-      </c>
-      <c r="S10" s="5" t="n">
-        <v>163</v>
-      </c>
-      <c r="T10" s="5" t="n">
-        <v>19967.5</v>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v>15.38461538461539</v>
-      </c>
-      <c r="V10" s="8" t="n">
-        <v>3.846153846153846</v>
-      </c>
-      <c r="W10" s="5" t="n">
-        <v>78</v>
-      </c>
-      <c r="X10" s="8" t="n">
-        <v>1.825383104202262</v>
-      </c>
-      <c r="Y10" s="8" t="n">
-        <v>63.9838633351069</v>
-      </c>
-      <c r="Z10" s="8" t="n">
-        <v>21.29761785174411</v>
-      </c>
-      <c r="AA10" s="8" t="n">
-        <v>2.683382018662976</v>
-      </c>
-      <c r="AB10" s="8" t="n">
-        <v>4.459796628844548</v>
-      </c>
-      <c r="AC10" s="8" t="n">
-        <v>9.296928978152618</v>
-      </c>
-      <c r="AD10" s="8" t="n">
-        <v>6.751587964115469</v>
-      </c>
-      <c r="AE10" s="8" t="n">
-        <v>-6.724314093916462</v>
-      </c>
-      <c r="AF10" s="6" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="AG10" s="6" t="inlineStr"/>
-      <c r="AH10" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AI10" s="7" t="inlineStr">
-        <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | Volume 1.8x avg | OBV rising | Beating NIFTY 1M</t>
-        </is>
-      </c>
-      <c r="AJ10" s="7" t="inlineStr"/>
-      <c r="AK10" s="7" t="inlineStr">
-        <is>
-          <t>[15 Oct 2026] Punjab National Bank (PNB.NS) Climbs 1.67% to ₹118.5 as PSU Bank Stock Approaches Key Resistance - Size Factor - https://www.siam.in/ | [19 Oct 2026] Punjab National Bank shares gain 8% as Q2 profit beats estimates; here’s what analysts said - Upstox | [14 Oct 2026] Punjab National Bank Share Price: Today’s Rise Explained - Univest | [18 Oct 2026] Is Now The Time To Put Punjab National Bank (NSE:PNB) On Your Watchlist? - Simply Wall Street</t>
-        </is>
-      </c>
-      <c r="AL10" s="10" t="inlineStr">
-        <is>
-          <t>Open filings</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>MVGJL</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>Manoj Vaibhav Gems N Jewellers Limited</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr"/>
-      <c r="E11" s="6" t="inlineStr">
-        <is>
-          <t>TREND CONTINUATION</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>BUY ZONE</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="H11" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I11" s="9" t="n">
-        <v>220.3600006103516</v>
-      </c>
-      <c r="J11" s="9" t="n">
-        <v>220.3600006103516</v>
-      </c>
-      <c r="K11" s="9" t="n">
-        <v>218.156400604248</v>
-      </c>
-      <c r="L11" s="9" t="n">
-        <v>222.5636006164551</v>
-      </c>
-      <c r="M11" s="9" t="n">
-        <v>206.0366005706787</v>
-      </c>
-      <c r="N11" s="8" t="n">
-        <v>6.499999999999992</v>
-      </c>
-      <c r="O11" s="9" t="n">
-        <v>235.7852006530762</v>
-      </c>
-      <c r="P11" s="9" t="n">
-        <v>242.3960006713867</v>
-      </c>
-      <c r="Q11" s="8" t="n">
-        <v>1.076923076923078</v>
-      </c>
-      <c r="R11" s="8" t="n">
-        <v>1.538461538461541</v>
-      </c>
-      <c r="S11" s="5" t="n">
-        <v>69</v>
-      </c>
-      <c r="T11" s="5" t="n">
-        <v>15204.84004211426</v>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v>36.36363636363637</v>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v>18.18181818181818</v>
-      </c>
-      <c r="W11" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="X11" s="8" t="n">
-        <v>2.329543882078586</v>
-      </c>
-      <c r="Y11" s="8" t="n">
-        <v>56.18764713704237</v>
-      </c>
-      <c r="Z11" s="8" t="n">
-        <v>38.5651040676958</v>
-      </c>
-      <c r="AA11" s="8" t="n">
-        <v>6.807547746770114</v>
-      </c>
-      <c r="AB11" s="8" t="n">
-        <v>2.746304544283218</v>
-      </c>
-      <c r="AC11" s="8" t="n">
-        <v>39.27442732285695</v>
-      </c>
-      <c r="AD11" s="8" t="n">
-        <v>5.038095879554138</v>
-      </c>
-      <c r="AE11" s="8" t="n">
-        <v>-11.64394306207807</v>
-      </c>
-      <c r="AF11" s="6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AG11" s="6" t="inlineStr"/>
-      <c r="AH11" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AI11" s="7" t="inlineStr">
-        <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | Volume 2.3x avg | OBV rising | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 36% of similar setups</t>
-        </is>
-      </c>
-      <c r="AJ11" s="7" t="inlineStr">
-        <is>
-          <t>RELAXED smallcap</t>
-        </is>
-      </c>
-      <c r="AK11" s="7" t="inlineStr">
-        <is>
-          <t>[20 Oct 2026] how Fair Value spotted 62% gain in Indian jeweller in 3 months - Investing.com India | [16 Oct 2026] Timex Group India Limited (TIMEX.BO) Stock Price, News, Quote &amp; History - Yahoo! Finance Canada</t>
-        </is>
-      </c>
-      <c r="AL11" s="10" t="inlineStr">
-        <is>
-          <t>Open filings</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>TIPSMUSIC</t>
-        </is>
-      </c>
-      <c r="C12" s="7" t="inlineStr">
-        <is>
-          <t>Tips Music Limited</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>Media Entertainment &amp; Publication</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
-        <is>
-          <t>TREND CONTINUATION</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>BUY ZONE</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>74</v>
-      </c>
-      <c r="H12" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I12" s="9" t="n">
-        <v>748</v>
-      </c>
-      <c r="J12" s="9" t="n">
-        <v>748</v>
-      </c>
-      <c r="K12" s="9" t="n">
-        <v>740.52</v>
-      </c>
-      <c r="L12" s="9" t="n">
-        <v>755.48</v>
-      </c>
-      <c r="M12" s="9" t="n">
-        <v>699.38</v>
-      </c>
-      <c r="N12" s="8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O12" s="9" t="n">
-        <v>800.36</v>
-      </c>
-      <c r="P12" s="9" t="n">
-        <v>822.8000000000001</v>
-      </c>
-      <c r="Q12" s="8" t="n">
-        <v>1.076923076923077</v>
-      </c>
-      <c r="R12" s="8" t="n">
-        <v>1.53846153846154</v>
-      </c>
-      <c r="S12" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="T12" s="5" t="n">
-        <v>14960</v>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v>53.33333333333334</v>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v>26.66666666666667</v>
-      </c>
-      <c r="W12" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="X12" s="8" t="n">
-        <v>0.935577019623052</v>
-      </c>
-      <c r="Y12" s="8" t="n">
-        <v>63.58154366124493</v>
-      </c>
-      <c r="Z12" s="8" t="n">
-        <v>20.41909425836643</v>
-      </c>
-      <c r="AA12" s="8" t="n">
-        <v>4.223658915259712</v>
-      </c>
-      <c r="AB12" s="8" t="n">
-        <v>13.72966186969509</v>
-      </c>
-      <c r="AC12" s="8" t="n">
-        <v>5.026676099320526</v>
-      </c>
-      <c r="AD12" s="8" t="n">
-        <v>16.02145320496601</v>
-      </c>
-      <c r="AE12" s="8" t="n">
-        <v>-4.713375796178343</v>
-      </c>
-      <c r="AF12" s="6" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="AG12" s="6" t="inlineStr"/>
-      <c r="AH12" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AI12" s="7" t="inlineStr">
-        <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | OBV rising | Near 52W high | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 53% of similar setups</t>
-        </is>
-      </c>
-      <c r="AJ12" s="7" t="inlineStr">
-        <is>
-          <t>Extended &gt;7% above EMA20 | Volume below average</t>
-        </is>
-      </c>
-      <c r="AK12" s="7" t="inlineStr">
-        <is>
-          <t>[18 Oct 2026] TIPSMUSIC Stock Price and Chart — NSE:TIPSMUSIC - TradingView | [15 Oct 2026] Tips Music (NSEI:TIPSMUSIC) Stock Forecast &amp; Analyst Predictions - Simply Wall Street | [15 Oct 2026] Tips Music Q2FY27 Results: Analyst call scheduled for Oct 15 - scanx.trade | [15 Oct 2026] Earnings call transcript: Tips Music posts strong Q2 FY27 revenue growth - Investing.com India</t>
-        </is>
-      </c>
-      <c r="AL12" s="10" t="inlineStr">
-        <is>
-          <t>Open filings</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>MGEL</t>
-        </is>
-      </c>
-      <c r="C13" s="7" t="inlineStr">
-        <is>
-          <t>Mangalam Global Enterprise Limited</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>NEAR BREAKOUT</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>WAIT - trigger not hit (buy above 17.52)</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>73</v>
-      </c>
-      <c r="H13" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I13" s="9" t="n">
-        <v>17.04999923706055</v>
-      </c>
-      <c r="J13" s="9" t="n">
-        <v>17.04999923706055</v>
-      </c>
-      <c r="K13" s="9" t="n">
-        <v>17.5175</v>
-      </c>
-      <c r="L13" s="9" t="n">
-        <v>17.7625</v>
-      </c>
-      <c r="M13" s="9" t="n">
-        <v>16.4934</v>
-      </c>
-      <c r="N13" s="8" t="n">
-        <v>6.499999999999996</v>
-      </c>
-      <c r="O13" s="9" t="n">
-        <v>18.8748</v>
-      </c>
-      <c r="P13" s="9" t="n">
-        <v>19.404</v>
-      </c>
-      <c r="Q13" s="8" t="n">
-        <v>1.076923076923077</v>
-      </c>
-      <c r="R13" s="8" t="n">
-        <v>1.538461538461542</v>
-      </c>
-      <c r="S13" s="5" t="n">
-        <v>872</v>
-      </c>
-      <c r="T13" s="5" t="n">
-        <v>15382.08</v>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v>47.72727272727273</v>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v>27.27272727272727</v>
-      </c>
-      <c r="W13" s="5" t="n">
-        <v>44</v>
-      </c>
-      <c r="X13" s="8" t="n">
-        <v>1.122763536274079</v>
-      </c>
-      <c r="Y13" s="8" t="n">
-        <v>69.82740618209755</v>
-      </c>
-      <c r="Z13" s="8" t="n">
-        <v>24.8128267353296</v>
-      </c>
-      <c r="AA13" s="8" t="n">
-        <v>4.594131726800053</v>
-      </c>
-      <c r="AB13" s="8" t="n">
-        <v>9.015337997353502</v>
-      </c>
-      <c r="AC13" s="8" t="n">
-        <v>2.402400166334551</v>
-      </c>
-      <c r="AD13" s="8" t="n">
-        <v>11.30712933262442</v>
-      </c>
-      <c r="AE13" s="8" t="n">
-        <v>-2.571432931082585</v>
-      </c>
-      <c r="AF13" s="6" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="AG13" s="6" t="inlineStr"/>
-      <c r="AH13" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AI13" s="7" t="inlineStr">
-        <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | OBV rising | Near 52W high | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 48% of similar setups</t>
-        </is>
-      </c>
-      <c r="AJ13" s="7" t="inlineStr">
-        <is>
-          <t>RELAXED smallcap | Negative headline - check news</t>
-        </is>
-      </c>
-      <c r="AK13" s="7" t="inlineStr">
-        <is>
-          <t>[18 Oct 2026] Mangalam Global Enterprise (NSEI:MGEL) - Stock Analysis - Simply Wall Street | [19 Oct 2026] Mangalam Global Enterprise (MGEL.NS) Holds Near ₹17.02 as ₹17.87 Resistance Comes Into Focus - KAMA Signal - https://www.siam.in/ | [19 Oct 2026] Mangalam Global Q2FY27 net profit drops 53% YoY to ₹831.72 lakh - scanx.trade | [21 Oct 2026] Mangalam Global Enterprise (NSE:MGEL): What Did Its Q2 FY27 Results Newspaper Filing Disclose? - Kalkine India</t>
-        </is>
-      </c>
-      <c r="AL13" s="10" t="inlineStr">
-        <is>
-          <t>Open filings</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>MASTEK</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>Mastek Limited</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>MOMENTUM</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>BUY ZONE</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>73</v>
-      </c>
-      <c r="H14" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I14" s="9" t="n">
-        <v>1847.199951171875</v>
-      </c>
-      <c r="J14" s="9" t="n">
-        <v>1847.199951171875</v>
-      </c>
-      <c r="K14" s="9" t="n">
-        <v>1828.727951660156</v>
-      </c>
-      <c r="L14" s="9" t="n">
-        <v>1865.671950683594</v>
-      </c>
-      <c r="M14" s="9" t="n">
-        <v>1734.970432977554</v>
-      </c>
-      <c r="N14" s="8" t="n">
-        <v>6.075656191043183</v>
-      </c>
-      <c r="O14" s="9" t="n">
-        <v>1976.503947753906</v>
-      </c>
-      <c r="P14" s="9" t="n">
-        <v>2031.919946289063</v>
-      </c>
-      <c r="Q14" s="8" t="n">
-        <v>1.152138926215</v>
-      </c>
-      <c r="R14" s="8" t="n">
-        <v>1.645912751735713</v>
-      </c>
-      <c r="S14" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="T14" s="5" t="n">
-        <v>14777.599609375</v>
-      </c>
-      <c r="U14" s="6" t="inlineStr"/>
-      <c r="V14" s="6" t="inlineStr"/>
-      <c r="W14" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="X14" s="8" t="n">
-        <v>2.247428917120387</v>
-      </c>
-      <c r="Y14" s="8" t="n">
-        <v>68.49224564918718</v>
-      </c>
-      <c r="Z14" s="8" t="n">
-        <v>27.11851077235017</v>
-      </c>
-      <c r="AA14" s="8" t="n">
-        <v>3.375364550579543</v>
-      </c>
-      <c r="AB14" s="8" t="n">
-        <v>16.30777030366317</v>
-      </c>
-      <c r="AC14" s="8" t="n">
-        <v>6.657266066082657</v>
-      </c>
-      <c r="AD14" s="8" t="n">
-        <v>18.59956163893409</v>
-      </c>
-      <c r="AE14" s="8" t="n">
-        <v>-21.05312803023571</v>
-      </c>
-      <c r="AF14" s="6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AG14" s="6" t="inlineStr"/>
-      <c r="AH14" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AI14" s="7" t="inlineStr">
-        <is>
-          <t>MACD bullish | ADX&gt;=25 strong trend | Volume 2.2x avg | OBV rising | Closed above prior 20D high | BB squeeze before move | Beating NIFTY 1M</t>
-        </is>
-      </c>
-      <c r="AJ14" s="7" t="inlineStr">
-        <is>
-          <t>Extended &gt;7% above EMA20</t>
-        </is>
-      </c>
-      <c r="AK14" s="7" t="inlineStr">
-        <is>
-          <t>[21 Oct 2026] Mastek Q2FY27 Earnings Call Set for October 26, 2026 - Kalkine India | [17 Oct 2026] SRIT India Ltd Share Price Today NSE/BSE Charts - Alice Blue | [20 Oct 2026] Mastek Selected by Staffordshire County Council to Drive AI Enabled - Oracle Cloud Transformation - openPR.com</t>
-        </is>
-      </c>
-      <c r="AL14" s="10" t="inlineStr">
-        <is>
-          <t>Open filings</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>AAREYDRUGS</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>Aarey Drugs &amp; Pharmaceuticals Limited</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>NEAR BREAKOUT</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>WAIT - trigger not hit (buy above 114.91)</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>72</v>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="n">
-        <v>111.9300003051758</v>
-      </c>
-      <c r="J15" s="9" t="n">
-        <v>111.9300003051758</v>
-      </c>
-      <c r="K15" s="9" t="n">
-        <v>114.9148030548096</v>
-      </c>
-      <c r="L15" s="9" t="n">
-        <v>116.5220030975342</v>
-      </c>
-      <c r="M15" s="9" t="n">
-        <v>108.1967068762207</v>
-      </c>
-      <c r="N15" s="8" t="n">
-        <v>6.499999999999996</v>
-      </c>
-      <c r="O15" s="9" t="n">
-        <v>123.8186912915039</v>
-      </c>
-      <c r="P15" s="9" t="n">
-        <v>127.290243383789</v>
-      </c>
-      <c r="Q15" s="8" t="n">
-        <v>1.076923076923079</v>
-      </c>
-      <c r="R15" s="8" t="n">
-        <v>1.538461538461541</v>
-      </c>
-      <c r="S15" s="5" t="n">
-        <v>132</v>
-      </c>
-      <c r="T15" s="5" t="n">
-        <v>15274.82920605468</v>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v>68.25396825396825</v>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v>46.03174603174603</v>
-      </c>
-      <c r="W15" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="X15" s="8" t="n">
-        <v>0.9920496037316263</v>
-      </c>
-      <c r="Y15" s="8" t="n">
-        <v>66.91233739260727</v>
-      </c>
-      <c r="Z15" s="8" t="n">
-        <v>20.98602943571883</v>
-      </c>
-      <c r="AA15" s="8" t="n">
-        <v>4.419068066182359</v>
-      </c>
-      <c r="AB15" s="8" t="n">
-        <v>9.595616680024776</v>
-      </c>
-      <c r="AC15" s="8" t="n">
-        <v>44.36992398749382</v>
-      </c>
-      <c r="AD15" s="8" t="n">
-        <v>11.8874080152957</v>
-      </c>
-      <c r="AE15" s="8" t="n">
-        <v>-2.500002326034856</v>
-      </c>
-      <c r="AF15" s="6" t="inlineStr"/>
-      <c r="AG15" s="6" t="inlineStr"/>
-      <c r="AH15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AI15" s="7" t="inlineStr">
-        <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | OBV rising | Near 52W high | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 68% of similar setups</t>
-        </is>
-      </c>
-      <c r="AJ15" s="7" t="inlineStr">
-        <is>
-          <t>Volume below average</t>
-        </is>
-      </c>
-      <c r="AK15" s="7" t="inlineStr"/>
-      <c r="AL15" s="10" t="inlineStr">
-        <is>
-          <t>Open filings</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>MANOMAY</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Manomay Tex India Limited</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr"/>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>EMA20 PULLBACK</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>BUY ZONE</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>72</v>
-      </c>
-      <c r="H16" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I16" s="9" t="n">
-        <v>242.7700042724609</v>
-      </c>
-      <c r="J16" s="9" t="n">
-        <v>242.7700042724609</v>
-      </c>
-      <c r="K16" s="9" t="n">
-        <v>238.1906049900909</v>
-      </c>
-      <c r="L16" s="9" t="n">
-        <v>243.9838542938232</v>
-      </c>
-      <c r="M16" s="9" t="n">
-        <v>226.989953994751</v>
-      </c>
-      <c r="N16" s="8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O16" s="9" t="n">
-        <v>259.7639045715332</v>
-      </c>
-      <c r="P16" s="9" t="n">
-        <v>267.047004699707</v>
-      </c>
-      <c r="Q16" s="8" t="n">
-        <v>1.076923076923077</v>
-      </c>
-      <c r="R16" s="8" t="n">
-        <v>1.538461538461539</v>
-      </c>
-      <c r="S16" s="5" t="n">
-        <v>63</v>
-      </c>
-      <c r="T16" s="5" t="n">
-        <v>15294.51026916504</v>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v>57.14285714285714</v>
-      </c>
-      <c r="V16" s="8" t="n">
-        <v>38.77551020408163</v>
-      </c>
-      <c r="W16" s="5" t="n">
-        <v>49</v>
-      </c>
-      <c r="X16" s="8" t="n">
-        <v>1.209249903962571</v>
-      </c>
-      <c r="Y16" s="8" t="n">
-        <v>58.16607234088248</v>
-      </c>
-      <c r="Z16" s="8" t="n">
-        <v>21.42572437916148</v>
-      </c>
-      <c r="AA16" s="8" t="n">
-        <v>3.883556054230739</v>
-      </c>
-      <c r="AB16" s="8" t="n">
-        <v>5.699238947276397</v>
-      </c>
-      <c r="AC16" s="8" t="n">
-        <v>21.06418279075211</v>
-      </c>
-      <c r="AD16" s="8" t="n">
-        <v>7.991030282547317</v>
-      </c>
-      <c r="AE16" s="8" t="n">
-        <v>-6.583808022501369</v>
-      </c>
-      <c r="AF16" s="6" t="inlineStr"/>
-      <c r="AG16" s="6" t="inlineStr"/>
-      <c r="AH16" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AI16" s="7" t="inlineStr">
-        <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | OBV rising | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 57% of similar setups</t>
-        </is>
-      </c>
-      <c r="AJ16" s="7" t="inlineStr"/>
-      <c r="AK16" s="7" t="inlineStr"/>
-      <c r="AL16" s="10" t="inlineStr">
-        <is>
-          <t>Open filings</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t>HEXT</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>Hexaware Technologies Limited</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
-        <is>
-          <t>BREAKOUT</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>BUY ZONE</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>72</v>
-      </c>
-      <c r="H17" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I17" s="9" t="n">
-        <v>604.5999755859375</v>
-      </c>
-      <c r="J17" s="9" t="n">
-        <v>604.5999755859375</v>
-      </c>
-      <c r="K17" s="9" t="n">
-        <v>598.5539758300781</v>
-      </c>
-      <c r="L17" s="9" t="n">
-        <v>610.6459753417969</v>
-      </c>
-      <c r="M17" s="9" t="n">
-        <v>567.6477133358892</v>
-      </c>
-      <c r="N17" s="8" t="n">
-        <v>6.111853083393969</v>
-      </c>
-      <c r="O17" s="9" t="n">
-        <v>646.9219738769532</v>
-      </c>
-      <c r="P17" s="9" t="n">
-        <v>665.0599731445313</v>
-      </c>
-      <c r="Q17" s="8" t="n">
-        <v>1.145315488524938</v>
-      </c>
-      <c r="R17" s="8" t="n">
-        <v>1.636164983607054</v>
-      </c>
-      <c r="S17" s="5" t="n">
-        <v>27</v>
-      </c>
-      <c r="T17" s="5" t="n">
-        <v>16324.19934082031</v>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="X17" s="8" t="n">
-        <v>1.452786904736316</v>
-      </c>
-      <c r="Y17" s="8" t="n">
-        <v>75.69258148306497</v>
-      </c>
-      <c r="Z17" s="8" t="n">
-        <v>34.25890727221858</v>
-      </c>
-      <c r="AA17" s="8" t="n">
-        <v>3.395473935218868</v>
-      </c>
-      <c r="AB17" s="8" t="n">
-        <v>15.26069767531157</v>
-      </c>
-      <c r="AC17" s="8" t="n">
-        <v>7.95464490027582</v>
-      </c>
-      <c r="AD17" s="8" t="n">
-        <v>17.55248901058249</v>
-      </c>
-      <c r="AE17" s="8" t="n">
-        <v>-23.73564748088444</v>
-      </c>
-      <c r="AF17" s="6" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="AG17" s="6" t="inlineStr"/>
-      <c r="AH17" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AI17" s="7" t="inlineStr">
-        <is>
-          <t>MACD bullish | ADX&gt;=25 strong trend | Volume 1.5x avg | OBV rising | Closed above prior 20D high | BB squeeze before move | Beating NIFTY 1M</t>
-        </is>
-      </c>
-      <c r="AJ17" s="7" t="inlineStr">
-        <is>
-          <t>RELAXED smallcap</t>
-        </is>
-      </c>
-      <c r="AK17" s="7" t="inlineStr">
-        <is>
-          <t>[20 Oct 2026] Hexaware Technologies (NSE:HEXT): What Is the 2nd Interim Dividend Declared for FY2026? - Kalkine India | [20 Oct 2026] Hexaware Technologies Ltd declares 2nd interim dividend of Rs. 9.50 - EquityBulls | [16 Oct 2026] Tata Technologies (NSEI:TATATECH) Stock Forecast &amp; Analyst Predictions - Simply Wall Street | [15 Oct 2026] Hexaware Technologies (NSE:HEXT): Is a Second Interim Dividend for FY2026 on the Way? - Kalkine India</t>
-        </is>
-      </c>
-      <c r="AL17" s="10" t="inlineStr">
-        <is>
-          <t>Open filings</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>COFORGE</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>Coforge Limited</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>Information Technology</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>NEAR BREAKOUT</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>WAIT - trigger not hit (buy above 1971.97)</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>71</v>
-      </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I18" s="9" t="n">
-        <v>1951</v>
-      </c>
-      <c r="J18" s="9" t="n">
-        <v>1951</v>
-      </c>
-      <c r="K18" s="9" t="n">
-        <v>1971.97</v>
-      </c>
-      <c r="L18" s="9" t="n">
-        <v>1999.55</v>
-      </c>
-      <c r="M18" s="9" t="n">
-        <v>1881.476165209958</v>
-      </c>
-      <c r="N18" s="8" t="n">
-        <v>5.251583010537089</v>
-      </c>
-      <c r="O18" s="9" t="n">
-        <v>2124.7632</v>
-      </c>
-      <c r="P18" s="9" t="n">
-        <v>2184.336</v>
-      </c>
-      <c r="Q18" s="8" t="n">
-        <v>1.332931420098433</v>
-      </c>
-      <c r="R18" s="8" t="n">
-        <v>1.90418774299776</v>
-      </c>
-      <c r="S18" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="T18" s="5" t="n">
-        <v>17871.84</v>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v>35.71428571428572</v>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v>9.523809523809524</v>
-      </c>
-      <c r="W18" s="5" t="n">
-        <v>42</v>
-      </c>
-      <c r="X18" s="8" t="n">
-        <v>1.002842997044937</v>
-      </c>
-      <c r="Y18" s="8" t="n">
-        <v>62.5154729366246</v>
-      </c>
-      <c r="Z18" s="8" t="n">
-        <v>19.30972655528189</v>
-      </c>
-      <c r="AA18" s="8" t="n">
-        <v>2.969526590068949</v>
-      </c>
-      <c r="AB18" s="8" t="n">
-        <v>5.975013579576327</v>
-      </c>
-      <c r="AC18" s="8" t="n">
-        <v>30.89324987006981</v>
-      </c>
-      <c r="AD18" s="8" t="n">
-        <v>8.266804914847247</v>
-      </c>
-      <c r="AE18" s="8" t="n">
-        <v>-3.473181915088297</v>
-      </c>
-      <c r="AF18" s="6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AG18" s="6" t="inlineStr"/>
-      <c r="AH18" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AI18" s="7" t="inlineStr">
-        <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | OBV rising | Near 52W high | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 36% of similar setups</t>
-        </is>
-      </c>
-      <c r="AJ18" s="7" t="inlineStr">
-        <is>
-          <t>Weak trend (ADX&lt;20)</t>
-        </is>
-      </c>
-      <c r="AK18" s="7" t="inlineStr">
-        <is>
-          <t>[15 Oct 2026] Coforge (NSEI:COFORGE) Stock Price - Simply Wall Street | [16 Oct 2026] Tata Consultancy Services Limited (TCS.BO) stock price, news, quote and history - Yahoo Finance UK | [19 Oct 2026] Coforge schedules October 23 results call for Coforge stock - ad-hoc-news.de | [19 Oct 2026] HCL Technologies Limited (HCLTECH.NS) stock price, news, quote and history - Yahoo Finance UK</t>
-        </is>
-      </c>
-      <c r="AL18" s="10" t="inlineStr">
-        <is>
-          <t>Open filings</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>SINGERIND</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>Singer India Limited</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>MOMENTUM</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>BUY ZONE</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>71</v>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I19" s="9" t="n">
-        <v>88.41000366210938</v>
-      </c>
-      <c r="J19" s="9" t="n">
-        <v>88.41000366210938</v>
-      </c>
-      <c r="K19" s="9" t="n">
-        <v>87.52590362548828</v>
-      </c>
-      <c r="L19" s="9" t="n">
-        <v>89.29410369873047</v>
-      </c>
-      <c r="M19" s="9" t="n">
-        <v>82.66335342407227</v>
-      </c>
-      <c r="N19" s="8" t="n">
-        <v>6.499999999999996</v>
-      </c>
-      <c r="O19" s="9" t="n">
-        <v>94.59870391845703</v>
-      </c>
-      <c r="P19" s="9" t="n">
-        <v>97.25100402832032</v>
-      </c>
-      <c r="Q19" s="8" t="n">
-        <v>1.076923076923078</v>
-      </c>
-      <c r="R19" s="8" t="n">
-        <v>1.538461538461541</v>
-      </c>
-      <c r="S19" s="5" t="n">
-        <v>174</v>
-      </c>
-      <c r="T19" s="5" t="n">
-        <v>15383.34063720703</v>
-      </c>
-      <c r="U19" s="6" t="inlineStr"/>
-      <c r="V19" s="6" t="inlineStr"/>
-      <c r="W19" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="X19" s="8" t="n">
-        <v>1.660547293380202</v>
-      </c>
-      <c r="Y19" s="8" t="n">
-        <v>66.90974802020604</v>
-      </c>
-      <c r="Z19" s="8" t="n">
-        <v>19.52771574707711</v>
-      </c>
-      <c r="AA19" s="8" t="n">
-        <v>5.283275396041455</v>
-      </c>
-      <c r="AB19" s="8" t="n">
-        <v>15.90194687588891</v>
-      </c>
-      <c r="AC19" s="8" t="n">
-        <v>36.97125076460732</v>
-      </c>
-      <c r="AD19" s="8" t="n">
-        <v>18.19373821115983</v>
-      </c>
-      <c r="AE19" s="6" t="inlineStr"/>
-      <c r="AF19" s="6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
-      <c r="AG19" s="6" t="inlineStr"/>
-      <c r="AH19" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="AI19" s="7" t="inlineStr">
-        <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | Volume 1.7x avg | OBV rising | BB squeeze before move | Beating NIFTY 1M</t>
-        </is>
-      </c>
-      <c r="AJ19" s="7" t="inlineStr">
-        <is>
-          <t>RELAXED smallcap</t>
-        </is>
-      </c>
-      <c r="AK19" s="7" t="inlineStr">
-        <is>
-          <t>[18 Oct 2026] Singer India AGM resolutions pass with 99.99% shareholder support - scanx.trade | [18 Oct 2026] Singer India net profit turns positive in Q1FY27; revenue up 57% - scanx.trade | [16 Oct 2026] Volume Gainers Today, October 16, 2026, at 3:30 PM IST - HDFC Sky</t>
-        </is>
-      </c>
-      <c r="AL19" s="10" t="inlineStr">
-        <is>
-          <t>Open filings</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:AL19"/>
-  <conditionalFormatting sqref="F5:F19">
+  <autoFilter ref="A4:AL9"/>
+  <conditionalFormatting sqref="F5:F9">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>LEFT(F5,3)="BUY"</formula>
     </cfRule>
@@ -3725,7 +1953,7 @@
       <formula>OR(LEFT(F5,5)="AVOID",LEFT(F5,6)="REVIEW",LEFT(F5,4)="SKIP")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:G19">
+  <conditionalFormatting sqref="G5:G9">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="50"/>
@@ -3743,16 +1971,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL7" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL8" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL9" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL11" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL12" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL13" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL14" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL15" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL16" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL17" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL18" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AL19" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3817,7 +2035,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Universe: NSE_LISTED | NIFTY regime: BEAR | Generated: 21-Oct-2026 16:46 | Targets: +7% / +10% | *Qty sized for Rs 100,000 capital, 1% risk</t>
+          <t>Universe: NSE_LISTED | NIFTY regime: BEAR | Generated: 21-Oct-2026 19:34 | Targets: +7% / +10% | *Qty sized for Rs 100,000 capital, 1% risk</t>
         </is>
       </c>
     </row>
@@ -4019,12 +2237,12 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>TATVA</t>
+          <t>MVGJL</t>
         </is>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>Tatva Chintan Pharma Chem Limited</t>
+          <t>Manoj Vaibhav Gems N Jewellers Limited</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr"/>
@@ -4039,7 +2257,7 @@
         </is>
       </c>
       <c r="G5" s="5" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
@@ -4047,77 +2265,77 @@
         </is>
       </c>
       <c r="I5" s="9" t="n">
-        <v>1890.099975585938</v>
+        <v>220.3600006103516</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>1890.099975585938</v>
+        <v>220.3600006103516</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>1871.198975830078</v>
+        <v>218.156400604248</v>
       </c>
       <c r="L5" s="9" t="n">
-        <v>1909.000975341797</v>
+        <v>222.5636006164551</v>
       </c>
       <c r="M5" s="9" t="n">
-        <v>1773.189475708008</v>
+        <v>206.0366005706787</v>
       </c>
       <c r="N5" s="8" t="n">
-        <v>6.185413543624166</v>
+        <v>6.499999999999992</v>
       </c>
       <c r="O5" s="9" t="n">
-        <v>2022.406973876953</v>
+        <v>235.7852006530762</v>
       </c>
       <c r="P5" s="9" t="n">
-        <v>2079.109973144532</v>
+        <v>242.3960006713867</v>
       </c>
       <c r="Q5" s="8" t="n">
-        <v>1.13169474451963</v>
+        <v>1.076923076923078</v>
       </c>
       <c r="R5" s="8" t="n">
-        <v>1.616706777885186</v>
+        <v>1.538461538461541</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>15120.7998046875</v>
+        <v>15204.84004211426</v>
       </c>
       <c r="U5" s="8" t="n">
-        <v>77.08333333333334</v>
+        <v>36.36363636363637</v>
       </c>
       <c r="V5" s="8" t="n">
-        <v>58.33333333333334</v>
+        <v>18.18181818181818</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="X5" s="8" t="n">
-        <v>8.084786396208008</v>
+        <v>2.329543882078586</v>
       </c>
       <c r="Y5" s="8" t="n">
-        <v>56.30276892733634</v>
+        <v>56.18764713704237</v>
       </c>
       <c r="Z5" s="8" t="n">
-        <v>26.90121478247604</v>
+        <v>38.5651040676958</v>
       </c>
       <c r="AA5" s="8" t="n">
-        <v>5.919967289065546</v>
+        <v>6.807547746770114</v>
       </c>
       <c r="AB5" s="8" t="n">
-        <v>6.773247526907267</v>
+        <v>2.746304544283218</v>
       </c>
       <c r="AC5" s="8" t="n">
-        <v>12.30748274392155</v>
+        <v>39.27442732285695</v>
       </c>
       <c r="AD5" s="8" t="n">
-        <v>9.065038862178188</v>
+        <v>5.038095879554138</v>
       </c>
       <c r="AE5" s="8" t="n">
-        <v>-10.57438076001934</v>
+        <v>-11.64394306207807</v>
       </c>
       <c r="AF5" s="6" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AG5" s="6" t="inlineStr"/>
@@ -4128,17 +2346,17 @@
       </c>
       <c r="AI5" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | Volume 8.1x avg | Beating NIFTY 1M | Stock hit +7% in 15d 77% of similar setups</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | Volume 2.3x avg | OBV rising | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 36% of similar setups</t>
         </is>
       </c>
       <c r="AJ5" s="7" t="inlineStr">
         <is>
-          <t>High volatility</t>
+          <t>RELAXED smallcap | High volatility</t>
         </is>
       </c>
       <c r="AK5" s="7" t="inlineStr">
         <is>
-          <t>[20 Oct 2026] Tatva Chintan Pharma Chem (TATVA.NS) Slips 2.09% to ₹1903.4, Pulling Back Toward Key Support - Trading Ideas - www.siam.in | [19 Oct 2026] Tatva Chintan Q2FY27 results: Revenue up 76% YoY to ₹2,173 crore - scanx.trade | [19 Oct 2026] Tatva Chintan Pharma Chem (NSE:TATVA): What Did Q2 FY27 Results Reveal? - Kalkine India | [19 Oct 2026] Tatva Chintan Q2 Profit Jumps 116% to Rs 21.45 Crore - Whalesbook</t>
+          <t>[20 Oct 2026] how Fair Value spotted 62% gain in Indian jeweller in 3 months - Investing.com India | [16 Oct 2026] Timex Group India Limited (TIMEX.BO) Stock Price, News, Quote &amp; History - Yahoo! Finance Canada</t>
         </is>
       </c>
       <c r="AL5" s="10" t="inlineStr">
@@ -4153,18 +2371,22 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>KROSS</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>Kross Limited</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr"/>
+          <t>Punjab National Bank</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>TREND CONTINUATION</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -4173,7 +2395,7 @@
         </is>
       </c>
       <c r="G6" s="5" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
@@ -4181,73 +2403,73 @@
         </is>
       </c>
       <c r="I6" s="9" t="n">
-        <v>278.2999877929688</v>
+        <v>122.5</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>278.2999877929688</v>
+        <v>122.5</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>275.5169879150391</v>
+        <v>121.275</v>
       </c>
       <c r="L6" s="9" t="n">
-        <v>281.0829876708984</v>
+        <v>123.725</v>
       </c>
       <c r="M6" s="9" t="n">
-        <v>260.2104885864258</v>
+        <v>116.5831426488481</v>
       </c>
       <c r="N6" s="8" t="n">
-        <v>6.499999999999989</v>
+        <v>4.830087633593356</v>
       </c>
       <c r="O6" s="9" t="n">
-        <v>297.7809869384766</v>
+        <v>131.075</v>
       </c>
       <c r="P6" s="9" t="n">
-        <v>306.1299865722656</v>
+        <v>134.75</v>
       </c>
       <c r="Q6" s="8" t="n">
-        <v>1.07692307692308</v>
+        <v>1.449249067721851</v>
       </c>
       <c r="R6" s="8" t="n">
-        <v>1.538461538461542</v>
+        <v>2.070355811031212</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>55</v>
+        <v>163</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>15306.49932861328</v>
+        <v>19967.5</v>
       </c>
       <c r="U6" s="8" t="n">
-        <v>51.51515151515152</v>
+        <v>15.38461538461539</v>
       </c>
       <c r="V6" s="8" t="n">
-        <v>39.39393939393939</v>
+        <v>3.846153846153846</v>
       </c>
       <c r="W6" s="5" t="n">
-        <v>33</v>
+        <v>78</v>
       </c>
       <c r="X6" s="8" t="n">
-        <v>1.241093910380829</v>
+        <v>1.825383104202262</v>
       </c>
       <c r="Y6" s="8" t="n">
-        <v>60.3548257207129</v>
+        <v>63.9838633351069</v>
       </c>
       <c r="Z6" s="8" t="n">
-        <v>34.96697287402402</v>
+        <v>21.29761785174411</v>
       </c>
       <c r="AA6" s="8" t="n">
-        <v>6.413843370810207</v>
+        <v>2.683382018662976</v>
       </c>
       <c r="AB6" s="8" t="n">
-        <v>16.35101172806885</v>
+        <v>4.459796628844548</v>
       </c>
       <c r="AC6" s="8" t="n">
-        <v>31.75211542963898</v>
+        <v>9.296928978152618</v>
       </c>
       <c r="AD6" s="8" t="n">
-        <v>18.64280306333978</v>
+        <v>6.751587964115469</v>
       </c>
       <c r="AE6" s="8" t="n">
-        <v>-14.73652175335831</v>
+        <v>-6.724314093916462</v>
       </c>
       <c r="AF6" s="6" t="inlineStr">
         <is>
@@ -4262,17 +2484,13 @@
       </c>
       <c r="AI6" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | OBV rising | Beating NIFTY 1M | Stock hit +7% in 15d 52% of similar setups</t>
-        </is>
-      </c>
-      <c r="AJ6" s="7" t="inlineStr">
-        <is>
-          <t>Extended &gt;7% above EMA20 | High volatility</t>
-        </is>
-      </c>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | Volume 1.8x avg | OBV rising | Beating NIFTY 1M</t>
+        </is>
+      </c>
+      <c r="AJ6" s="7" t="inlineStr"/>
       <c r="AK6" s="7" t="inlineStr">
         <is>
-          <t>[16 Oct 2026] KROSS LIMITED Share Price - Upstox | [19 Oct 2026] Kross Limited September Quarter Results and Stock Update - Kalkine India | [19 Oct 2026] Kross share price jumps 20% after Q2 results: What lies ahead? Technical analyst weighs in - Livemint | [20 Oct 2026] Kross Ltd uploads audio recording of Q2FY27 earnings conference call - scanx.trade</t>
+          <t>[15 Oct 2026] Punjab National Bank (PNB.NS) Climbs 1.67% to ₹118.5 as PSU Bank Stock Approaches Key Resistance - Size Factor - https://www.siam.in/ | [16 Oct 2026] PNB Outlook for the Week - Equitypandit | [19 Oct 2026] Punjab National Bank shares gain 8% as Q2 profit beats estimates; here’s what analysts said - Upstox | [14 Oct 2026] Punjab National Bank Share Price: Today’s Rise Explained - Univest</t>
         </is>
       </c>
       <c r="AL6" s="10" t="inlineStr">
@@ -4287,18 +2505,22 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>PREMEXPLN</t>
+          <t>TIPSMUSIC</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Premier Explosives Limited</t>
-        </is>
-      </c>
-      <c r="D7" s="6" t="inlineStr"/>
+          <t>Tips Music Limited</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Media Entertainment &amp; Publication</t>
+        </is>
+      </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>NEAR BREAKOUT</t>
+          <t>TREND CONTINUATION</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
@@ -4307,7 +2529,7 @@
         </is>
       </c>
       <c r="G7" s="5" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
@@ -4315,77 +2537,77 @@
         </is>
       </c>
       <c r="I7" s="9" t="n">
-        <v>692.5</v>
+        <v>748</v>
       </c>
       <c r="J7" s="9" t="n">
-        <v>692.5</v>
+        <v>748</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>695.2445377807617</v>
+        <v>740.52</v>
       </c>
       <c r="L7" s="9" t="n">
-        <v>704.9682376098632</v>
+        <v>755.48</v>
       </c>
       <c r="M7" s="9" t="n">
-        <v>679.103196064453</v>
+        <v>699.38</v>
       </c>
       <c r="N7" s="8" t="n">
-        <v>3.000000000000007</v>
+        <v>6.5</v>
       </c>
       <c r="O7" s="9" t="n">
-        <v>749.1138348339842</v>
+        <v>800.36</v>
       </c>
       <c r="P7" s="9" t="n">
-        <v>770.1170264648437</v>
+        <v>822.8000000000001</v>
       </c>
       <c r="Q7" s="8" t="n">
-        <v>2.333333333333328</v>
+        <v>1.076923076923077</v>
       </c>
       <c r="R7" s="8" t="n">
-        <v>3.333333333333328</v>
+        <v>1.53846153846154</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>19602.97885546875</v>
+        <v>14960</v>
       </c>
       <c r="U7" s="8" t="n">
-        <v>48.48484848484848</v>
+        <v>53.33333333333334</v>
       </c>
       <c r="V7" s="8" t="n">
-        <v>30.3030303030303</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="X7" s="8" t="n">
-        <v>4.153208308318388</v>
+        <v>0.935577019623052</v>
       </c>
       <c r="Y7" s="8" t="n">
-        <v>66.70787117571641</v>
+        <v>63.58154366124482</v>
       </c>
       <c r="Z7" s="8" t="n">
-        <v>46.76226185030922</v>
+        <v>20.41909425836191</v>
       </c>
       <c r="AA7" s="8" t="n">
-        <v>1.130474203678186</v>
+        <v>4.223658915259715</v>
       </c>
       <c r="AB7" s="8" t="n">
-        <v>3.705784997361627</v>
+        <v>13.72966186969509</v>
       </c>
       <c r="AC7" s="8" t="n">
-        <v>5.369303159076821</v>
+        <v>5.026676099320526</v>
       </c>
       <c r="AD7" s="8" t="n">
-        <v>5.997576332632548</v>
+        <v>16.02145320496601</v>
       </c>
       <c r="AE7" s="8" t="n">
-        <v>-16.48422293160215</v>
+        <v>-4.713375796178343</v>
       </c>
       <c r="AF7" s="6" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AG7" s="6" t="inlineStr"/>
@@ -4396,17 +2618,17 @@
       </c>
       <c r="AI7" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | Volume 4.2x avg | OBV rising | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 48% of similar setups</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | OBV rising | Near 52W high | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 53% of similar setups</t>
         </is>
       </c>
       <c r="AJ7" s="7" t="inlineStr">
         <is>
-          <t>RELAXED smallcap</t>
+          <t>Extended &gt;7% above EMA20 | Volume below average</t>
         </is>
       </c>
       <c r="AK7" s="7" t="inlineStr">
         <is>
-          <t>[16 Oct 2026] Premier Explosives (PREMEXPLN.NS) Holds Near ₹691 as Stock Consolidates Below ₹726 Resistance - Wyckoff Accumulation - https://www.siam.in/</t>
+          <t>[18 Oct 2026] TIPSMUSIC Stock Price and Chart — NSE:TIPSMUSIC - TradingView | [15 Oct 2026] Tips Music (NSEI:TIPSMUSIC) Stock Forecast &amp; Analyst Predictions - Simply Wall Street | [15 Oct 2026] Tips Music Q2FY27 Results: Analyst call scheduled for Oct 15 - scanx.trade | [15 Oct 2026] Tips Music TIPSMUSIC Interim Dividend FY27 Q2 Results - Kalkine India</t>
         </is>
       </c>
       <c r="AL7" s="10" t="inlineStr">
@@ -4421,27 +2643,27 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>SMARTLINK</t>
+          <t>MGEL</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Smartlink Holdings Limited</t>
+          <t>Mangalam Global Enterprise Limited</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr"/>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>EMA20 PULLBACK</t>
+          <t>NEAR BREAKOUT</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>BUY ZONE</t>
+          <t>WAIT - trigger not hit (buy above 17.52)</t>
         </is>
       </c>
       <c r="G8" s="5" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
@@ -4449,77 +2671,77 @@
         </is>
       </c>
       <c r="I8" s="9" t="n">
-        <v>225.1000061035156</v>
+        <v>17.04999923706055</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>225.1000061035156</v>
+        <v>17.04999923706055</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>221.6149047954655</v>
+        <v>17.5175</v>
       </c>
       <c r="L8" s="9" t="n">
-        <v>226.2255061340332</v>
+        <v>17.7625</v>
       </c>
       <c r="M8" s="9" t="n">
-        <v>210.4685057067871</v>
+        <v>16.4934</v>
       </c>
       <c r="N8" s="8" t="n">
-        <v>6.499999999999999</v>
+        <v>6.499999999999996</v>
       </c>
       <c r="O8" s="9" t="n">
-        <v>240.8570065307617</v>
+        <v>18.8748</v>
       </c>
       <c r="P8" s="9" t="n">
-        <v>247.6100067138672</v>
+        <v>19.404</v>
       </c>
       <c r="Q8" s="8" t="n">
-        <v>1.076923076923078</v>
+        <v>1.076923076923077</v>
       </c>
       <c r="R8" s="8" t="n">
-        <v>1.538461538461541</v>
+        <v>1.538461538461542</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>68</v>
+        <v>872</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>15306.80041503906</v>
+        <v>15382.08</v>
       </c>
       <c r="U8" s="8" t="n">
-        <v>68.18181818181817</v>
+        <v>47.72727272727273</v>
       </c>
       <c r="V8" s="8" t="n">
-        <v>68.18181818181817</v>
+        <v>27.27272727272727</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="X8" s="8" t="n">
-        <v>6.808585302932585</v>
+        <v>1.122763536274079</v>
       </c>
       <c r="Y8" s="8" t="n">
-        <v>51.89520874760166</v>
+        <v>69.82740618209755</v>
       </c>
       <c r="Z8" s="8" t="n">
-        <v>18.69283495119275</v>
+        <v>24.8128267353296</v>
       </c>
       <c r="AA8" s="8" t="n">
-        <v>6.817651461381653</v>
+        <v>4.594131726800053</v>
       </c>
       <c r="AB8" s="8" t="n">
-        <v>2.109326023880675</v>
+        <v>9.015337997353502</v>
       </c>
       <c r="AC8" s="8" t="n">
-        <v>1.023246882843565</v>
+        <v>2.402400166334551</v>
       </c>
       <c r="AD8" s="8" t="n">
-        <v>4.401117359151597</v>
+        <v>11.30712933262442</v>
       </c>
       <c r="AE8" s="8" t="n">
-        <v>-15.05660147037147</v>
+        <v>-2.571432931082585</v>
       </c>
       <c r="AF8" s="6" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="AG8" s="6" t="inlineStr"/>
@@ -4530,17 +2752,17 @@
       </c>
       <c r="AI8" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | Volume 6.8x avg | OBV rising | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 68% of similar setups</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | OBV rising | Near 52W high | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 48% of similar setups</t>
         </is>
       </c>
       <c r="AJ8" s="7" t="inlineStr">
         <is>
-          <t>RELAXED smallcap</t>
+          <t>RELAXED smallcap | Negative headline - check news</t>
         </is>
       </c>
       <c r="AK8" s="7" t="inlineStr">
         <is>
-          <t>[19 Oct 2026] Smartlink Holdings Share Price and Technical Outlook - Kalkine India | [21 Oct 2026] Other investing cash flow items (total) of Smartlink Holdings Limited – NSE:SMARTLINK - TradingView | [19 Oct 2026] Kross, DCM Shriram Industries and 6 Other Stocks Hit 20% Upper Circuit Today; Do You Hold Any? - Trade Brains</t>
+          <t>[18 Oct 2026] Mangalam Global Enterprise (NSEI:MGEL) - Stock Analysis - Simply Wall Street | [19 Oct 2026] Mangalam Global Enterprise (MGEL.NS) Holds Near ₹17.02 as ₹17.87 Resistance Comes Into Focus - KAMA Signal - https://www.siam.in/ | [19 Oct 2026] Mangalam Global Q2FY27 net profit drops 53% YoY to ₹831.72 lakh - scanx.trade | [21 Oct 2026] Mangalam Global Enterprise (NSE:MGEL): What Did Its Q2 FY27 Results Newspaper Filing Disclose? - Kalkine India</t>
         </is>
       </c>
       <c r="AL8" s="10" t="inlineStr">
@@ -4555,18 +2777,22 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>IBULLSLTD</t>
+          <t>MASTEK</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Indiabulls Limited</t>
-        </is>
-      </c>
-      <c r="D9" s="6" t="inlineStr"/>
+          <t>Mastek Limited</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>TREND CONTINUATION</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -4575,7 +2801,7 @@
         </is>
       </c>
       <c r="G9" s="5" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
@@ -4583,77 +2809,73 @@
         </is>
       </c>
       <c r="I9" s="9" t="n">
-        <v>34.56999969482422</v>
+        <v>1847.199951171875</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>34.56999969482422</v>
+        <v>1847.199951171875</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>34.22429969787598</v>
+        <v>1828.727951660156</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>34.91569969177246</v>
+        <v>1865.671950683594</v>
       </c>
       <c r="M9" s="9" t="n">
-        <v>32.32294971466064</v>
+        <v>1734.970432977555</v>
       </c>
       <c r="N9" s="8" t="n">
-        <v>6.499999999999999</v>
+        <v>6.075656191043172</v>
       </c>
       <c r="O9" s="9" t="n">
-        <v>36.98989967346191</v>
+        <v>1976.503947753906</v>
       </c>
       <c r="P9" s="9" t="n">
-        <v>38.02699966430664</v>
+        <v>2031.919946289063</v>
       </c>
       <c r="Q9" s="8" t="n">
-        <v>1.076923076923077</v>
+        <v>1.152138926215002</v>
       </c>
       <c r="R9" s="8" t="n">
-        <v>1.53846153846154</v>
+        <v>1.645912751735716</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>445</v>
+        <v>8</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>15383.64986419678</v>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v>64.81481481481481</v>
-      </c>
-      <c r="V9" s="8" t="n">
-        <v>59.25925925925925</v>
-      </c>
+        <v>14777.599609375</v>
+      </c>
+      <c r="U9" s="6" t="inlineStr"/>
+      <c r="V9" s="6" t="inlineStr"/>
       <c r="W9" s="5" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="X9" s="8" t="n">
-        <v>1.892055834504154</v>
+        <v>2.247428917120387</v>
       </c>
       <c r="Y9" s="8" t="n">
-        <v>59.1057335831394</v>
+        <v>68.4922456491872</v>
       </c>
       <c r="Z9" s="8" t="n">
-        <v>33.82534715842232</v>
+        <v>27.11851077235103</v>
       </c>
       <c r="AA9" s="8" t="n">
-        <v>6.471656802364642</v>
+        <v>3.375364550579543</v>
       </c>
       <c r="AB9" s="8" t="n">
-        <v>13.75452579508636</v>
+        <v>16.30777030366317</v>
       </c>
       <c r="AC9" s="8" t="n">
-        <v>19.37154968129626</v>
+        <v>6.657266066082657</v>
       </c>
       <c r="AD9" s="8" t="n">
-        <v>16.04631713035728</v>
+        <v>18.59956163893409</v>
       </c>
       <c r="AE9" s="8" t="n">
-        <v>-11.10825343950531</v>
+        <v>-21.05312803023571</v>
       </c>
       <c r="AF9" s="6" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Neutral</t>
         </is>
       </c>
       <c r="AG9" s="6" t="inlineStr"/>
@@ -4664,17 +2886,17 @@
       </c>
       <c r="AI9" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | Volume 1.9x avg | OBV rising | Beating NIFTY 1M | Stock hit +7% in 15d 65% of similar setups</t>
+          <t>MACD bullish | ADX&gt;=25 strong trend | Volume 2.2x avg | OBV rising | Closed above prior 20D high | BB squeeze before move | Beating NIFTY 1M</t>
         </is>
       </c>
       <c r="AJ9" s="7" t="inlineStr">
         <is>
-          <t>High volatility | Negative headline - check news</t>
+          <t>Extended &gt;7% above EMA20</t>
         </is>
       </c>
       <c r="AK9" s="7" t="inlineStr">
         <is>
-          <t>[18 Oct 2026] Indiabulls shareholders approve ₹1000.07 crore warrant issue - scanx.trade | [19 Oct 2026] Indiabulls Limited Sees High Volume Amid Mixed Price Action and Downgrade to Buy - MarketsMojo | [15 Oct 2026] RBI grants Core Investment Company registration to Indiabulls - BusinessLine | [19 Oct 2026] Indiabulls Limited is Rated Buy by MarketsMOJO - MarketsMojo</t>
+          <t>[21 Oct 2026] Mastek Q2FY27 Earnings Call Set for October 26, 2026 - Kalkine India | [17 Oct 2026] SRIT India Ltd Share Price Today NSE/BSE Charts - Alice Blue | [20 Oct 2026] Mastek Selected by Staffordshire County Council to Drive AI Enabled - Oracle Cloud Transformation - openPR.com</t>
         </is>
       </c>
       <c r="AL9" s="10" t="inlineStr">
@@ -4689,31 +2911,27 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>JUSTDIAL</t>
+          <t>AAREYDRUGS</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Just Dial Limited</t>
-        </is>
-      </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>Consumer Services</t>
-        </is>
-      </c>
+          <t>Aarey Drugs &amp; Pharmaceuticals Limited</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr"/>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>NEAR BREAKOUT</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>BUY ZONE</t>
+          <t>WAIT - trigger not hit (buy above 114.91)</t>
         </is>
       </c>
       <c r="G10" s="5" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
@@ -4721,75 +2939,75 @@
         </is>
       </c>
       <c r="I10" s="9" t="n">
-        <v>767.25</v>
+        <v>111.9300003051758</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>767.25</v>
+        <v>111.9300003051758</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>759.5775</v>
+        <v>114.9148030548096</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>774.9225</v>
+        <v>116.5220030975342</v>
       </c>
       <c r="M10" s="9" t="n">
-        <v>717.3787500000001</v>
+        <v>108.1967068762207</v>
       </c>
       <c r="N10" s="8" t="n">
-        <v>6.499999999999989</v>
+        <v>6.499999999999996</v>
       </c>
       <c r="O10" s="9" t="n">
-        <v>820.9575000000001</v>
+        <v>123.8186912915039</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>843.975</v>
+        <v>127.290243383789</v>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>1.076923076923081</v>
+        <v>1.076923076923079</v>
       </c>
       <c r="R10" s="8" t="n">
         <v>1.538461538461541</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>20</v>
+        <v>132</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>15345</v>
-      </c>
-      <c r="U10" s="6" t="inlineStr"/>
-      <c r="V10" s="6" t="inlineStr"/>
+        <v>15274.82920605468</v>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v>68.25396825396825</v>
+      </c>
+      <c r="V10" s="8" t="n">
+        <v>46.03174603174603</v>
+      </c>
       <c r="W10" s="5" t="n">
-        <v>2</v>
+        <v>63</v>
       </c>
       <c r="X10" s="8" t="n">
-        <v>7.22832342986085</v>
+        <v>0.9920496037316263</v>
       </c>
       <c r="Y10" s="8" t="n">
-        <v>74.34297471836601</v>
+        <v>66.91233739260727</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>19.66555906133593</v>
+        <v>20.98602943571883</v>
       </c>
       <c r="AA10" s="8" t="n">
-        <v>4.257877454430662</v>
+        <v>4.419068066182359</v>
       </c>
       <c r="AB10" s="8" t="n">
-        <v>14.68609865470851</v>
+        <v>9.595616680024776</v>
       </c>
       <c r="AC10" s="8" t="n">
-        <v>3.20822905605036</v>
+        <v>44.36992398749382</v>
       </c>
       <c r="AD10" s="8" t="n">
-        <v>16.97788998997943</v>
+        <v>11.8874080152957</v>
       </c>
       <c r="AE10" s="8" t="n">
-        <v>-8.47548477007919</v>
-      </c>
-      <c r="AF10" s="6" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
+        <v>-2.500002326034856</v>
+      </c>
+      <c r="AF10" s="6" t="inlineStr"/>
       <c r="AG10" s="6" t="inlineStr"/>
       <c r="AH10" s="6" t="inlineStr">
         <is>
@@ -4798,19 +3016,15 @@
       </c>
       <c r="AI10" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | Volume 7.2x avg | OBV rising | Beating NIFTY 1M</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | OBV rising | Near 52W high | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 68% of similar setups</t>
         </is>
       </c>
       <c r="AJ10" s="7" t="inlineStr">
         <is>
-          <t>RELAXED smallcap | Negative headline - check news</t>
-        </is>
-      </c>
-      <c r="AK10" s="7" t="inlineStr">
-        <is>
-          <t>[19 Oct 2026] Just Dial Limited Reports Earnings Results for the Second Quarter and Six Months Ended September 30, 2026 - www.marketscreener.com | [19 Oct 2026] Just Dial Q2FY27 results: Net profit drops 9.7% YoY to ₹107.8 crore - scanx.trade | [19 Oct 2026] Just Dial Q2 FY27 Results: Revenue Up 13.1%, Profit Dips - Kalkine India | [19 Oct 2026] Volume Gainers Today, October 19, 2026, at 12:00 PM IST - HDFC Sky</t>
-        </is>
-      </c>
+          <t>Volume below average</t>
+        </is>
+      </c>
+      <c r="AK10" s="7" t="inlineStr"/>
       <c r="AL10" s="10" t="inlineStr">
         <is>
           <t>Open filings</t>
@@ -4823,31 +3037,27 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>CEIGALL</t>
+          <t>MANOMAY</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>Ceigall India Limited</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>Construction</t>
-        </is>
-      </c>
+          <t>Manomay Tex India Limited</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr"/>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>NEAR BREAKOUT</t>
+          <t>EMA20 PULLBACK</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>WAIT - trigger not hit (buy above 396.40)</t>
+          <t>BUY ZONE</t>
         </is>
       </c>
       <c r="G11" s="5" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
@@ -4855,79 +3065,75 @@
         </is>
       </c>
       <c r="I11" s="9" t="n">
-        <v>389.8500061035156</v>
+        <v>242.7700042724609</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>389.8500061035156</v>
+        <v>242.7700042724609</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>396.396</v>
+        <v>238.1906049900909</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>401.9399999999999</v>
+        <v>243.9838542938232</v>
       </c>
       <c r="M11" s="9" t="n">
-        <v>375.1380262209537</v>
+        <v>226.989953994751</v>
       </c>
       <c r="N11" s="8" t="n">
-        <v>6.020015076119894</v>
+        <v>6.5</v>
       </c>
       <c r="O11" s="9" t="n">
-        <v>427.10976</v>
+        <v>259.7639045715332</v>
       </c>
       <c r="P11" s="9" t="n">
-        <v>439.0848</v>
+        <v>267.047004699707</v>
       </c>
       <c r="Q11" s="8" t="n">
-        <v>1.162787785659791</v>
+        <v>1.076923076923077</v>
       </c>
       <c r="R11" s="8" t="n">
-        <v>1.661125408085414</v>
+        <v>1.538461538461539</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>16365.888</v>
+        <v>15294.51026916504</v>
       </c>
       <c r="U11" s="8" t="n">
-        <v>66.66666666666666</v>
+        <v>57.14285714285714</v>
       </c>
       <c r="V11" s="8" t="n">
-        <v>43.33333333333334</v>
+        <v>38.77551020408163</v>
       </c>
       <c r="W11" s="5" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="X11" s="8" t="n">
-        <v>0.9844392004288897</v>
+        <v>1.209249903962571</v>
       </c>
       <c r="Y11" s="8" t="n">
-        <v>60.60011450704495</v>
+        <v>58.16607234088248</v>
       </c>
       <c r="Z11" s="8" t="n">
-        <v>35.32341757505722</v>
+        <v>21.42572437916148</v>
       </c>
       <c r="AA11" s="8" t="n">
-        <v>3.424390207463202</v>
+        <v>3.883556054230739</v>
       </c>
       <c r="AB11" s="8" t="n">
-        <v>4.307693940739976</v>
+        <v>5.699238947276397</v>
       </c>
       <c r="AC11" s="8" t="n">
-        <v>14.12509444087739</v>
+        <v>21.06418279075211</v>
       </c>
       <c r="AD11" s="8" t="n">
-        <v>6.599485276010897</v>
+        <v>7.991030282547317</v>
       </c>
       <c r="AE11" s="8" t="n">
-        <v>-3.779923398667484</v>
-      </c>
-      <c r="AF11" s="6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
+        <v>-6.583808022501369</v>
+      </c>
+      <c r="AF11" s="6" t="inlineStr"/>
       <c r="AG11" s="6" t="inlineStr"/>
       <c r="AH11" s="6" t="inlineStr">
         <is>
@@ -4936,19 +3142,11 @@
       </c>
       <c r="AI11" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | OBV rising | Near 52W high | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 67% of similar setups</t>
-        </is>
-      </c>
-      <c r="AJ11" s="7" t="inlineStr">
-        <is>
-          <t>Volume below average</t>
-        </is>
-      </c>
-      <c r="AK11" s="7" t="inlineStr">
-        <is>
-          <t>[18 Oct 2026] ETFs Investing in Ceigall India Limited Stocks - TradingView | [21 Oct 2026] Ceigall India subsidiary secures financial close for ₹2,160 Cr highway project - scanx.trade | [19 Oct 2026] Ceigall India Subsidiary Receives Provisional Completion Certificate for ₹684 Crore Highway Project in Haryana - EquityBulls | [19 Oct 2026] Ceigall India: ₹684 करोड़ के हाईवे प्रोजेक्ट को मिली बड़ी मंजूरी, अब शुरू होगी कमाई - Whalesbook</t>
-        </is>
-      </c>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | OBV rising | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 57% of similar setups</t>
+        </is>
+      </c>
+      <c r="AJ11" s="7" t="inlineStr"/>
+      <c r="AK11" s="7" t="inlineStr"/>
       <c r="AL11" s="10" t="inlineStr">
         <is>
           <t>Open filings</t>
@@ -4961,27 +3159,31 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>KRISHANA</t>
+          <t>HEXT</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Krishana Phoschem Limited</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="inlineStr"/>
+          <t>Hexaware Technologies Limited</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>NEAR BREAKOUT</t>
+          <t>BREAKOUT</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>WAIT - trigger not hit (buy above 216.14)</t>
+          <t>BUY ZONE</t>
         </is>
       </c>
       <c r="G12" s="5" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
@@ -4989,77 +3191,77 @@
         </is>
       </c>
       <c r="I12" s="9" t="n">
-        <v>209.5</v>
+        <v>604.5999755859375</v>
       </c>
       <c r="J12" s="9" t="n">
-        <v>209.5</v>
+        <v>604.5999755859375</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>216.1359181671142</v>
+        <v>598.5539758300781</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>219.1587981414795</v>
+        <v>610.6459753417969</v>
       </c>
       <c r="M12" s="9" t="n">
-        <v>203.5002798742676</v>
+        <v>567.6477133358892</v>
       </c>
       <c r="N12" s="8" t="n">
-        <v>6.499999999999997</v>
+        <v>6.111853083393969</v>
       </c>
       <c r="O12" s="9" t="n">
-        <v>232.8826732250976</v>
+        <v>646.9219738769532</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>239.4120939697266</v>
+        <v>665.0599731445313</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>1.076923076923078</v>
+        <v>1.145315488524938</v>
       </c>
       <c r="R12" s="8" t="n">
-        <v>1.53846153846154</v>
+        <v>1.636164983607054</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>15235.31507080078</v>
+        <v>16324.19934082031</v>
       </c>
       <c r="U12" s="8" t="n">
-        <v>64.28571428571429</v>
+        <v>0</v>
       </c>
       <c r="V12" s="8" t="n">
-        <v>55.95238095238096</v>
+        <v>0</v>
       </c>
       <c r="W12" s="5" t="n">
-        <v>84</v>
+        <v>12</v>
       </c>
       <c r="X12" s="8" t="n">
-        <v>0.8031980992340177</v>
+        <v>1.452786904736316</v>
       </c>
       <c r="Y12" s="8" t="n">
-        <v>65.00810496147996</v>
+        <v>75.69258148306517</v>
       </c>
       <c r="Z12" s="8" t="n">
-        <v>24.99417691601515</v>
+        <v>34.25890727222002</v>
       </c>
       <c r="AA12" s="8" t="n">
-        <v>3.823622115345472</v>
+        <v>3.395473935218872</v>
       </c>
       <c r="AB12" s="8" t="n">
-        <v>16.46005932003769</v>
+        <v>15.26069767531157</v>
       </c>
       <c r="AC12" s="8" t="n">
-        <v>46.65732660045303</v>
+        <v>7.95464490027582</v>
       </c>
       <c r="AD12" s="8" t="n">
-        <v>18.75185065530861</v>
+        <v>17.55248901058249</v>
       </c>
       <c r="AE12" s="8" t="n">
-        <v>-3.009259259259256</v>
+        <v>-23.73564748088444</v>
       </c>
       <c r="AF12" s="6" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AG12" s="6" t="inlineStr"/>
@@ -5070,17 +3272,17 @@
       </c>
       <c r="AI12" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | OBV rising | Near 52W high | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 64% of similar setups</t>
+          <t>MACD bullish | ADX&gt;=25 strong trend | Volume 1.5x avg | OBV rising | Closed above prior 20D high | BB squeeze before move | Beating NIFTY 1M</t>
         </is>
       </c>
       <c r="AJ12" s="7" t="inlineStr">
         <is>
-          <t>Volume below average</t>
+          <t>RELAXED smallcap | RSI&gt;70 (hot) | Extended &gt;7% above EMA20 | Big 1D spike | Low hist. +7% hit-rate</t>
         </is>
       </c>
       <c r="AK12" s="7" t="inlineStr">
         <is>
-          <t>[17 Oct 2026] Canadian Phosphate Limited (CP8.AX) stock price, news, quote and history - Yahoo Finance UK | [16 Oct 2026] Canadian Phosphate Limited (CP8.AX) Stock Price, News, Quote &amp; History - Yahoo! Finance Canada</t>
+          <t>[20 Oct 2026] Hexaware Technologies (NSE:HEXT): What Is the 2nd Interim Dividend Declared for FY2026? - Kalkine India | [20 Oct 2026] Hexaware Technologies Ltd declares 2nd interim dividend of Rs. 9.50 - EquityBulls | [15 Oct 2026] Hexaware Technologies (NSE:HEXT): Is a Second Interim Dividend for FY2026 on the Way? - Kalkine India | [16 Oct 2026] Tata Technologies (NSEI:TATATECH) Stock Forecast &amp; Analyst Predictions - Simply Wall Street</t>
         </is>
       </c>
       <c r="AL12" s="10" t="inlineStr">
@@ -5095,22 +3297,18 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>PVRINOX</t>
+          <t>TFCILTD</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>PVR INOX Limited</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>Media Entertainment &amp; Publication</t>
-        </is>
-      </c>
+          <t>Tourism Finance Corporation of India Limited</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr"/>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>TREND CONTINUATION</t>
+          <t>EMA20 PULLBACK</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -5119,7 +3317,7 @@
         </is>
       </c>
       <c r="G13" s="5" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
@@ -5127,84 +3325,84 @@
         </is>
       </c>
       <c r="I13" s="9" t="n">
-        <v>1417.900024414062</v>
+        <v>150.1999969482422</v>
       </c>
       <c r="J13" s="9" t="n">
-        <v>1417.900024414062</v>
+        <v>150.1999969482422</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>1403.721024169922</v>
+        <v>148.6034311026721</v>
       </c>
       <c r="L13" s="9" t="n">
-        <v>1432.079024658203</v>
+        <v>150.9509969329834</v>
       </c>
       <c r="M13" s="9" t="n">
-        <v>1328.926186474387</v>
+        <v>140.5536945343018</v>
       </c>
       <c r="N13" s="8" t="n">
-        <v>6.27504312064905</v>
+        <v>6.422305332845288</v>
       </c>
       <c r="O13" s="9" t="n">
-        <v>1517.153026123047</v>
+        <v>160.7139967346191</v>
       </c>
       <c r="P13" s="9" t="n">
-        <v>1559.690026855469</v>
+        <v>165.2199966430664</v>
       </c>
       <c r="Q13" s="8" t="n">
-        <v>1.115530182886769</v>
+        <v>1.089951292754681</v>
       </c>
       <c r="R13" s="8" t="n">
-        <v>1.593614546981101</v>
+        <v>1.557073275363831</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>11</v>
+        <v>103</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>15596.90026855469</v>
+        <v>15470.59968566895</v>
       </c>
       <c r="U13" s="8" t="n">
-        <v>58.33333333333334</v>
+        <v>62.62626262626263</v>
       </c>
       <c r="V13" s="8" t="n">
-        <v>33.33333333333333</v>
+        <v>51.51515151515152</v>
       </c>
       <c r="W13" s="5" t="n">
-        <v>12</v>
+        <v>99</v>
       </c>
       <c r="X13" s="8" t="n">
-        <v>1.120039499192308</v>
+        <v>1.014430895810536</v>
       </c>
       <c r="Y13" s="8" t="n">
-        <v>65.6005916128039</v>
+        <v>55.55823012731431</v>
       </c>
       <c r="Z13" s="8" t="n">
-        <v>36.89022604213147</v>
+        <v>38.81636756382034</v>
       </c>
       <c r="AA13" s="8" t="n">
-        <v>3.48613506702725</v>
+        <v>4.098715893470102</v>
       </c>
       <c r="AB13" s="8" t="n">
-        <v>7.035561008343016</v>
+        <v>7.577712506131062</v>
       </c>
       <c r="AC13" s="8" t="n">
-        <v>41.63420827017548</v>
+        <v>81.45131454641812</v>
       </c>
       <c r="AD13" s="8" t="n">
-        <v>9.327352343613937</v>
+        <v>9.869503841401983</v>
       </c>
       <c r="AE13" s="8" t="n">
-        <v>-0.9846351666157438</v>
+        <v>-7.255325854532247</v>
       </c>
       <c r="AF13" s="6" t="inlineStr"/>
       <c r="AG13" s="6" t="inlineStr"/>
       <c r="AH13" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Supportive</t>
         </is>
       </c>
       <c r="AI13" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | OBV rising | Near 52W high | Beating NIFTY 1M | Stock hit +7% in 15d 58% of similar setups</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | OBV rising | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 63% of similar setups</t>
         </is>
       </c>
       <c r="AJ13" s="7" t="inlineStr"/>
@@ -5221,27 +3419,31 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>TFCILTD</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Tourism Finance Corporation of India Limited</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr"/>
+          <t>Coforge Limited</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Information Technology</t>
+        </is>
+      </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>EMA20 PULLBACK</t>
+          <t>NEAR BREAKOUT</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>BUY ZONE</t>
+          <t>WAIT - trigger not hit (buy above 1971.97)</t>
         </is>
       </c>
       <c r="G14" s="5" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
@@ -5249,75 +3451,79 @@
         </is>
       </c>
       <c r="I14" s="9" t="n">
-        <v>150.1999969482422</v>
+        <v>1951</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>150.1999969482422</v>
+        <v>1951</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>148.6034311026721</v>
+        <v>1971.97</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>150.9509969329834</v>
+        <v>1999.55</v>
       </c>
       <c r="M14" s="9" t="n">
-        <v>140.5536945343018</v>
+        <v>1881.476165209958</v>
       </c>
       <c r="N14" s="8" t="n">
-        <v>6.422305332845288</v>
+        <v>5.251583010537089</v>
       </c>
       <c r="O14" s="9" t="n">
-        <v>160.7139967346191</v>
+        <v>2124.7632</v>
       </c>
       <c r="P14" s="9" t="n">
-        <v>165.2199966430664</v>
+        <v>2184.336</v>
       </c>
       <c r="Q14" s="8" t="n">
-        <v>1.089951292754681</v>
+        <v>1.332931420098433</v>
       </c>
       <c r="R14" s="8" t="n">
-        <v>1.557073275363831</v>
+        <v>1.90418774299776</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>103</v>
+        <v>9</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>15470.59968566895</v>
+        <v>17871.84</v>
       </c>
       <c r="U14" s="8" t="n">
-        <v>62.62626262626263</v>
+        <v>35.71428571428572</v>
       </c>
       <c r="V14" s="8" t="n">
-        <v>51.51515151515152</v>
+        <v>9.523809523809524</v>
       </c>
       <c r="W14" s="5" t="n">
-        <v>99</v>
+        <v>42</v>
       </c>
       <c r="X14" s="8" t="n">
-        <v>1.014430895810536</v>
+        <v>1.002842997044937</v>
       </c>
       <c r="Y14" s="8" t="n">
-        <v>55.55823012731431</v>
+        <v>62.51547293662475</v>
       </c>
       <c r="Z14" s="8" t="n">
-        <v>38.81636756382034</v>
+        <v>19.30972655529489</v>
       </c>
       <c r="AA14" s="8" t="n">
-        <v>4.098715893470102</v>
+        <v>2.969526590068945</v>
       </c>
       <c r="AB14" s="8" t="n">
-        <v>7.577712506131062</v>
+        <v>5.975013579576327</v>
       </c>
       <c r="AC14" s="8" t="n">
-        <v>81.45131454641812</v>
+        <v>30.89324987006981</v>
       </c>
       <c r="AD14" s="8" t="n">
-        <v>9.869503841401983</v>
+        <v>8.266804914847247</v>
       </c>
       <c r="AE14" s="8" t="n">
-        <v>-7.255325854532247</v>
-      </c>
-      <c r="AF14" s="6" t="inlineStr"/>
+        <v>-3.473181915088297</v>
+      </c>
+      <c r="AF14" s="6" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
       <c r="AG14" s="6" t="inlineStr"/>
       <c r="AH14" s="6" t="inlineStr">
         <is>
@@ -5326,11 +3532,19 @@
       </c>
       <c r="AI14" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | OBV rising | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 63% of similar setups</t>
-        </is>
-      </c>
-      <c r="AJ14" s="7" t="inlineStr"/>
-      <c r="AK14" s="7" t="inlineStr"/>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | OBV rising | Near 52W high | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 36% of similar setups</t>
+        </is>
+      </c>
+      <c r="AJ14" s="7" t="inlineStr">
+        <is>
+          <t>Weak trend (ADX&lt;20)</t>
+        </is>
+      </c>
+      <c r="AK14" s="7" t="inlineStr">
+        <is>
+          <t>[15 Oct 2026] Coforge (NSEI:COFORGE) Stock Price - Simply Wall Street | [16 Oct 2026] Tata Consultancy Services Limited (TCS.BO) stock price, news, quote and history - Yahoo Finance UK | [19 Oct 2026] Coforge schedules October 23 results call for Coforge stock - ad-hoc-news.de | [20 Oct 2026] HCL Technologies Limited (HCLTECH.NS) stock price, news, quote and history - Yahoo Finance Singapore</t>
+        </is>
+      </c>
       <c r="AL14" s="10" t="inlineStr">
         <is>
           <t>Open filings</t>
@@ -5343,18 +3557,18 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>OAL</t>
+          <t>SINGERIND</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Oriental Aromatics Limited</t>
+          <t>Singer India Limited</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr"/>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>TREND CONTINUATION</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -5363,7 +3577,7 @@
         </is>
       </c>
       <c r="G15" s="5" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
@@ -5371,74 +3585,68 @@
         </is>
       </c>
       <c r="I15" s="9" t="n">
-        <v>604.5</v>
+        <v>88.41000366210938</v>
       </c>
       <c r="J15" s="9" t="n">
-        <v>604.5</v>
+        <v>88.41000366210938</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>598.455</v>
+        <v>87.52590362548828</v>
       </c>
       <c r="L15" s="9" t="n">
-        <v>610.545</v>
+        <v>89.29410369873047</v>
       </c>
       <c r="M15" s="9" t="n">
-        <v>565.2075</v>
+        <v>82.66335342407227</v>
       </c>
       <c r="N15" s="8" t="n">
-        <v>6.500000000000003</v>
+        <v>6.499999999999996</v>
       </c>
       <c r="O15" s="9" t="n">
-        <v>646.8150000000001</v>
+        <v>94.59870391845703</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>664.95</v>
+        <v>97.25100402832032</v>
       </c>
       <c r="Q15" s="8" t="n">
         <v>1.076923076923078</v>
       </c>
       <c r="R15" s="8" t="n">
-        <v>1.538461538461539</v>
+        <v>1.538461538461541</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>25</v>
+        <v>174</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>15112.5</v>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v>73.33333333333333</v>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v>53.33333333333334</v>
-      </c>
+        <v>15383.34063720703</v>
+      </c>
+      <c r="U15" s="6" t="inlineStr"/>
+      <c r="V15" s="6" t="inlineStr"/>
       <c r="W15" s="5" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="X15" s="8" t="n">
-        <v>0.6680246302457933</v>
+        <v>1.660547293380202</v>
       </c>
       <c r="Y15" s="8" t="n">
-        <v>67.66230132499675</v>
+        <v>66.90974802020604</v>
       </c>
       <c r="Z15" s="8" t="n">
-        <v>31.56900392148759</v>
+        <v>19.52771574707711</v>
       </c>
       <c r="AA15" s="8" t="n">
-        <v>5.815662234776609</v>
+        <v>5.283275396041455</v>
       </c>
       <c r="AB15" s="8" t="n">
-        <v>17.57268721107277</v>
+        <v>15.90194687588891</v>
       </c>
       <c r="AC15" s="8" t="n">
-        <v>73.9104507960857</v>
+        <v>36.97125076460732</v>
       </c>
       <c r="AD15" s="8" t="n">
-        <v>19.86447854634369</v>
-      </c>
-      <c r="AE15" s="8" t="n">
-        <v>-5.39906103286385</v>
-      </c>
+        <v>18.19373821115983</v>
+      </c>
+      <c r="AE15" s="6" t="inlineStr"/>
       <c r="AF15" s="6" t="inlineStr">
         <is>
           <t>Neutral</t>
@@ -5452,17 +3660,17 @@
       </c>
       <c r="AI15" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | OBV rising | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 73% of similar setups</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | Volume 1.7x avg | OBV rising | BB squeeze before move | Beating NIFTY 1M</t>
         </is>
       </c>
       <c r="AJ15" s="7" t="inlineStr">
         <is>
-          <t>RELAXED smallcap</t>
+          <t>RELAXED smallcap | Extended &gt;7% above EMA20 | Weak trend (ADX&lt;20) | High volatility</t>
         </is>
       </c>
       <c r="AK15" s="7" t="inlineStr">
         <is>
-          <t>[15 Oct 2026] Oriental Aromatics Share Price and Technical Outlook - Kalkine India | [16 Oct 2026] Oriental Aromatics (OAL.NS) Q2 2026 Earnings: Revenue Climbs 10.92% YoY as Stock Surges 8.43% - Adjusted Earnings Analysis - https://www.siam.in/ | [16 Oct 2026] Oriental Aromatics OAL Volume Surge: NSE Clarification - Kalkine India</t>
+          <t>[18 Oct 2026] Singer India AGM resolutions pass with 99.99% shareholder support - scanx.trade | [18 Oct 2026] Singer India net profit turns positive in Q1FY27; revenue up 57% - scanx.trade | [16 Oct 2026] Volume Gainers Today, October 16, 2026, at 3:30 PM IST - HDFC Sky</t>
         </is>
       </c>
       <c r="AL15" s="10" t="inlineStr">
@@ -5477,22 +3685,18 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>BHARTIHEXA</t>
+          <t>TATVA</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Bharti Hexacom Limited</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>Telecommunication</t>
-        </is>
-      </c>
+          <t>Tatva Chintan Pharma Chem Limited</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr"/>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>TREND CONTINUATION</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -5501,7 +3705,7 @@
         </is>
       </c>
       <c r="G16" s="5" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
@@ -5509,77 +3713,77 @@
         </is>
       </c>
       <c r="I16" s="9" t="n">
-        <v>1629.300048828125</v>
+        <v>1890.099975585938</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1629.300048828125</v>
+        <v>1890.099975585938</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>1613.007048339844</v>
+        <v>1871.198975830078</v>
       </c>
       <c r="L16" s="9" t="n">
-        <v>1645.593049316406</v>
+        <v>1909.000975341797</v>
       </c>
       <c r="M16" s="9" t="n">
-        <v>1534.995065630638</v>
+        <v>1773.189475708008</v>
       </c>
       <c r="N16" s="8" t="n">
-        <v>5.788067290939834</v>
+        <v>6.185413543624166</v>
       </c>
       <c r="O16" s="9" t="n">
-        <v>1743.351052246094</v>
+        <v>2022.406973876953</v>
       </c>
       <c r="P16" s="9" t="n">
-        <v>1792.230053710938</v>
+        <v>2079.109973144532</v>
       </c>
       <c r="Q16" s="8" t="n">
-        <v>1.209384695813269</v>
+        <v>1.13169474451963</v>
       </c>
       <c r="R16" s="8" t="n">
-        <v>1.727692422590386</v>
+        <v>1.616706777885186</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>16293.00048828125</v>
+        <v>15120.7998046875</v>
       </c>
       <c r="U16" s="8" t="n">
-        <v>35.71428571428572</v>
+        <v>77.08333333333334</v>
       </c>
       <c r="V16" s="8" t="n">
-        <v>28.57142857142857</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="W16" s="5" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="X16" s="8" t="n">
-        <v>1.267479921686761</v>
+        <v>8.084786396208008</v>
       </c>
       <c r="Y16" s="8" t="n">
-        <v>64.12386080902328</v>
+        <v>56.30276892733634</v>
       </c>
       <c r="Z16" s="8" t="n">
-        <v>22.89856761005461</v>
+        <v>26.90121478247604</v>
       </c>
       <c r="AA16" s="8" t="n">
-        <v>3.215592939411016</v>
+        <v>5.919967289065546</v>
       </c>
       <c r="AB16" s="8" t="n">
-        <v>5.791836546731388</v>
+        <v>6.773247526907267</v>
       </c>
       <c r="AC16" s="8" t="n">
-        <v>-0.2346057846205785</v>
+        <v>12.30748274392155</v>
       </c>
       <c r="AD16" s="8" t="n">
-        <v>8.083627882002309</v>
+        <v>9.065038862178188</v>
       </c>
       <c r="AE16" s="8" t="n">
-        <v>-15.7687488028333</v>
+        <v>-10.57438076001934</v>
       </c>
       <c r="AF16" s="6" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AG16" s="6" t="inlineStr"/>
@@ -5590,13 +3794,17 @@
       </c>
       <c r="AI16" s="7" t="inlineStr">
         <is>
-          <t>MACD bullish | OBV rising | Beating NIFTY 1M | Stock hit +7% in 15d 36% of similar setups</t>
-        </is>
-      </c>
-      <c r="AJ16" s="7" t="inlineStr"/>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | Volume 8.1x avg | Beating NIFTY 1M | Stock hit +7% in 15d 77% of similar setups</t>
+        </is>
+      </c>
+      <c r="AJ16" s="7" t="inlineStr">
+        <is>
+          <t>High volatility</t>
+        </is>
+      </c>
       <c r="AK16" s="7" t="inlineStr">
         <is>
-          <t>[15 Oct 2026] Bharti (BHARTIHEXA.NS) Jumps +1.39% — Is Institutional Money Flowing In? 2026-10-14 - Negative Gamma - www.siam.in</t>
+          <t>[20 Oct 2026] Tatva Chintan Pharma Chem (TATVA.NS) Slips 2.09% to ₹1903.4, Pulling Back Toward Key Support - Trading Ideas - www.siam.in | [19 Oct 2026] Tatva Chintan Q2FY27 results: Revenue up 76% YoY to ₹2,173 crore - scanx.trade | [19 Oct 2026] Tatva Chintan Pharma Chem (NSE:TATVA): What Did Q2 FY27 Results Reveal? - Kalkine India | [19 Oct 2026] Tatva Chintan Q2 Profit Jumps 116% to Rs 21.45 Crore - Whalesbook</t>
         </is>
       </c>
       <c r="AL16" s="10" t="inlineStr">
@@ -5611,18 +3819,18 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>JKIPL</t>
+          <t>KROSS</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Jinkushal Industries Limited</t>
+          <t>Kross Limited</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr"/>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>TREND CONTINUATION</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -5631,7 +3839,7 @@
         </is>
       </c>
       <c r="G17" s="5" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
@@ -5639,75 +3847,79 @@
         </is>
       </c>
       <c r="I17" s="9" t="n">
-        <v>117.5100021362305</v>
+        <v>278.2999877929688</v>
       </c>
       <c r="J17" s="9" t="n">
-        <v>117.5100021362305</v>
+        <v>278.2999877929688</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>116.3349021148682</v>
+        <v>275.5169879150391</v>
       </c>
       <c r="L17" s="9" t="n">
-        <v>118.6851021575928</v>
+        <v>281.0829876708984</v>
       </c>
       <c r="M17" s="9" t="n">
-        <v>109.8718519973755</v>
+        <v>260.2104885864258</v>
       </c>
       <c r="N17" s="8" t="n">
         <v>6.499999999999989</v>
       </c>
       <c r="O17" s="9" t="n">
-        <v>125.7357022857666</v>
+        <v>297.7809869384766</v>
       </c>
       <c r="P17" s="9" t="n">
-        <v>129.2610023498535</v>
+        <v>306.1299865722656</v>
       </c>
       <c r="Q17" s="8" t="n">
-        <v>1.076923076923079</v>
+        <v>1.07692307692308</v>
       </c>
       <c r="R17" s="8" t="n">
-        <v>1.538461538461543</v>
+        <v>1.538461538461542</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>15276.30027770996</v>
+        <v>15306.49932861328</v>
       </c>
       <c r="U17" s="8" t="n">
-        <v>45.45454545454545</v>
+        <v>51.51515151515152</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>18.18181818181818</v>
+        <v>39.39393939393939</v>
       </c>
       <c r="W17" s="5" t="n">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="X17" s="8" t="n">
-        <v>0.7222030161031204</v>
+        <v>1.241093910380829</v>
       </c>
       <c r="Y17" s="8" t="n">
-        <v>60.41544032177482</v>
+        <v>60.3548257207129</v>
       </c>
       <c r="Z17" s="8" t="n">
-        <v>32.47961144595103</v>
+        <v>34.96697287402402</v>
       </c>
       <c r="AA17" s="8" t="n">
-        <v>6.907943964796669</v>
+        <v>6.413843370810207</v>
       </c>
       <c r="AB17" s="8" t="n">
-        <v>19.17850299670396</v>
+        <v>16.35101172806885</v>
       </c>
       <c r="AC17" s="8" t="n">
-        <v>25.82717946698643</v>
+        <v>31.75211542963898</v>
       </c>
       <c r="AD17" s="8" t="n">
-        <v>21.47029433197488</v>
+        <v>18.64280306333978</v>
       </c>
       <c r="AE17" s="8" t="n">
-        <v>-13.57017039316968</v>
-      </c>
-      <c r="AF17" s="6" t="inlineStr"/>
+        <v>-14.73652175335831</v>
+      </c>
+      <c r="AF17" s="6" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
       <c r="AG17" s="6" t="inlineStr"/>
       <c r="AH17" s="6" t="inlineStr">
         <is>
@@ -5716,15 +3928,19 @@
       </c>
       <c r="AI17" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | OBV rising | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 45% of similar setups</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | OBV rising | Beating NIFTY 1M | Stock hit +7% in 15d 52% of similar setups</t>
         </is>
       </c>
       <c r="AJ17" s="7" t="inlineStr">
         <is>
-          <t>RELAXED smallcap</t>
-        </is>
-      </c>
-      <c r="AK17" s="7" t="inlineStr"/>
+          <t>Extended &gt;7% above EMA20 | High volatility</t>
+        </is>
+      </c>
+      <c r="AK17" s="7" t="inlineStr">
+        <is>
+          <t>[16 Oct 2026] KROSS LIMITED Share Price - Upstox | [19 Oct 2026] Kross Limited September Quarter Results and Stock Update - Kalkine India | [19 Oct 2026] Kross share price jumps 20% after Q2 results: What lies ahead? Technical analyst weighs in - Livemint | [20 Oct 2026] Kross Ltd uploads audio recording of Q2FY27 earnings conference call - scanx.trade</t>
+        </is>
+      </c>
       <c r="AL17" s="10" t="inlineStr">
         <is>
           <t>Open filings</t>
@@ -5737,18 +3953,18 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>DHANBANK</t>
+          <t>PREMEXPLN</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Dhanlaxmi Bank Limited</t>
+          <t>Premier Explosives Limited</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr"/>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>TREND CONTINUATION</t>
+          <t>NEAR BREAKOUT</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -5757,7 +3973,7 @@
         </is>
       </c>
       <c r="G18" s="5" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
@@ -5765,75 +3981,79 @@
         </is>
       </c>
       <c r="I18" s="9" t="n">
-        <v>35.52999877929688</v>
+        <v>692.5</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>35.52999877929688</v>
+        <v>692.5</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>35.17469879150391</v>
+        <v>695.2445377807617</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>35.88529876708984</v>
+        <v>704.9682376098632</v>
       </c>
       <c r="M18" s="9" t="n">
-        <v>33.22054885864258</v>
+        <v>679.103196064453</v>
       </c>
       <c r="N18" s="8" t="n">
-        <v>6.499999999999995</v>
+        <v>3.000000000000007</v>
       </c>
       <c r="O18" s="9" t="n">
-        <v>38.01709869384766</v>
+        <v>749.1138348339842</v>
       </c>
       <c r="P18" s="9" t="n">
-        <v>39.08299865722657</v>
+        <v>770.1170264648437</v>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>1.076923076923078</v>
+        <v>2.333333333333328</v>
       </c>
       <c r="R18" s="8" t="n">
-        <v>1.538461538461542</v>
+        <v>3.333333333333328</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>433</v>
+        <v>28</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>15384.48947143555</v>
+        <v>19602.97885546875</v>
       </c>
       <c r="U18" s="8" t="n">
-        <v>44.44444444444444</v>
+        <v>48.48484848484848</v>
       </c>
       <c r="V18" s="8" t="n">
-        <v>5.555555555555555</v>
+        <v>30.3030303030303</v>
       </c>
       <c r="W18" s="5" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="X18" s="8" t="n">
-        <v>0.7728284813055751</v>
+        <v>4.153208308318388</v>
       </c>
       <c r="Y18" s="8" t="n">
-        <v>63.06759519124925</v>
+        <v>66.70787117571641</v>
       </c>
       <c r="Z18" s="8" t="n">
-        <v>27.935343580819</v>
+        <v>46.76226185030922</v>
       </c>
       <c r="AA18" s="8" t="n">
-        <v>5.630729879863613</v>
+        <v>1.130474203678186</v>
       </c>
       <c r="AB18" s="8" t="n">
-        <v>20.56328336321427</v>
+        <v>3.705784997361627</v>
       </c>
       <c r="AC18" s="8" t="n">
-        <v>3.737222713275545</v>
+        <v>5.369303159076821</v>
       </c>
       <c r="AD18" s="8" t="n">
-        <v>22.85507469848519</v>
+        <v>5.997576332632548</v>
       </c>
       <c r="AE18" s="8" t="n">
-        <v>-5.253336588541668</v>
-      </c>
-      <c r="AF18" s="6" t="inlineStr"/>
+        <v>-16.48422293160215</v>
+      </c>
+      <c r="AF18" s="6" t="inlineStr">
+        <is>
+          <t>Neutral</t>
+        </is>
+      </c>
       <c r="AG18" s="6" t="inlineStr"/>
       <c r="AH18" s="6" t="inlineStr">
         <is>
@@ -5842,7 +4062,7 @@
       </c>
       <c r="AI18" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | OBV rising | Beating NIFTY 1M | Stock hit +7% in 15d 44% of similar setups</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | Volume 4.2x avg | OBV rising | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 48% of similar setups</t>
         </is>
       </c>
       <c r="AJ18" s="7" t="inlineStr">
@@ -5850,7 +4070,11 @@
           <t>RELAXED smallcap</t>
         </is>
       </c>
-      <c r="AK18" s="7" t="inlineStr"/>
+      <c r="AK18" s="7" t="inlineStr">
+        <is>
+          <t>[16 Oct 2026] Premier Explosives (PREMEXPLN.NS) Holds Near ₹691 as Stock Consolidates Below ₹726 Resistance - Wyckoff Accumulation - https://www.siam.in/</t>
+        </is>
+      </c>
       <c r="AL18" s="10" t="inlineStr">
         <is>
           <t>Open filings</t>
@@ -5863,19 +4087,15 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>SMARTLINK</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Petronet LNG Limited</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>Oil Gas &amp; Consumable Fuels</t>
-        </is>
-      </c>
+          <t>Smartlink Holdings Limited</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr"/>
       <c r="E19" s="6" t="inlineStr">
         <is>
           <t>EMA20 PULLBACK</t>
@@ -5887,7 +4107,7 @@
         </is>
       </c>
       <c r="G19" s="5" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H19" s="6" t="inlineStr">
         <is>
@@ -5895,73 +4115,73 @@
         </is>
       </c>
       <c r="I19" s="9" t="n">
-        <v>295</v>
+        <v>225.1000061035156</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>295</v>
+        <v>225.1000061035156</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>291.0425660285314</v>
+        <v>221.6149047954655</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>296.475</v>
+        <v>226.2255061340332</v>
       </c>
       <c r="M19" s="9" t="n">
-        <v>286.15</v>
+        <v>210.4685057067871</v>
       </c>
       <c r="N19" s="8" t="n">
-        <v>3.000000000000008</v>
+        <v>6.499999999999999</v>
       </c>
       <c r="O19" s="9" t="n">
-        <v>315.65</v>
+        <v>240.8570065307617</v>
       </c>
       <c r="P19" s="9" t="n">
-        <v>324.5</v>
+        <v>247.6100067138672</v>
       </c>
       <c r="Q19" s="8" t="n">
-        <v>2.333333333333331</v>
+        <v>1.076923076923078</v>
       </c>
       <c r="R19" s="8" t="n">
-        <v>3.333333333333325</v>
+        <v>1.538461538461541</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>19765</v>
+        <v>15306.80041503906</v>
       </c>
       <c r="U19" s="8" t="n">
-        <v>15</v>
+        <v>68.18181818181817</v>
       </c>
       <c r="V19" s="8" t="n">
-        <v>0</v>
+        <v>68.18181818181817</v>
       </c>
       <c r="W19" s="5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="X19" s="8" t="n">
-        <v>1.674574317541534</v>
+        <v>6.808585302932585</v>
       </c>
       <c r="Y19" s="8" t="n">
-        <v>56.59393292417634</v>
+        <v>51.89520874760166</v>
       </c>
       <c r="Z19" s="8" t="n">
-        <v>19.45919177234353</v>
+        <v>18.69283495119275</v>
       </c>
       <c r="AA19" s="8" t="n">
-        <v>1.982710979639583</v>
+        <v>6.817651461381653</v>
       </c>
       <c r="AB19" s="8" t="n">
-        <v>0.8202302961112462</v>
+        <v>2.109326023880675</v>
       </c>
       <c r="AC19" s="8" t="n">
-        <v>6.632932047120077</v>
+        <v>1.023246882843565</v>
       </c>
       <c r="AD19" s="8" t="n">
-        <v>3.112021631382167</v>
+        <v>4.401117359151597</v>
       </c>
       <c r="AE19" s="8" t="n">
-        <v>-8.577454441370547</v>
+        <v>-15.05660147037147</v>
       </c>
       <c r="AF19" s="6" t="inlineStr">
         <is>
@@ -5976,17 +4196,17 @@
       </c>
       <c r="AI19" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | Volume 1.7x avg | OBV rising | Beating NIFTY 1M</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | Volume 6.8x avg | OBV rising | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 68% of similar setups</t>
         </is>
       </c>
       <c r="AJ19" s="7" t="inlineStr">
         <is>
-          <t>RELAXED smallcap</t>
+          <t>RELAXED smallcap | Weak trend (ADX&lt;20) | High volatility</t>
         </is>
       </c>
       <c r="AK19" s="7" t="inlineStr">
         <is>
-          <t>[15 Oct 2026] Petronet LNG MD Speaks on India’s LNG Demand at Americas Summit - PSU Connect</t>
+          <t>[19 Oct 2026] Smartlink Holdings Share Price and Technical Outlook - Kalkine India | [19 Oct 2026] Kross, DCM Shriram Industries and 6 Other Stocks Hit 20% Upper Circuit Today; Do You Hold Any? - Trade Brains</t>
         </is>
       </c>
       <c r="AL19" s="10" t="inlineStr">
@@ -6001,19 +4221,15 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>ANANDRATHI</t>
+          <t>IBULLSLTD</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Anand Rathi Wealth Limited</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
+          <t>Indiabulls Limited</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr"/>
       <c r="E20" s="6" t="inlineStr">
         <is>
           <t>TREND CONTINUATION</t>
@@ -6021,11 +4237,11 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>AVOID - negative news, read headlines</t>
+          <t>BUY ZONE</t>
         </is>
       </c>
       <c r="G20" s="5" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
@@ -6033,73 +4249,73 @@
         </is>
       </c>
       <c r="I20" s="9" t="n">
-        <v>2200</v>
+        <v>34.56999969482422</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>2200</v>
+        <v>34.56999969482422</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>2178</v>
+        <v>34.22429969787598</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>2222</v>
+        <v>34.91569969177246</v>
       </c>
       <c r="M20" s="9" t="n">
-        <v>2108.750769386265</v>
+        <v>32.32294971466064</v>
       </c>
       <c r="N20" s="8" t="n">
-        <v>4.147692300624302</v>
+        <v>6.499999999999999</v>
       </c>
       <c r="O20" s="9" t="n">
-        <v>2354</v>
+        <v>36.98989967346191</v>
       </c>
       <c r="P20" s="9" t="n">
-        <v>2420</v>
+        <v>38.02699966430664</v>
       </c>
       <c r="Q20" s="8" t="n">
-        <v>1.687685462816606</v>
+        <v>1.076923076923077</v>
       </c>
       <c r="R20" s="8" t="n">
-        <v>2.410979232595152</v>
+        <v>1.53846153846154</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>9</v>
+        <v>445</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>19800</v>
+        <v>15383.64986419678</v>
       </c>
       <c r="U20" s="8" t="n">
-        <v>35.38461538461539</v>
+        <v>64.81481481481481</v>
       </c>
       <c r="V20" s="8" t="n">
-        <v>26.15384615384616</v>
+        <v>59.25925925925925</v>
       </c>
       <c r="W20" s="5" t="n">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="X20" s="8" t="n">
-        <v>1.59729183391757</v>
+        <v>1.892055834504154</v>
       </c>
       <c r="Y20" s="8" t="n">
-        <v>59.56889649475414</v>
+        <v>59.1057335831394</v>
       </c>
       <c r="Z20" s="8" t="n">
-        <v>29.28237029068234</v>
+        <v>33.82534715842232</v>
       </c>
       <c r="AA20" s="8" t="n">
-        <v>2.304273500346835</v>
+        <v>6.471656802364642</v>
       </c>
       <c r="AB20" s="8" t="n">
-        <v>-1.131948779784009</v>
+        <v>13.75452579508636</v>
       </c>
       <c r="AC20" s="8" t="n">
-        <v>5.40189384670593</v>
+        <v>19.37154968129626</v>
       </c>
       <c r="AD20" s="8" t="n">
-        <v>1.159842555486912</v>
+        <v>16.04631713035728</v>
       </c>
       <c r="AE20" s="8" t="n">
-        <v>-2.83176105433246</v>
+        <v>-11.10825343950531</v>
       </c>
       <c r="AF20" s="6" t="inlineStr">
         <is>
@@ -6114,17 +4330,17 @@
       </c>
       <c r="AI20" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | Volume 1.6x avg | OBV rising | Near 52W high | Stock hit +7% in 15d 35% of similar setups</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | Volume 1.9x avg | OBV rising | Beating NIFTY 1M | Stock hit +7% in 15d 65% of similar setups</t>
         </is>
       </c>
       <c r="AJ20" s="7" t="inlineStr">
         <is>
-          <t>RELAXED smallcap | Multiple negative headlines</t>
+          <t>High volatility | Negative headline - check news</t>
         </is>
       </c>
       <c r="AK20" s="7" t="inlineStr">
         <is>
-          <t>[16 Oct 2026] Anand Rathi Wealth promoter shifts pledge of 88.46 lakh shares to Yes Bank - scanx.trade | [16 Oct 2026] Anand Rathi Wealth Promoter Changes Share-Pledge Arrangement - Kalkine India | [15 Oct 2026] Anand Rathi Wealth to host virtual investor meet on October 22, 2026 - scanx.trade | [16 Oct 2026] NFO Insight: Carnelian Small Cap Fund opens for subscription with Rs 5,000 crore size cap. Can it deliver - The Economic Times</t>
+          <t>[18 Oct 2026] Indiabulls shareholders approve ₹1000.07 crore warrant issue - scanx.trade | [19 Oct 2026] Indiabulls Limited Sees High Volume Amid Mixed Price Action and Downgrade to Buy - MarketsMojo | [15 Oct 2026] RBI grants Core Investment Company registration to Indiabulls - BusinessLine | [19 Oct 2026] Indiabulls Limited is Rated Buy by MarketsMOJO - MarketsMojo</t>
         </is>
       </c>
       <c r="AL20" s="10" t="inlineStr">
@@ -6139,18 +4355,22 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>BALAJITELE</t>
+          <t>JUSTDIAL</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Balaji Telefilms Limited</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="inlineStr"/>
+          <t>Just Dial Limited</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Consumer Services</t>
+        </is>
+      </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>EMA20 PULLBACK</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -6159,7 +4379,7 @@
         </is>
       </c>
       <c r="G21" s="5" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
@@ -6167,77 +4387,73 @@
         </is>
       </c>
       <c r="I21" s="9" t="n">
-        <v>93.65000152587891</v>
+        <v>767.25</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>93.65000152587891</v>
+        <v>767.25</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>91.68656006747858</v>
+        <v>759.5775</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>94.11825153350829</v>
+        <v>774.9225</v>
       </c>
       <c r="M21" s="9" t="n">
-        <v>87.56275142669678</v>
+        <v>717.3787500000001</v>
       </c>
       <c r="N21" s="8" t="n">
-        <v>6.499999999999999</v>
+        <v>6.499999999999989</v>
       </c>
       <c r="O21" s="9" t="n">
-        <v>100.2055016326904</v>
+        <v>820.9575000000001</v>
       </c>
       <c r="P21" s="9" t="n">
-        <v>103.0150016784668</v>
+        <v>843.975</v>
       </c>
       <c r="Q21" s="8" t="n">
-        <v>1.076923076923079</v>
+        <v>1.076923076923081</v>
       </c>
       <c r="R21" s="8" t="n">
-        <v>1.538461538461539</v>
+        <v>1.538461538461541</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>164</v>
+        <v>20</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>15358.60025024414</v>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v>61.11111111111111</v>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v>51.38888888888889</v>
-      </c>
+        <v>15345</v>
+      </c>
+      <c r="U21" s="6" t="inlineStr"/>
+      <c r="V21" s="6" t="inlineStr"/>
       <c r="W21" s="5" t="n">
-        <v>72</v>
+        <v>2</v>
       </c>
       <c r="X21" s="8" t="n">
-        <v>6.947042780966337</v>
+        <v>7.22832342986085</v>
       </c>
       <c r="Y21" s="8" t="n">
-        <v>56.17383484391576</v>
+        <v>74.34297471836601</v>
       </c>
       <c r="Z21" s="8" t="n">
-        <v>20.53393652304001</v>
+        <v>19.66555906133593</v>
       </c>
       <c r="AA21" s="8" t="n">
-        <v>3.941129144224689</v>
+        <v>4.257877454430662</v>
       </c>
       <c r="AB21" s="8" t="n">
-        <v>-1.679788424274109</v>
+        <v>14.68609865470851</v>
       </c>
       <c r="AC21" s="8" t="n">
-        <v>8.115906899546111</v>
+        <v>3.20822905605036</v>
       </c>
       <c r="AD21" s="8" t="n">
-        <v>0.6120029109968117</v>
+        <v>16.97788998997943</v>
       </c>
       <c r="AE21" s="8" t="n">
-        <v>-29.05302914706144</v>
+        <v>-8.47548477007919</v>
       </c>
       <c r="AF21" s="6" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="AG21" s="6" t="inlineStr"/>
@@ -6248,17 +4464,17 @@
       </c>
       <c r="AI21" s="7" t="inlineStr">
         <is>
-          <t>MACD bullish | Volume 6.9x avg | OBV rising | BB squeeze before move | Stock hit +7% in 15d 61% of similar setups</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | Volume 7.2x avg | OBV rising | Beating NIFTY 1M</t>
         </is>
       </c>
       <c r="AJ21" s="7" t="inlineStr">
         <is>
-          <t>RELAXED smallcap</t>
+          <t>RELAXED smallcap | RSI&gt;70 (hot) | Extended &gt;7% above EMA20 | Weak trend (ADX&lt;20) | Negative headline - check news</t>
         </is>
       </c>
       <c r="AK21" s="7" t="inlineStr">
         <is>
-          <t>[16 Oct 2026] Balaji Telefilms Share Price - Upstox | [18 Oct 2026] TIPSMUSIC Stock Price and Chart — NSE:TIPSMUSIC - TradingView</t>
+          <t>[19 Oct 2026] Just Dial Limited Reports Earnings Results for the Second Quarter and Six Months Ended September 30, 2026 - www.marketscreener.com | [19 Oct 2026] Just Dial Q2FY27 results: Net profit drops 9.7% YoY to ₹107.8 crore - scanx.trade | [19 Oct 2026] Just Dial Q2 FY27 Results: Revenue Up 13.1%, Profit Dips - Kalkine India | [19 Oct 2026] Volume Gainers Today, October 19, 2026, at 12:00 PM IST - HDFC Sky</t>
         </is>
       </c>
       <c r="AL21" s="10" t="inlineStr">
@@ -6273,27 +4489,31 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>RISHABH</t>
+          <t>CEIGALL</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Rishabh Instruments Limited</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr"/>
+          <t>Ceigall India Limited</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>EMA20 PULLBACK</t>
+          <t>NEAR BREAKOUT</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>BUY ZONE</t>
+          <t>WAIT - trigger not hit (buy above 396.40)</t>
         </is>
       </c>
       <c r="G22" s="5" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
@@ -6301,73 +4521,73 @@
         </is>
       </c>
       <c r="I22" s="9" t="n">
-        <v>701.9500122070312</v>
+        <v>389.8500061035156</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>701.9500122070312</v>
+        <v>389.8500061035156</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>698.2399587691323</v>
+        <v>396.396</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>705.4597622680664</v>
+        <v>401.9399999999999</v>
       </c>
       <c r="M22" s="9" t="n">
-        <v>656.3232614135743</v>
+        <v>375.1380262209537</v>
       </c>
       <c r="N22" s="8" t="n">
-        <v>6.499999999999988</v>
+        <v>6.020015076119894</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>751.0865130615235</v>
+        <v>427.10976</v>
       </c>
       <c r="P22" s="9" t="n">
-        <v>772.1450134277344</v>
+        <v>439.0848</v>
       </c>
       <c r="Q22" s="8" t="n">
-        <v>1.076923076923081</v>
+        <v>1.162787785659791</v>
       </c>
       <c r="R22" s="8" t="n">
-        <v>1.538461538461542</v>
+        <v>1.661125408085414</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>14740.95025634766</v>
+        <v>16365.888</v>
       </c>
       <c r="U22" s="8" t="n">
-        <v>62.5</v>
+        <v>66.66666666666666</v>
       </c>
       <c r="V22" s="8" t="n">
-        <v>45.3125</v>
+        <v>43.33333333333334</v>
       </c>
       <c r="W22" s="5" t="n">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="X22" s="8" t="n">
-        <v>3.582480611672469</v>
+        <v>0.9844392004288897</v>
       </c>
       <c r="Y22" s="8" t="n">
-        <v>50.13690801943186</v>
+        <v>60.60011450704495</v>
       </c>
       <c r="Z22" s="8" t="n">
-        <v>26.01148018016203</v>
+        <v>35.32341757505722</v>
       </c>
       <c r="AA22" s="8" t="n">
-        <v>5.365609974846699</v>
+        <v>3.424390207463202</v>
       </c>
       <c r="AB22" s="8" t="n">
-        <v>-8.205832221565512</v>
+        <v>4.307693940739976</v>
       </c>
       <c r="AC22" s="8" t="n">
-        <v>7.903389784710169</v>
+        <v>14.12509444087739</v>
       </c>
       <c r="AD22" s="8" t="n">
-        <v>-5.914040886294591</v>
+        <v>6.599485276010897</v>
       </c>
       <c r="AE22" s="8" t="n">
-        <v>-17.61150091466769</v>
+        <v>-3.779923398667484</v>
       </c>
       <c r="AF22" s="6" t="inlineStr">
         <is>
@@ -6382,17 +4602,17 @@
       </c>
       <c r="AI22" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | Volume 3.6x avg | OBV rising | BB squeeze before move | Stock hit +7% in 15d 62% of similar setups</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | OBV rising | Near 52W high | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 67% of similar setups</t>
         </is>
       </c>
       <c r="AJ22" s="7" t="inlineStr">
         <is>
-          <t>RELAXED smallcap</t>
+          <t>Volume below average</t>
         </is>
       </c>
       <c r="AK22" s="7" t="inlineStr">
         <is>
-          <t>[18 Oct 2026] Rishabh Instruments Limited Actuals &amp; Estimates (NSE:RISHABH) - TradingView | [15 Oct 2026] Rishabh Instruments (RISHABH.NS) Slips 3.50% to ₹671.6 as Stock Drifts Toward Key Support - RSI Overbought Alerts - https://www.siam.in/ | [15 Oct 2026] Rishabh Instruments files BRSR for FY 2025-26 - scanx.trade</t>
+          <t>[18 Oct 2026] ETFs Investing in Ceigall India Limited Stocks - TradingView | [21 Oct 2026] Ceigall India Limited Subsidiary Achieves Financial Close for Rs 2,160 Crore Highway Project in Bihar - EquityBulls | [21 Oct 2026] Ceigall India subsidiary secures financial close for ₹2,160 Cr highway project - scanx.trade | [16 Oct 2026] Stocks to Watch Today: HCL Tech, Nazara, BOI, TD Power, Juniper Green, Airflow Rail, Globus Power, Vikran Engg, ARSS Infra Ceigall India, IRCON - BusinessLine</t>
         </is>
       </c>
       <c r="AL22" s="10" t="inlineStr">
@@ -6407,27 +4627,27 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>SEJALLTD</t>
+          <t>KRISHANA</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
-          <t>Sejal Glass Limited</t>
+          <t>Krishana Phoschem Limited</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr"/>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>TREND CONTINUATION</t>
+          <t>NEAR BREAKOUT</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>BUY ZONE</t>
+          <t>WAIT - trigger not hit (buy above 216.14)</t>
         </is>
       </c>
       <c r="G23" s="5" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
@@ -6435,73 +4655,73 @@
         </is>
       </c>
       <c r="I23" s="9" t="n">
-        <v>839.2999877929688</v>
+        <v>209.5</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>839.2999877929688</v>
+        <v>209.5</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>830.9069879150391</v>
+        <v>216.1359181671142</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>847.6929876708984</v>
+        <v>219.1587981414795</v>
       </c>
       <c r="M23" s="9" t="n">
-        <v>784.7454885864258</v>
+        <v>203.5002798742676</v>
       </c>
       <c r="N23" s="8" t="n">
-        <v>6.499999999999993</v>
+        <v>6.499999999999997</v>
       </c>
       <c r="O23" s="9" t="n">
-        <v>898.0509869384766</v>
+        <v>232.8826732250976</v>
       </c>
       <c r="P23" s="9" t="n">
-        <v>923.2299865722657</v>
+        <v>239.4120939697266</v>
       </c>
       <c r="Q23" s="8" t="n">
-        <v>1.076923076923079</v>
+        <v>1.076923076923078</v>
       </c>
       <c r="R23" s="8" t="n">
-        <v>1.538461538461542</v>
+        <v>1.53846153846154</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>15107.39978027344</v>
+        <v>15235.31507080078</v>
       </c>
       <c r="U23" s="8" t="n">
-        <v>41.66666666666667</v>
+        <v>64.28571428571429</v>
       </c>
       <c r="V23" s="8" t="n">
-        <v>29.16666666666667</v>
+        <v>55.95238095238096</v>
       </c>
       <c r="W23" s="5" t="n">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="X23" s="8" t="n">
-        <v>0.7091259076412276</v>
+        <v>0.8031980992340177</v>
       </c>
       <c r="Y23" s="8" t="n">
-        <v>61.4453698267056</v>
+        <v>65.00810496147996</v>
       </c>
       <c r="Z23" s="8" t="n">
-        <v>32.03034826313974</v>
+        <v>24.99417691601504</v>
       </c>
       <c r="AA23" s="8" t="n">
-        <v>7.637068546009766</v>
+        <v>3.823622115345472</v>
       </c>
       <c r="AB23" s="8" t="n">
-        <v>17.48319696396243</v>
+        <v>16.46005932003769</v>
       </c>
       <c r="AC23" s="8" t="n">
-        <v>13.48026169525565</v>
+        <v>46.65732660045303</v>
       </c>
       <c r="AD23" s="8" t="n">
-        <v>19.77498829923336</v>
+        <v>18.75185065530861</v>
       </c>
       <c r="AE23" s="8" t="n">
-        <v>-19.0411857505894</v>
+        <v>-3.009259259259256</v>
       </c>
       <c r="AF23" s="6" t="inlineStr">
         <is>
@@ -6516,17 +4736,17 @@
       </c>
       <c r="AI23" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | OBV rising | Beating NIFTY 1M | Stock hit +7% in 15d 42% of similar setups</t>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | OBV rising | Near 52W high | BB squeeze before move | Beating NIFTY 1M | Stock hit +7% in 15d 64% of similar setups</t>
         </is>
       </c>
       <c r="AJ23" s="7" t="inlineStr">
         <is>
-          <t>RELAXED smallcap</t>
+          <t>Volume below average</t>
         </is>
       </c>
       <c r="AK23" s="7" t="inlineStr">
         <is>
-          <t>[15 Oct 2026] Sejal Glass Share Price and Quarterly Earnings Review - Kalkine India | [19 Oct 2026] Sejal Glass Maintains FY27 Revenue Growth Target Of 25-40% With 18% EBITDA Margin - Sahi | [18 Oct 2026] Sejal Glass Q2FY27 results: Revenue up 33%, EBITDA margin hits 18.35% - scanx.trade</t>
+          <t>[17 Oct 2026] Canadian Phosphate Limited (CP8.AX) stock price, news, quote and history - Yahoo Finance UK | [16 Oct 2026] Canadian Phosphate Limited (CP8.AX) Stock Price, News, Quote &amp; History - Yahoo! Finance Canada</t>
         </is>
       </c>
       <c r="AL23" s="10" t="inlineStr">
@@ -6541,18 +4761,22 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>TEXINFRA</t>
+          <t>PVRINOX</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Texmaco Infrastructure &amp; Holdings Limited</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr"/>
+          <t>PVR INOX Limited</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Media Entertainment &amp; Publication</t>
+        </is>
+      </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>EMA20 PULLBACK</t>
+          <t>TREND CONTINUATION</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -6561,7 +4785,7 @@
         </is>
       </c>
       <c r="G24" s="5" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
@@ -6569,79 +4793,75 @@
         </is>
       </c>
       <c r="I24" s="9" t="n">
-        <v>122.2799987792969</v>
+        <v>1417.900024414062</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>122.2799987792969</v>
+        <v>1417.900024414062</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>120.9107641533407</v>
+        <v>1403.721024169922</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>122.8913987731933</v>
+        <v>1432.079024658203</v>
       </c>
       <c r="M24" s="9" t="n">
-        <v>114.3317988586426</v>
+        <v>1328.926186474387</v>
       </c>
       <c r="N24" s="8" t="n">
-        <v>6.499999999999993</v>
+        <v>6.27504312064905</v>
       </c>
       <c r="O24" s="9" t="n">
-        <v>130.8395986938477</v>
+        <v>1517.153026123047</v>
       </c>
       <c r="P24" s="9" t="n">
-        <v>134.5079986572266</v>
+        <v>1559.690026855469</v>
       </c>
       <c r="Q24" s="8" t="n">
-        <v>1.07692307692308</v>
+        <v>1.115530182886769</v>
       </c>
       <c r="R24" s="8" t="n">
-        <v>1.538461538461542</v>
+        <v>1.593614546981101</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>125</v>
+        <v>11</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>15284.99984741211</v>
+        <v>15596.90026855469</v>
       </c>
       <c r="U24" s="8" t="n">
-        <v>40.625</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="V24" s="8" t="n">
-        <v>21.875</v>
+        <v>33.33333333333333</v>
       </c>
       <c r="W24" s="5" t="n">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="X24" s="8" t="n">
-        <v>0.9185624929455689</v>
+        <v>1.120039499192308</v>
       </c>
       <c r="Y24" s="8" t="n">
-        <v>53.70978301135534</v>
+        <v>65.6005916128039</v>
       </c>
       <c r="Z24" s="8" t="n">
-        <v>27.06654697453134</v>
+        <v>36.89022604213147</v>
       </c>
       <c r="AA24" s="8" t="n">
-        <v>4.309743330146079</v>
+        <v>3.48613506702725</v>
       </c>
       <c r="AB24" s="8" t="n">
-        <v>7.697725729518012</v>
+        <v>7.035561008343016</v>
       </c>
       <c r="AC24" s="8" t="n">
-        <v>7.393807168707123</v>
+        <v>41.63420827017548</v>
       </c>
       <c r="AD24" s="8" t="n">
-        <v>9.989517064788933</v>
+        <v>9.327352343613937</v>
       </c>
       <c r="AE24" s="8" t="n">
-        <v>-6.499464810627897</v>
-      </c>
-      <c r="AF24" s="6" t="inlineStr">
-        <is>
-          <t>Neutral</t>
-        </is>
-      </c>
+        <v>-0.9846351666157438</v>
+      </c>
+      <c r="AF24" s="6" t="inlineStr"/>
       <c r="AG24" s="6" t="inlineStr"/>
       <c r="AH24" s="6" t="inlineStr">
         <is>
@@ -6650,19 +4870,11 @@
       </c>
       <c r="AI24" s="7" t="inlineStr">
         <is>
-          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | OBV rising | Beating NIFTY 1M | Stock hit +7% in 15d 41% of similar setups</t>
-        </is>
-      </c>
-      <c r="AJ24" s="7" t="inlineStr">
-        <is>
-          <t>Volume below average</t>
-        </is>
-      </c>
-      <c r="AK24" s="7" t="inlineStr">
-        <is>
-          <t>[14 Oct 2026] Texmaco Infrastructure &amp; Holdings Limited (TEXINFRA.BO) - Yahoo! Finance Canada</t>
-        </is>
-      </c>
+          <t>Price&gt;EMA20&gt;EMA50&gt;EMA200 | MACD bullish | ADX&gt;=25 strong trend | OBV rising | Near 52W high | Beating NIFTY 1M | Stock hit +7% in 15d 58% of similar setups</t>
+        </is>
+      </c>
+      <c r="AJ24" s="7" t="inlineStr"/>
+      <c r="AK24" s="7" t="inlineStr"/>
       <c r="AL24" s="10" t="inlineStr">
         <is>
           <t>Open filings</t>
@@ -6726,7 +4938,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO39"/>
+  <dimension ref="A1:AO29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -6782,7 +4994,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Universe: NSE_LISTED | NIFTY regime: BEAR | Generated: 21-Oct-2026 16:46 | Targets: +7% / +10% | *Qty sized for Rs 100,000 capital, 1% risk</t>
+          <t>Universe: NSE_LISTED | NIFTY regime: BEAR | Generated: 21-Oct-2026 19:34 | Targets: +7% / +10% | *Qty sized for Rs 100,000 capital, 1% risk</t>
         </is>
       </c>
     </row>
@@ -7017,10 +5229,10 @@
         <v>49.59245330043947</v>
       </c>
       <c r="G5" s="9" t="n">
-        <v>47.75803558110091</v>
+        <v>47.75803558110181</v>
       </c>
       <c r="H5" s="9" t="n">
-        <v>42.9685070952092</v>
+        <v>42.96850709727519</v>
       </c>
       <c r="I5" s="8" t="n">
         <v>75.6141110683601</v>
@@ -7035,13 +5247,13 @@
         <v>0.6691219704525797</v>
       </c>
       <c r="M5" s="8" t="n">
-        <v>26.39500914229825</v>
+        <v>26.39500914229831</v>
       </c>
       <c r="N5" s="8" t="n">
         <v>37.08599842473007</v>
       </c>
       <c r="O5" s="8" t="n">
-        <v>9.57705226428353</v>
+        <v>9.577052264283527</v>
       </c>
       <c r="P5" s="9" t="n">
         <v>1.853131303245163</v>
@@ -7061,10 +5273,10 @@
         <v>4.60659317947286</v>
       </c>
       <c r="U5" s="8" t="n">
-        <v>1.100836045437472</v>
+        <v>1.100836045437653</v>
       </c>
       <c r="V5" s="8" t="n">
-        <v>19.77055638385545</v>
+        <v>19.7705563838495</v>
       </c>
       <c r="W5" s="6" t="inlineStr">
         <is>
@@ -7075,7 +5287,7 @@
         <v>87.37673711693139</v>
       </c>
       <c r="Y5" s="8" t="n">
-        <v>88.0292178630993</v>
+        <v>88.02921786309935</v>
       </c>
       <c r="Z5" s="8" t="n">
         <v>1.308519943112785</v>
@@ -7506,40 +5718,40 @@
         <v>1195.599975585938</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>1116.087579972192</v>
+        <v>1116.087579987063</v>
       </c>
       <c r="G9" s="9" t="n">
-        <v>1074.773871410806</v>
+        <v>1074.773871923889</v>
       </c>
       <c r="H9" s="9" t="n">
-        <v>971.8291503061586</v>
+        <v>971.8291522173467</v>
       </c>
       <c r="I9" s="8" t="n">
-        <v>68.27988496543384</v>
+        <v>68.27988449590266</v>
       </c>
       <c r="J9" s="9" t="n">
-        <v>33.46109029056174</v>
+        <v>33.4610902303782</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>18.60973717896452</v>
+        <v>18.60973709101035</v>
       </c>
       <c r="L9" s="9" t="n">
-        <v>14.85135311159723</v>
+        <v>14.85135313936785</v>
       </c>
       <c r="M9" s="8" t="n">
-        <v>24.83134818788051</v>
+        <v>24.83134681575903</v>
       </c>
       <c r="N9" s="8" t="n">
-        <v>30.88434392264565</v>
+        <v>30.88434383226162</v>
       </c>
       <c r="O9" s="8" t="n">
-        <v>9.927707880127622</v>
+        <v>9.927707967899844</v>
       </c>
       <c r="P9" s="9" t="n">
-        <v>40.68009740826596</v>
+        <v>40.68009755305386</v>
       </c>
       <c r="Q9" s="8" t="n">
-        <v>3.402483961103256</v>
+        <v>3.402483973213317</v>
       </c>
       <c r="R9" s="8" t="n">
         <v>1.67906950564853</v>
@@ -7553,10 +5765,10 @@
         <v>2.432866834382094</v>
       </c>
       <c r="U9" s="8" t="n">
-        <v>0.9292866762074549</v>
+        <v>0.929286676207477</v>
       </c>
       <c r="V9" s="8" t="n">
-        <v>20.09892035520459</v>
+        <v>20.09892035520356</v>
       </c>
       <c r="W9" s="6" t="inlineStr">
         <is>
@@ -7567,7 +5779,7 @@
         <v>80.08868096937361</v>
       </c>
       <c r="Y9" s="8" t="n">
-        <v>87.38191472209193</v>
+        <v>87.38191472209195</v>
       </c>
       <c r="Z9" s="8" t="n">
         <v>-2.527311317219905</v>
@@ -7588,7 +5800,7 @@
         <v>-3.619510230879686</v>
       </c>
       <c r="AF9" s="8" t="n">
-        <v>7.124207547917205</v>
+        <v>7.124207546489836</v>
       </c>
       <c r="AG9" s="6" t="inlineStr">
         <is>
@@ -7610,11 +5822,11 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>MVGJL</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -7623,49 +5835,49 @@
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>122.5</v>
+        <v>220.3600006103516</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>116.6543973258008</v>
+        <v>212.8906391375839</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>115.1755776972354</v>
+        <v>197.2563541614874</v>
       </c>
       <c r="H10" s="9" t="n">
-        <v>111.7858046448731</v>
+        <v>180.1063416116381</v>
       </c>
       <c r="I10" s="8" t="n">
-        <v>63.9838633351069</v>
+        <v>56.18764713704237</v>
       </c>
       <c r="J10" s="9" t="n">
-        <v>1.157884157685473</v>
+        <v>7.994784951675598</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.3369493961111242</v>
+        <v>7.579044642335193</v>
       </c>
       <c r="L10" s="9" t="n">
-        <v>0.8209347615743486</v>
+        <v>0.4157403093404053</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>21.29761785174411</v>
+        <v>38.5651040676958</v>
       </c>
       <c r="N10" s="8" t="n">
-        <v>32.28903395533808</v>
+        <v>29.60051682007033</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>11.71964723716259</v>
+        <v>14.08873855140625</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>3.287142972862145</v>
+        <v>15.0011122563326</v>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>2.683382018662976</v>
+        <v>6.807547746770114</v>
       </c>
       <c r="R10" s="8" t="n">
-        <v>1.825383104202262</v>
+        <v>2.329543882078586</v>
       </c>
       <c r="S10" s="6" t="inlineStr">
         <is>
@@ -7673,45 +5885,45 @@
         </is>
       </c>
       <c r="T10" s="8" t="n">
-        <v>7.984863858027571</v>
+        <v>2.630111557177157</v>
       </c>
       <c r="U10" s="8" t="n">
-        <v>1.019462149160593</v>
+        <v>0.6703099447975798</v>
       </c>
       <c r="V10" s="8" t="n">
-        <v>11.32030774129693</v>
+        <v>16.64054430225472</v>
       </c>
       <c r="W10" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X10" s="8" t="n">
-        <v>82.83910736556741</v>
+        <v>42.32373670992567</v>
       </c>
       <c r="Y10" s="8" t="n">
-        <v>76.45695053046516</v>
+        <v>73.24218932088527</v>
       </c>
       <c r="Z10" s="8" t="n">
-        <v>0.4922054689176614</v>
+        <v>-8.62118756472251</v>
       </c>
       <c r="AA10" s="8" t="n">
-        <v>5.105102353021729</v>
+        <v>3.401998957925878</v>
       </c>
       <c r="AB10" s="8" t="n">
-        <v>4.459796628844548</v>
+        <v>2.746304544283218</v>
       </c>
       <c r="AC10" s="8" t="n">
-        <v>9.296928978152618</v>
+        <v>39.27442732285695</v>
       </c>
       <c r="AD10" s="8" t="n">
-        <v>-2.172177922206742</v>
+        <v>-9.688524340019855</v>
       </c>
       <c r="AE10" s="8" t="n">
-        <v>-6.724314093916462</v>
+        <v>-11.64394306207807</v>
       </c>
       <c r="AF10" s="8" t="n">
-        <v>5.011043568184737</v>
+        <v>3.508543871645053</v>
       </c>
       <c r="AG10" s="6" t="inlineStr">
         <is>
@@ -7733,11 +5945,11 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>MVGJL</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -7749,46 +5961,46 @@
         <v>74</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>220.3600006103516</v>
+        <v>122.5</v>
       </c>
       <c r="F11" s="9" t="n">
-        <v>212.8906391375839</v>
+        <v>116.6543973258008</v>
       </c>
       <c r="G11" s="9" t="n">
-        <v>197.2563541614874</v>
+        <v>115.1755776972347</v>
       </c>
       <c r="H11" s="9" t="n">
-        <v>180.1063416116381</v>
+        <v>111.7858045843213</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>56.18764713704237</v>
+        <v>63.9838633351069</v>
       </c>
       <c r="J11" s="9" t="n">
-        <v>7.994784951675598</v>
+        <v>1.157884157685473</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>7.579044642335193</v>
+        <v>0.3369493961111242</v>
       </c>
       <c r="L11" s="9" t="n">
-        <v>0.4157403093404053</v>
+        <v>0.8209347615743486</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>38.5651040676958</v>
+        <v>21.29761785174411</v>
       </c>
       <c r="N11" s="8" t="n">
-        <v>29.60051682007033</v>
+        <v>32.28903395533808</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>14.08873855140625</v>
+        <v>11.71964723716259</v>
       </c>
       <c r="P11" s="9" t="n">
-        <v>15.0011122563326</v>
+        <v>3.287142972862145</v>
       </c>
       <c r="Q11" s="8" t="n">
-        <v>6.807547746770114</v>
+        <v>2.683382018662976</v>
       </c>
       <c r="R11" s="8" t="n">
-        <v>2.329543882078586</v>
+        <v>1.825383104202262</v>
       </c>
       <c r="S11" s="6" t="inlineStr">
         <is>
@@ -7796,45 +6008,45 @@
         </is>
       </c>
       <c r="T11" s="8" t="n">
-        <v>2.630111557177157</v>
+        <v>7.984863858027571</v>
       </c>
       <c r="U11" s="8" t="n">
-        <v>0.6703099447975798</v>
+        <v>1.019462149160777</v>
       </c>
       <c r="V11" s="8" t="n">
-        <v>16.64054430225472</v>
+        <v>11.3203077412929</v>
       </c>
       <c r="W11" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X11" s="8" t="n">
-        <v>42.32373670992567</v>
+        <v>82.83910736556741</v>
       </c>
       <c r="Y11" s="8" t="n">
-        <v>73.24218932088527</v>
+        <v>76.45695053046518</v>
       </c>
       <c r="Z11" s="8" t="n">
-        <v>-8.62118756472251</v>
+        <v>0.4922054689176614</v>
       </c>
       <c r="AA11" s="8" t="n">
-        <v>3.401998957925878</v>
+        <v>5.105102353021729</v>
       </c>
       <c r="AB11" s="8" t="n">
-        <v>2.746304544283218</v>
+        <v>4.459796628844548</v>
       </c>
       <c r="AC11" s="8" t="n">
-        <v>39.27442732285695</v>
+        <v>9.296928978152618</v>
       </c>
       <c r="AD11" s="8" t="n">
-        <v>-9.688524340019855</v>
+        <v>-2.172177922206742</v>
       </c>
       <c r="AE11" s="8" t="n">
-        <v>-11.64394306207807</v>
+        <v>-6.724314093916462</v>
       </c>
       <c r="AF11" s="8" t="n">
-        <v>3.508543871645053</v>
+        <v>5.011043568184737</v>
       </c>
       <c r="AG11" s="6" t="inlineStr">
         <is>
@@ -7856,7 +6068,7 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
@@ -7878,37 +6090,37 @@
         <v>688.3491360872083</v>
       </c>
       <c r="G12" s="9" t="n">
-        <v>670.8665872836547</v>
+        <v>670.8665872840307</v>
       </c>
       <c r="H12" s="9" t="n">
-        <v>634.574910087748</v>
+        <v>634.5749103375026</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>63.58154366124493</v>
+        <v>63.58154366124482</v>
       </c>
       <c r="J12" s="9" t="n">
         <v>22.14683695555368</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>10.12839058121485</v>
+        <v>10.12839058121484</v>
       </c>
       <c r="L12" s="9" t="n">
-        <v>12.01844637433883</v>
+        <v>12.01844637433884</v>
       </c>
       <c r="M12" s="8" t="n">
-        <v>20.41909425836643</v>
+        <v>20.41909425836191</v>
       </c>
       <c r="N12" s="8" t="n">
-        <v>29.06531719716947</v>
+        <v>29.06531719716964</v>
       </c>
       <c r="O12" s="8" t="n">
-        <v>14.94981873075661</v>
+        <v>14.94981873075672</v>
       </c>
       <c r="P12" s="9" t="n">
-        <v>31.59296868614264</v>
+        <v>31.59296868614267</v>
       </c>
       <c r="Q12" s="8" t="n">
-        <v>4.223658915259712</v>
+        <v>4.223658915259715</v>
       </c>
       <c r="R12" s="8" t="n">
         <v>0.935577019623052</v>
@@ -7922,10 +6134,10 @@
         <v>3.111621265517688</v>
       </c>
       <c r="U12" s="8" t="n">
-        <v>0.931319896043049</v>
+        <v>0.9313198960430479</v>
       </c>
       <c r="V12" s="8" t="n">
-        <v>24.78956666200447</v>
+        <v>24.78956666200453</v>
       </c>
       <c r="W12" s="6" t="inlineStr">
         <is>
@@ -7979,7 +6191,7 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
@@ -8102,7 +6314,7 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
@@ -8124,34 +6336,34 @@
         <v>1697.695398900391</v>
       </c>
       <c r="G14" s="9" t="n">
-        <v>1681.315757048436</v>
+        <v>1681.315757047815</v>
       </c>
       <c r="H14" s="9" t="n">
-        <v>1769.929411615097</v>
+        <v>1769.929409970859</v>
       </c>
       <c r="I14" s="8" t="n">
-        <v>68.49224564918718</v>
+        <v>68.4922456491872</v>
       </c>
       <c r="J14" s="9" t="n">
         <v>41.8427394085661</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>11.77720289633632</v>
+        <v>11.77720289633633</v>
       </c>
       <c r="L14" s="9" t="n">
-        <v>30.06553651222978</v>
+        <v>30.06553651222977</v>
       </c>
       <c r="M14" s="8" t="n">
-        <v>27.11851077235017</v>
+        <v>27.11851077235103</v>
       </c>
       <c r="N14" s="8" t="n">
-        <v>35.91864313586981</v>
+        <v>35.91864313586977</v>
       </c>
       <c r="O14" s="8" t="n">
-        <v>9.29173542541451</v>
+        <v>9.291735425414466</v>
       </c>
       <c r="P14" s="9" t="n">
-        <v>62.34973233017811</v>
+        <v>62.34973233017809</v>
       </c>
       <c r="Q14" s="8" t="n">
         <v>3.375364550579543</v>
@@ -8168,10 +6380,10 @@
         <v>8.773563180028036</v>
       </c>
       <c r="U14" s="8" t="n">
-        <v>0.9930054604849806</v>
+        <v>0.9930054604848949</v>
       </c>
       <c r="V14" s="8" t="n">
-        <v>24.40810772803948</v>
+        <v>24.40810772804372</v>
       </c>
       <c r="W14" s="6" t="inlineStr">
         <is>
@@ -8225,7 +6437,7 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
@@ -8348,7 +6560,7 @@
     </row>
     <row r="16">
       <c r="A16" s="5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
@@ -8471,7 +6683,7 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
@@ -8493,37 +6705,37 @@
         <v>544.028568812026</v>
       </c>
       <c r="G17" s="9" t="n">
-        <v>535.485733834758</v>
+        <v>535.4857338348953</v>
       </c>
       <c r="H17" s="9" t="n">
-        <v>557.9397549615769</v>
+        <v>557.9397549272942</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>75.69258148306497</v>
+        <v>75.69258148306517</v>
       </c>
       <c r="J17" s="9" t="n">
         <v>17.05081563447754</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>6.282673868158058</v>
+        <v>6.282673868158055</v>
       </c>
       <c r="L17" s="9" t="n">
         <v>10.76814176631949</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>34.25890727221858</v>
+        <v>34.25890727222002</v>
       </c>
       <c r="N17" s="8" t="n">
-        <v>36.85596234087548</v>
+        <v>36.8559623408754</v>
       </c>
       <c r="O17" s="8" t="n">
-        <v>8.639015776594022</v>
+        <v>8.639015776593929</v>
       </c>
       <c r="P17" s="9" t="n">
-        <v>20.52903458336015</v>
+        <v>20.52903458336017</v>
       </c>
       <c r="Q17" s="8" t="n">
-        <v>3.395473935218868</v>
+        <v>3.395473935218872</v>
       </c>
       <c r="R17" s="8" t="n">
         <v>1.452786904736316</v>
@@ -8537,10 +6749,10 @@
         <v>170.7488854067985</v>
       </c>
       <c r="U17" s="8" t="n">
-        <v>1.003541598185116</v>
+        <v>1.003541598185125</v>
       </c>
       <c r="V17" s="8" t="n">
-        <v>29.53802163541473</v>
+        <v>29.53802163541426</v>
       </c>
       <c r="W17" s="6" t="inlineStr">
         <is>
@@ -8594,62 +6806,62 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>TFCILTD</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>NEAR BREAKOUT</t>
+          <t>EMA20 PULLBACK</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E18" s="9" t="n">
-        <v>1951</v>
+        <v>150.1999969482422</v>
       </c>
       <c r="F18" s="9" t="n">
-        <v>1875.466768057533</v>
+        <v>148.6034311026721</v>
       </c>
       <c r="G18" s="9" t="n">
-        <v>1818.310674791113</v>
+        <v>136.406951508431</v>
       </c>
       <c r="H18" s="9" t="n">
-        <v>1638.452175840209</v>
+        <v>99.43699802047756</v>
       </c>
       <c r="I18" s="8" t="n">
-        <v>62.5154729366246</v>
+        <v>55.55823012731431</v>
       </c>
       <c r="J18" s="9" t="n">
-        <v>31.70456367222846</v>
+        <v>5.334571853616467</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>17.87858401137785</v>
+        <v>5.185653051446711</v>
       </c>
       <c r="L18" s="9" t="n">
-        <v>13.82597966085061</v>
+        <v>0.1489188021697556</v>
       </c>
       <c r="M18" s="8" t="n">
-        <v>19.30972655528189</v>
+        <v>38.81636756382034</v>
       </c>
       <c r="N18" s="8" t="n">
-        <v>19.05175707696737</v>
+        <v>24.81263262971194</v>
       </c>
       <c r="O18" s="8" t="n">
-        <v>13.35208766426721</v>
+        <v>19.58751990156778</v>
       </c>
       <c r="P18" s="9" t="n">
-        <v>57.93546377224519</v>
+        <v>6.15627114690921</v>
       </c>
       <c r="Q18" s="8" t="n">
-        <v>2.969526590068949</v>
+        <v>4.098715893470102</v>
       </c>
       <c r="R18" s="8" t="n">
-        <v>1.002842997044937</v>
+        <v>1.014430895810536</v>
       </c>
       <c r="S18" s="6" t="inlineStr">
         <is>
@@ -8657,13 +6869,13 @@
         </is>
       </c>
       <c r="T18" s="8" t="n">
-        <v>1.571612486553095</v>
+        <v>1.97514623966385</v>
       </c>
       <c r="U18" s="8" t="n">
-        <v>0.8736533061306183</v>
+        <v>0.6025489221374285</v>
       </c>
       <c r="V18" s="8" t="n">
-        <v>15.39661296259011</v>
+        <v>20.95317723519181</v>
       </c>
       <c r="W18" s="6" t="inlineStr">
         <is>
@@ -8671,31 +6883,31 @@
         </is>
       </c>
       <c r="X18" s="8" t="n">
-        <v>91.39882394744069</v>
+        <v>52.90580586292285</v>
       </c>
       <c r="Y18" s="8" t="n">
-        <v>88.65176180157465</v>
+        <v>68.58294904486161</v>
       </c>
       <c r="Z18" s="8" t="n">
-        <v>1.350649350649347</v>
+        <v>-3.828912798038808</v>
       </c>
       <c r="AA18" s="8" t="n">
-        <v>1.140487299118709</v>
+        <v>-5.35005694281142</v>
       </c>
       <c r="AB18" s="8" t="n">
-        <v>5.975013579576327</v>
+        <v>7.577712506131062</v>
       </c>
       <c r="AC18" s="8" t="n">
-        <v>30.89324987006981</v>
+        <v>81.45131454641812</v>
       </c>
       <c r="AD18" s="8" t="n">
-        <v>-0.9644670050761417</v>
+        <v>-7.255325854532247</v>
       </c>
       <c r="AE18" s="8" t="n">
-        <v>-3.473181915088297</v>
+        <v>-7.255325854532247</v>
       </c>
       <c r="AF18" s="8" t="n">
-        <v>4.027436434968057</v>
+        <v>1.074380203554659</v>
       </c>
       <c r="AG18" s="6" t="inlineStr">
         <is>
@@ -8708,71 +6920,81 @@
       <c r="AI18" s="8" t="n">
         <v>-5.690287434648067</v>
       </c>
-      <c r="AJ18" s="6" t="inlineStr"/>
-      <c r="AK18" s="6" t="inlineStr"/>
+      <c r="AJ18" s="5" t="n">
+        <v>6953.918464</v>
+      </c>
+      <c r="AK18" s="8" t="n">
+        <v>45.105106</v>
+      </c>
       <c r="AL18" s="6" t="inlineStr"/>
-      <c r="AM18" s="6" t="inlineStr"/>
-      <c r="AN18" s="6" t="inlineStr"/>
-      <c r="AO18" s="6" t="inlineStr"/>
+      <c r="AM18" s="8" t="n">
+        <v>0.81939</v>
+      </c>
+      <c r="AN18" s="8" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="AO18" s="8" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>SINGERIND</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>NEAR BREAKOUT</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
         <v>71</v>
       </c>
       <c r="E19" s="9" t="n">
-        <v>88.41000366210938</v>
+        <v>1951</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>79.8283067157062</v>
+        <v>1875.466768057533</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>77.06363848040199</v>
+        <v>1818.310674792111</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>72.86769460332832</v>
+        <v>1638.452174990161</v>
       </c>
       <c r="I19" s="8" t="n">
-        <v>66.90974802020604</v>
+        <v>62.51547293662475</v>
       </c>
       <c r="J19" s="9" t="n">
-        <v>2.608905036124028</v>
+        <v>31.70456367222823</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>1.030891362640057</v>
+        <v>17.87858401137746</v>
       </c>
       <c r="L19" s="9" t="n">
-        <v>1.578013673483972</v>
+        <v>13.82597966085077</v>
       </c>
       <c r="M19" s="8" t="n">
-        <v>19.52771574707711</v>
+        <v>19.30972655529489</v>
       </c>
       <c r="N19" s="8" t="n">
-        <v>33.77488504436531</v>
+        <v>19.05175707696692</v>
       </c>
       <c r="O19" s="8" t="n">
-        <v>8.249807193681619</v>
+        <v>13.35208766426643</v>
       </c>
       <c r="P19" s="9" t="n">
-        <v>4.670943971119574</v>
+        <v>57.93546377224512</v>
       </c>
       <c r="Q19" s="8" t="n">
-        <v>5.283275396041455</v>
+        <v>2.969526590068945</v>
       </c>
       <c r="R19" s="8" t="n">
-        <v>1.660547293380202</v>
+        <v>1.002842997044937</v>
       </c>
       <c r="S19" s="6" t="inlineStr">
         <is>
@@ -8780,13 +7002,13 @@
         </is>
       </c>
       <c r="T19" s="8" t="n">
-        <v>7.062105814363507</v>
+        <v>1.571612486553095</v>
       </c>
       <c r="U19" s="8" t="n">
-        <v>0.9684698734411753</v>
+        <v>0.8736533061305675</v>
       </c>
       <c r="V19" s="8" t="n">
-        <v>26.72744832302393</v>
+        <v>15.39661296259221</v>
       </c>
       <c r="W19" s="6" t="inlineStr">
         <is>
@@ -8794,29 +7016,31 @@
         </is>
       </c>
       <c r="X19" s="8" t="n">
-        <v>64.98038084419765</v>
+        <v>91.39882394744069</v>
       </c>
       <c r="Y19" s="8" t="n">
-        <v>81.53493681693539</v>
+        <v>88.65176180157465</v>
       </c>
       <c r="Z19" s="8" t="n">
-        <v>-4.452604746072176</v>
+        <v>1.350649350649347</v>
       </c>
       <c r="AA19" s="8" t="n">
-        <v>15.94754578637294</v>
+        <v>1.140487299118709</v>
       </c>
       <c r="AB19" s="8" t="n">
-        <v>15.90194687588891</v>
+        <v>5.975013579576327</v>
       </c>
       <c r="AC19" s="8" t="n">
-        <v>36.97125076460732</v>
+        <v>30.89324987006981</v>
       </c>
       <c r="AD19" s="8" t="n">
-        <v>-8.326419095826587</v>
-      </c>
-      <c r="AE19" s="6" t="inlineStr"/>
+        <v>-0.9644670050761417</v>
+      </c>
+      <c r="AE19" s="8" t="n">
+        <v>-3.473181915088297</v>
+      </c>
       <c r="AF19" s="8" t="n">
-        <v>10.75019288203782</v>
+        <v>4.027436434968057</v>
       </c>
       <c r="AG19" s="6" t="inlineStr">
         <is>
@@ -8838,108 +7062,106 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>TATVA</t>
+          <t>SINGERIND</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>TREND CONTINUATION</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
         <v>71</v>
       </c>
       <c r="E20" s="9" t="n">
-        <v>1890.099975585938</v>
+        <v>88.41000366210938</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>1842.989654325005</v>
+        <v>79.8283067157062</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>1740.378285852139</v>
+        <v>77.06363848040199</v>
       </c>
       <c r="H20" s="9" t="n">
-        <v>1462.24312382702</v>
+        <v>72.86769460332832</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>56.30276892733634</v>
+        <v>66.90974802020604</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>58.26782377698328</v>
+        <v>2.608905036124028</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>56.85950278164436</v>
+        <v>1.030891362640057</v>
       </c>
       <c r="L20" s="9" t="n">
-        <v>1.408320995338919</v>
+        <v>1.578013673483972</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>26.90121478247604</v>
+        <v>19.52771574707711</v>
       </c>
       <c r="N20" s="8" t="n">
-        <v>26.06408986067177</v>
+        <v>33.77488504436531</v>
       </c>
       <c r="O20" s="8" t="n">
-        <v>13.0344029543037</v>
+        <v>8.249807193681619</v>
       </c>
       <c r="P20" s="9" t="n">
-        <v>111.8933002853234</v>
+        <v>4.670943971119574</v>
       </c>
       <c r="Q20" s="8" t="n">
-        <v>5.919967289065546</v>
+        <v>5.283275396041455</v>
       </c>
       <c r="R20" s="8" t="n">
-        <v>8.084786396208008</v>
+        <v>1.660547293380202</v>
       </c>
       <c r="S20" s="6" t="inlineStr">
         <is>
-          <t>Weak</t>
+          <t>Rising</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
-        <v>0.5078779031274573</v>
+        <v>7.062105814363507</v>
       </c>
       <c r="U20" s="8" t="n">
-        <v>0.6624258701903957</v>
+        <v>0.9684698734411753</v>
       </c>
       <c r="V20" s="8" t="n">
-        <v>16.80990180301226</v>
+        <v>26.72744832302393</v>
       </c>
       <c r="W20" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X20" s="8" t="n">
-        <v>48.10771208189792</v>
+        <v>64.98038084419765</v>
       </c>
       <c r="Y20" s="8" t="n">
-        <v>65.30949558174034</v>
+        <v>81.53493681693539</v>
       </c>
       <c r="Z20" s="8" t="n">
-        <v>-0.6987521623164406</v>
+        <v>-4.452604746072176</v>
       </c>
       <c r="AA20" s="8" t="n">
-        <v>2.650297369452126</v>
+        <v>15.94754578637294</v>
       </c>
       <c r="AB20" s="8" t="n">
-        <v>6.773247526907267</v>
+        <v>15.90194687588891</v>
       </c>
       <c r="AC20" s="8" t="n">
-        <v>12.30748274392155</v>
+        <v>36.97125076460732</v>
       </c>
       <c r="AD20" s="8" t="n">
-        <v>-5.90431515253168</v>
-      </c>
-      <c r="AE20" s="8" t="n">
-        <v>-10.57438076001934</v>
-      </c>
+        <v>-8.326419095826587</v>
+      </c>
+      <c r="AE20" s="6" t="inlineStr"/>
       <c r="AF20" s="8" t="n">
-        <v>2.556190217909071</v>
+        <v>10.75019288203782</v>
       </c>
       <c r="AG20" s="6" t="inlineStr">
         <is>
@@ -8961,76 +7183,76 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>KROSS</t>
+          <t>TATVA</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>TREND CONTINUATION</t>
         </is>
       </c>
       <c r="D21" s="5" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E21" s="9" t="n">
-        <v>278.2999877929688</v>
+        <v>1890.099975585938</v>
       </c>
       <c r="F21" s="9" t="n">
-        <v>259.5414512658439</v>
+        <v>1842.989654325005</v>
       </c>
       <c r="G21" s="9" t="n">
-        <v>240.1661853682125</v>
+        <v>1740.378285852139</v>
       </c>
       <c r="H21" s="9" t="n">
-        <v>209.0401391373265</v>
+        <v>1462.24312382702</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>60.3548257207129</v>
+        <v>56.30276892733634</v>
       </c>
       <c r="J21" s="9" t="n">
-        <v>11.49883593257886</v>
+        <v>58.26782377698328</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>9.735102306838497</v>
+        <v>56.85950278164436</v>
       </c>
       <c r="L21" s="9" t="n">
-        <v>1.763733625740359</v>
+        <v>1.408320995338919</v>
       </c>
       <c r="M21" s="8" t="n">
-        <v>34.96697287402402</v>
+        <v>26.90121478247604</v>
       </c>
       <c r="N21" s="8" t="n">
-        <v>39.9620948590197</v>
+        <v>26.06408986067177</v>
       </c>
       <c r="O21" s="8" t="n">
-        <v>17.47905896456665</v>
+        <v>13.0344029543037</v>
       </c>
       <c r="P21" s="9" t="n">
-        <v>17.84972531802494</v>
+        <v>111.8933002853234</v>
       </c>
       <c r="Q21" s="8" t="n">
-        <v>6.413843370810207</v>
+        <v>5.919967289065546</v>
       </c>
       <c r="R21" s="8" t="n">
-        <v>1.241093910380829</v>
+        <v>8.084786396208008</v>
       </c>
       <c r="S21" s="6" t="inlineStr">
         <is>
-          <t>Rising</t>
+          <t>Weak</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
-        <v>5.014420038393031</v>
+        <v>0.5078779031274573</v>
       </c>
       <c r="U21" s="8" t="n">
-        <v>0.771969913173298</v>
+        <v>0.6624258701903957</v>
       </c>
       <c r="V21" s="8" t="n">
-        <v>22.15950373469972</v>
+        <v>16.80990180301226</v>
       </c>
       <c r="W21" s="6" t="inlineStr">
         <is>
@@ -9038,31 +7260,31 @@
         </is>
       </c>
       <c r="X21" s="8" t="n">
-        <v>47.91552693882885</v>
+        <v>48.10771208189792</v>
       </c>
       <c r="Y21" s="8" t="n">
-        <v>65.97968363437536</v>
+        <v>65.30949558174034</v>
       </c>
       <c r="Z21" s="8" t="n">
-        <v>-6.469501189626625</v>
+        <v>-0.6987521623164406</v>
       </c>
       <c r="AA21" s="8" t="n">
-        <v>14.15093696036038</v>
+        <v>2.650297369452126</v>
       </c>
       <c r="AB21" s="8" t="n">
-        <v>16.35101172806885</v>
+        <v>6.773247526907267</v>
       </c>
       <c r="AC21" s="8" t="n">
-        <v>31.75211542963898</v>
+        <v>12.30748274392155</v>
       </c>
       <c r="AD21" s="8" t="n">
-        <v>-14.73652175335831</v>
+        <v>-5.90431515253168</v>
       </c>
       <c r="AE21" s="8" t="n">
-        <v>-14.73652175335831</v>
+        <v>-10.57438076001934</v>
       </c>
       <c r="AF21" s="8" t="n">
-        <v>7.227568635235371</v>
+        <v>2.556190217909071</v>
       </c>
       <c r="AG21" s="6" t="inlineStr">
         <is>
@@ -9084,62 +7306,62 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>PREMEXPLN</t>
+          <t>KROSS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>NEAR BREAKOUT</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D22" s="5" t="n">
         <v>70</v>
       </c>
       <c r="E22" s="9" t="n">
-        <v>692.5</v>
+        <v>278.2999877929688</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>684.8719005900904</v>
+        <v>259.5414512658439</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>676.8786920727016</v>
+        <v>240.1661853682125</v>
       </c>
       <c r="H22" s="9" t="n">
-        <v>621.0198240159968</v>
+        <v>209.0401391373265</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>66.70787117571641</v>
+        <v>60.3548257207129</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>5.534008581310218</v>
+        <v>11.49883593257886</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>5.15814272087527</v>
+        <v>9.735102306838497</v>
       </c>
       <c r="L22" s="9" t="n">
-        <v>0.3758658604349474</v>
+        <v>1.763733625740359</v>
       </c>
       <c r="M22" s="8" t="n">
-        <v>46.76226185030922</v>
+        <v>34.96697287402402</v>
       </c>
       <c r="N22" s="8" t="n">
-        <v>22.2066236325665</v>
+        <v>39.9620948590197</v>
       </c>
       <c r="O22" s="8" t="n">
-        <v>6.924050911455695</v>
+        <v>17.47905896456665</v>
       </c>
       <c r="P22" s="9" t="n">
-        <v>7.828533860471436</v>
+        <v>17.84972531802494</v>
       </c>
       <c r="Q22" s="8" t="n">
-        <v>1.130474203678186</v>
+        <v>6.413843370810207</v>
       </c>
       <c r="R22" s="8" t="n">
-        <v>4.153208308318388</v>
+        <v>1.241093910380829</v>
       </c>
       <c r="S22" s="6" t="inlineStr">
         <is>
@@ -9147,45 +7369,45 @@
         </is>
       </c>
       <c r="T22" s="8" t="n">
-        <v>1.22923739727929</v>
+        <v>5.014420038393031</v>
       </c>
       <c r="U22" s="8" t="n">
-        <v>0.8236370837102031</v>
+        <v>0.771969913173298</v>
       </c>
       <c r="V22" s="8" t="n">
-        <v>3.51880798613692</v>
+        <v>22.15950373469972</v>
       </c>
       <c r="W22" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X22" s="8" t="n">
-        <v>86.84210526315789</v>
+        <v>47.91552693882885</v>
       </c>
       <c r="Y22" s="8" t="n">
-        <v>89.05521077517547</v>
+        <v>65.97968363437536</v>
       </c>
       <c r="Z22" s="8" t="n">
-        <v>-0.05051246276533972</v>
+        <v>-6.469501189626625</v>
       </c>
       <c r="AA22" s="8" t="n">
-        <v>0.5006911353531374</v>
+        <v>14.15093696036038</v>
       </c>
       <c r="AB22" s="8" t="n">
-        <v>3.705784997361627</v>
+        <v>16.35101172806885</v>
       </c>
       <c r="AC22" s="8" t="n">
-        <v>5.369303159076821</v>
+        <v>31.75211542963898</v>
       </c>
       <c r="AD22" s="8" t="n">
-        <v>-0.295153384061364</v>
+        <v>-14.73652175335831</v>
       </c>
       <c r="AE22" s="8" t="n">
-        <v>-16.48422293160215</v>
+        <v>-14.73652175335831</v>
       </c>
       <c r="AF22" s="8" t="n">
-        <v>1.113799442397512</v>
+        <v>7.227568635235371</v>
       </c>
       <c r="AG22" s="6" t="inlineStr">
         <is>
@@ -9207,62 +7429,62 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>SMARTLINK</t>
+          <t>PREMEXPLN</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>EMA20 PULLBACK</t>
+          <t>NEAR BREAKOUT</t>
         </is>
       </c>
       <c r="D23" s="5" t="n">
         <v>70</v>
       </c>
       <c r="E23" s="9" t="n">
-        <v>225.1000061035156</v>
+        <v>692.5</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>221.6149047954655</v>
+        <v>684.8719005900904</v>
       </c>
       <c r="G23" s="9" t="n">
-        <v>215.7510141611334</v>
+        <v>676.8786920727016</v>
       </c>
       <c r="H23" s="9" t="n">
-        <v>181.8591515068511</v>
+        <v>621.0198240159968</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>51.89520874760166</v>
+        <v>66.70787117571641</v>
       </c>
       <c r="J23" s="9" t="n">
-        <v>3.107290398667715</v>
+        <v>5.534008581310218</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>1.453529083609551</v>
+        <v>5.15814272087527</v>
       </c>
       <c r="L23" s="9" t="n">
-        <v>1.653761315058163</v>
+        <v>0.3758658604349474</v>
       </c>
       <c r="M23" s="8" t="n">
-        <v>18.69283495119275</v>
+        <v>46.76226185030922</v>
       </c>
       <c r="N23" s="8" t="n">
-        <v>28.17327797238993</v>
+        <v>22.2066236325665</v>
       </c>
       <c r="O23" s="8" t="n">
-        <v>14.11569339682238</v>
+        <v>6.924050911455695</v>
       </c>
       <c r="P23" s="9" t="n">
-        <v>15.34653385568652</v>
+        <v>7.828533860471436</v>
       </c>
       <c r="Q23" s="8" t="n">
-        <v>6.817651461381653</v>
+        <v>1.130474203678186</v>
       </c>
       <c r="R23" s="8" t="n">
-        <v>6.808585302932585</v>
+        <v>4.153208308318388</v>
       </c>
       <c r="S23" s="6" t="inlineStr">
         <is>
@@ -9270,13 +7492,13 @@
         </is>
       </c>
       <c r="T23" s="8" t="n">
-        <v>2.313837871255248</v>
+        <v>1.22923739727929</v>
       </c>
       <c r="U23" s="8" t="n">
-        <v>0.6303295809498551</v>
+        <v>0.8236370837102031</v>
       </c>
       <c r="V23" s="8" t="n">
-        <v>19.48401173344025</v>
+        <v>3.51880798613692</v>
       </c>
       <c r="W23" s="6" t="inlineStr">
         <is>
@@ -9284,31 +7506,31 @@
         </is>
       </c>
       <c r="X23" s="8" t="n">
-        <v>35.64517113470262</v>
+        <v>86.84210526315789</v>
       </c>
       <c r="Y23" s="8" t="n">
-        <v>57.5080359284133</v>
+        <v>89.05521077517547</v>
       </c>
       <c r="Z23" s="8" t="n">
-        <v>-12.40563604945467</v>
+        <v>-0.05051246276533972</v>
       </c>
       <c r="AA23" s="8" t="n">
-        <v>2.808864691022239</v>
+        <v>0.5006911353531374</v>
       </c>
       <c r="AB23" s="8" t="n">
-        <v>2.109326023880675</v>
+        <v>3.705784997361627</v>
       </c>
       <c r="AC23" s="8" t="n">
-        <v>1.023246882843565</v>
+        <v>5.369303159076821</v>
       </c>
       <c r="AD23" s="8" t="n">
-        <v>-12.67747413706866</v>
+        <v>-0.295153384061364</v>
       </c>
       <c r="AE23" s="8" t="n">
-        <v>-15.05660147037147</v>
+        <v>-16.48422293160215</v>
       </c>
       <c r="AF23" s="8" t="n">
-        <v>1.572593373747422</v>
+        <v>1.113799442397512</v>
       </c>
       <c r="AG23" s="6" t="inlineStr">
         <is>
@@ -9330,62 +7552,62 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>IBULLSLTD</t>
+          <t>SMARTLINK</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>TREND CONTINUATION</t>
+          <t>EMA20 PULLBACK</t>
         </is>
       </c>
       <c r="D24" s="5" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E24" s="9" t="n">
-        <v>34.56999969482422</v>
+        <v>225.1000061035156</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>33.09365179579358</v>
+        <v>221.6149047954655</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>30.35993396776341</v>
+        <v>215.7510141611334</v>
       </c>
       <c r="H24" s="9" t="n">
-        <v>23.83756827207516</v>
+        <v>181.8591515068511</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>59.1057335831394</v>
+        <v>51.89520874760166</v>
       </c>
       <c r="J24" s="9" t="n">
-        <v>2.027549691453743</v>
+        <v>3.107290398667715</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>1.973920060469503</v>
+        <v>1.453529083609551</v>
       </c>
       <c r="L24" s="9" t="n">
-        <v>0.0536296309842399</v>
+        <v>1.653761315058163</v>
       </c>
       <c r="M24" s="8" t="n">
-        <v>33.82534715842232</v>
+        <v>18.69283495119275</v>
       </c>
       <c r="N24" s="8" t="n">
-        <v>25.48484811572801</v>
+        <v>28.17327797238993</v>
       </c>
       <c r="O24" s="8" t="n">
-        <v>23.312974801597</v>
+        <v>14.11569339682238</v>
       </c>
       <c r="P24" s="9" t="n">
-        <v>2.237251736827528</v>
+        <v>15.34653385568652</v>
       </c>
       <c r="Q24" s="8" t="n">
-        <v>6.471656802364642</v>
+        <v>6.817651461381653</v>
       </c>
       <c r="R24" s="8" t="n">
-        <v>1.892055834504154</v>
+        <v>6.808585302932585</v>
       </c>
       <c r="S24" s="6" t="inlineStr">
         <is>
@@ -9393,45 +7615,45 @@
         </is>
       </c>
       <c r="T24" s="8" t="n">
-        <v>3.241470010570246</v>
+        <v>2.313837871255248</v>
       </c>
       <c r="U24" s="8" t="n">
-        <v>0.6482572646672726</v>
+        <v>0.6303295809498551</v>
       </c>
       <c r="V24" s="8" t="n">
-        <v>41.40767931120109</v>
+        <v>19.48401173344025</v>
       </c>
       <c r="W24" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X24" s="8" t="n">
-        <v>58.09893386420898</v>
+        <v>35.64517113470262</v>
       </c>
       <c r="Y24" s="8" t="n">
-        <v>59.91547673767479</v>
+        <v>57.5080359284133</v>
       </c>
       <c r="Z24" s="8" t="n">
-        <v>1.141016343377221</v>
+        <v>-12.40563604945467</v>
       </c>
       <c r="AA24" s="8" t="n">
-        <v>-5.494811469703298</v>
+        <v>2.808864691022239</v>
       </c>
       <c r="AB24" s="8" t="n">
-        <v>13.75452579508636</v>
+        <v>2.109326023880675</v>
       </c>
       <c r="AC24" s="8" t="n">
-        <v>19.37154968129626</v>
+        <v>1.023246882843565</v>
       </c>
       <c r="AD24" s="8" t="n">
-        <v>-11.10825343950531</v>
+        <v>-12.67747413706866</v>
       </c>
       <c r="AE24" s="8" t="n">
-        <v>-11.10825343950531</v>
+        <v>-15.05660147037147</v>
       </c>
       <c r="AF24" s="8" t="n">
-        <v>4.461121148371694</v>
+        <v>1.572593373747422</v>
       </c>
       <c r="AG24" s="6" t="inlineStr">
         <is>
@@ -9453,62 +7675,62 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>JUSTDIAL</t>
+          <t>IBULLSLTD</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>MOMENTUM</t>
+          <t>TREND CONTINUATION</t>
         </is>
       </c>
       <c r="D25" s="5" t="n">
         <v>69</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>767.25</v>
+        <v>34.56999969482422</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>685.4692696941277</v>
+        <v>33.09365179579358</v>
       </c>
       <c r="G25" s="9" t="n">
-        <v>674.1895350176654</v>
+        <v>30.35993396776341</v>
       </c>
       <c r="H25" s="9" t="n">
-        <v>663.4476517046772</v>
+        <v>23.83756827207516</v>
       </c>
       <c r="I25" s="8" t="n">
-        <v>74.34297471836601</v>
+        <v>59.1057335831394</v>
       </c>
       <c r="J25" s="9" t="n">
-        <v>12.62689463783363</v>
+        <v>2.027549691453743</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>1.131727889051859</v>
+        <v>1.973920060469503</v>
       </c>
       <c r="L25" s="9" t="n">
-        <v>11.49516674878177</v>
+        <v>0.0536296309842399</v>
       </c>
       <c r="M25" s="8" t="n">
-        <v>19.66555906133593</v>
+        <v>33.82534715842232</v>
       </c>
       <c r="N25" s="8" t="n">
-        <v>33.19818465281759</v>
+        <v>25.48484811572801</v>
       </c>
       <c r="O25" s="8" t="n">
-        <v>13.40503856509307</v>
+        <v>23.312974801597</v>
       </c>
       <c r="P25" s="9" t="n">
-        <v>32.66856476911926</v>
+        <v>2.237251736827528</v>
       </c>
       <c r="Q25" s="8" t="n">
-        <v>4.257877454430662</v>
+        <v>6.471656802364642</v>
       </c>
       <c r="R25" s="8" t="n">
-        <v>7.22832342986085</v>
+        <v>1.892055834504154</v>
       </c>
       <c r="S25" s="6" t="inlineStr">
         <is>
@@ -9516,13 +7738,13 @@
         </is>
       </c>
       <c r="T25" s="8" t="n">
-        <v>117.4310405131024</v>
+        <v>3.241470010570246</v>
       </c>
       <c r="U25" s="8" t="n">
-        <v>1.226878650876753</v>
+        <v>0.6482572646672726</v>
       </c>
       <c r="V25" s="8" t="n">
-        <v>18.72833387915385</v>
+        <v>41.40767931120109</v>
       </c>
       <c r="W25" s="6" t="inlineStr">
         <is>
@@ -9530,31 +7752,31 @@
         </is>
       </c>
       <c r="X25" s="8" t="n">
-        <v>80.3227605866288</v>
+        <v>58.09893386420898</v>
       </c>
       <c r="Y25" s="8" t="n">
-        <v>77.90123552086489</v>
+        <v>59.91547673767479</v>
       </c>
       <c r="Z25" s="8" t="n">
-        <v>4.851383669285969</v>
+        <v>1.141016343377221</v>
       </c>
       <c r="AA25" s="8" t="n">
-        <v>14.02987706611065</v>
+        <v>-5.494811469703298</v>
       </c>
       <c r="AB25" s="8" t="n">
-        <v>14.68609865470851</v>
+        <v>13.75452579508636</v>
       </c>
       <c r="AC25" s="8" t="n">
-        <v>3.20822905605036</v>
+        <v>19.37154968129626</v>
       </c>
       <c r="AD25" s="8" t="n">
-        <v>-4.332917705735662</v>
+        <v>-11.10825343950531</v>
       </c>
       <c r="AE25" s="8" t="n">
-        <v>-8.47548477007919</v>
+        <v>-11.10825343950531</v>
       </c>
       <c r="AF25" s="8" t="n">
-        <v>11.93061949259444</v>
+        <v>4.461121148371694</v>
       </c>
       <c r="AG25" s="6" t="inlineStr">
         <is>
@@ -9576,62 +7798,62 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>CEIGALL</t>
+          <t>JUSTDIAL</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>NEAR BREAKOUT</t>
+          <t>MOMENTUM</t>
         </is>
       </c>
       <c r="D26" s="5" t="n">
         <v>69</v>
       </c>
       <c r="E26" s="9" t="n">
-        <v>389.8500061035156</v>
+        <v>767.25</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>380.6793728293881</v>
+        <v>685.4692696941277</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>368.4450481878343</v>
+        <v>674.1895350176654</v>
       </c>
       <c r="H26" s="9" t="n">
-        <v>334.0378448081911</v>
+        <v>663.4476517046772</v>
       </c>
       <c r="I26" s="8" t="n">
-        <v>60.60011450704495</v>
+        <v>74.34297471836601</v>
       </c>
       <c r="J26" s="9" t="n">
-        <v>6.619811863613904</v>
+        <v>12.62689463783363</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>6.323765118452346</v>
+        <v>1.131727889051859</v>
       </c>
       <c r="L26" s="9" t="n">
-        <v>0.2960467451615578</v>
+        <v>11.49516674878177</v>
       </c>
       <c r="M26" s="8" t="n">
-        <v>35.32341757505722</v>
+        <v>19.66555906133593</v>
       </c>
       <c r="N26" s="8" t="n">
-        <v>22.49127638073906</v>
+        <v>33.19818465281759</v>
       </c>
       <c r="O26" s="8" t="n">
-        <v>10.43515542396491</v>
+        <v>13.40503856509307</v>
       </c>
       <c r="P26" s="9" t="n">
-        <v>13.34998543280348</v>
+        <v>32.66856476911926</v>
       </c>
       <c r="Q26" s="8" t="n">
-        <v>3.424390207463202</v>
+        <v>4.257877454430662</v>
       </c>
       <c r="R26" s="8" t="n">
-        <v>0.9844392004288897</v>
+        <v>7.22832342986085</v>
       </c>
       <c r="S26" s="6" t="inlineStr">
         <is>
@@ -9639,45 +7861,45 @@
         </is>
       </c>
       <c r="T26" s="8" t="n">
-        <v>2.362402002651652</v>
+        <v>117.4310405131024</v>
       </c>
       <c r="U26" s="8" t="n">
-        <v>0.7783810478005316</v>
+        <v>1.226878650876753</v>
       </c>
       <c r="V26" s="8" t="n">
-        <v>7.807034072745902</v>
+        <v>18.72833387915385</v>
       </c>
       <c r="W26" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X26" s="8" t="n">
-        <v>84.41066668316962</v>
+        <v>80.3227605866288</v>
       </c>
       <c r="Y26" s="8" t="n">
-        <v>91.88132093537502</v>
+        <v>77.90123552086489</v>
       </c>
       <c r="Z26" s="8" t="n">
-        <v>-1.003042613482696</v>
+        <v>4.851383669285969</v>
       </c>
       <c r="AA26" s="8" t="n">
-        <v>1.642554689363585</v>
+        <v>14.02987706611065</v>
       </c>
       <c r="AB26" s="8" t="n">
-        <v>4.307693940739976</v>
+        <v>14.68609865470851</v>
       </c>
       <c r="AC26" s="8" t="n">
-        <v>14.12509444087739</v>
+        <v>3.20822905605036</v>
       </c>
       <c r="AD26" s="8" t="n">
-        <v>-1.553028761738473</v>
+        <v>-4.332917705735662</v>
       </c>
       <c r="AE26" s="8" t="n">
-        <v>-3.779923398667484</v>
+        <v>-8.47548477007919</v>
       </c>
       <c r="AF26" s="8" t="n">
-        <v>2.409017648097689</v>
+        <v>11.93061949259444</v>
       </c>
       <c r="AG26" s="6" t="inlineStr">
         <is>
@@ -9699,11 +7921,11 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>KRISHANA</t>
+          <t>CEIGALL</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -9715,46 +7937,46 @@
         <v>69</v>
       </c>
       <c r="E27" s="9" t="n">
-        <v>209.5</v>
+        <v>389.8500061035156</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>197.4961410712459</v>
+        <v>380.6793728293881</v>
       </c>
       <c r="G27" s="9" t="n">
-        <v>187.3185506384039</v>
+        <v>368.4450481878343</v>
       </c>
       <c r="H27" s="9" t="n">
-        <v>149.3886493581162</v>
+        <v>334.0378448081911</v>
       </c>
       <c r="I27" s="8" t="n">
-        <v>65.00810496147996</v>
+        <v>60.60011450704495</v>
       </c>
       <c r="J27" s="9" t="n">
-        <v>6.688970282033779</v>
+        <v>6.619811863613904</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>4.560914053086163</v>
+        <v>6.323765118452346</v>
       </c>
       <c r="L27" s="9" t="n">
-        <v>2.128056228947615</v>
+        <v>0.2960467451615578</v>
       </c>
       <c r="M27" s="8" t="n">
-        <v>24.99417691601515</v>
+        <v>35.32341757505722</v>
       </c>
       <c r="N27" s="8" t="n">
-        <v>27.85339310251663</v>
+        <v>22.49127638073906</v>
       </c>
       <c r="O27" s="8" t="n">
-        <v>11.20361905731984</v>
+        <v>10.43515542396491</v>
       </c>
       <c r="P27" s="9" t="n">
-        <v>8.010488331648764</v>
+        <v>13.34998543280348</v>
       </c>
       <c r="Q27" s="8" t="n">
-        <v>3.823622115345472</v>
+        <v>3.424390207463202</v>
       </c>
       <c r="R27" s="8" t="n">
-        <v>0.8031980992340177</v>
+        <v>0.9844392004288897</v>
       </c>
       <c r="S27" s="6" t="inlineStr">
         <is>
@@ -9762,13 +7984,13 @@
         </is>
       </c>
       <c r="T27" s="8" t="n">
-        <v>3.288412774749878</v>
+        <v>2.362402002651652</v>
       </c>
       <c r="U27" s="8" t="n">
-        <v>0.876713709321978</v>
+        <v>0.7783810478005316</v>
       </c>
       <c r="V27" s="8" t="n">
-        <v>20.30450995140057</v>
+        <v>7.807034072745902</v>
       </c>
       <c r="W27" s="6" t="inlineStr">
         <is>
@@ -9776,31 +7998,31 @@
         </is>
       </c>
       <c r="X27" s="8" t="n">
-        <v>82.70816538109631</v>
+        <v>84.41066668316962</v>
       </c>
       <c r="Y27" s="8" t="n">
-        <v>85.13626686259249</v>
+        <v>91.88132093537502</v>
       </c>
       <c r="Z27" s="8" t="n">
-        <v>-1.592371365196821</v>
+        <v>-1.003042613482696</v>
       </c>
       <c r="AA27" s="8" t="n">
-        <v>6.118935236093481</v>
+        <v>1.642554689363585</v>
       </c>
       <c r="AB27" s="8" t="n">
-        <v>16.46005932003769</v>
+        <v>4.307693940739976</v>
       </c>
       <c r="AC27" s="8" t="n">
-        <v>46.65732660045303</v>
+        <v>14.12509444087739</v>
       </c>
       <c r="AD27" s="8" t="n">
-        <v>-2.973322630320707</v>
+        <v>-1.553028761738473</v>
       </c>
       <c r="AE27" s="8" t="n">
-        <v>-3.009259259259256</v>
+        <v>-3.779923398667484</v>
       </c>
       <c r="AF27" s="8" t="n">
-        <v>6.078022012806694</v>
+        <v>2.409017648097689</v>
       </c>
       <c r="AG27" s="6" t="inlineStr">
         <is>
@@ -9822,62 +8044,62 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>PVRINOX</t>
+          <t>KRISHANA</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>TREND CONTINUATION</t>
+          <t>NEAR BREAKOUT</t>
         </is>
       </c>
       <c r="D28" s="5" t="n">
         <v>69</v>
       </c>
       <c r="E28" s="9" t="n">
-        <v>1417.900024414062</v>
+        <v>209.5</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>1332.309178107311</v>
+        <v>197.4961410712459</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>1258.638635856032</v>
+        <v>187.3185506383982</v>
       </c>
       <c r="H28" s="9" t="n">
-        <v>1125.347867558656</v>
+        <v>149.3886493500878</v>
       </c>
       <c r="I28" s="8" t="n">
-        <v>65.6005916128039</v>
+        <v>65.00810496147996</v>
       </c>
       <c r="J28" s="9" t="n">
-        <v>47.21464310565693</v>
+        <v>6.688970282033779</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>37.6842694976652</v>
+        <v>4.560914053086163</v>
       </c>
       <c r="L28" s="9" t="n">
-        <v>9.530373607991734</v>
+        <v>2.128056228947615</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>36.89022604213147</v>
+        <v>24.99417691601504</v>
       </c>
       <c r="N28" s="8" t="n">
-        <v>32.29790840001962</v>
+        <v>27.85339310251663</v>
       </c>
       <c r="O28" s="8" t="n">
-        <v>9.238919993142714</v>
+        <v>11.20361905731984</v>
       </c>
       <c r="P28" s="9" t="n">
-        <v>49.42990996648658</v>
+        <v>8.010488331648764</v>
       </c>
       <c r="Q28" s="8" t="n">
-        <v>3.48613506702725</v>
+        <v>3.823622115345472</v>
       </c>
       <c r="R28" s="8" t="n">
-        <v>1.120039499192308</v>
+        <v>0.8031980992340177</v>
       </c>
       <c r="S28" s="6" t="inlineStr">
         <is>
@@ -9885,45 +8107,45 @@
         </is>
       </c>
       <c r="T28" s="8" t="n">
-        <v>9.052684116224988</v>
+        <v>3.288412774749878</v>
       </c>
       <c r="U28" s="8" t="n">
-        <v>0.8425543246104154</v>
+        <v>0.876713709321978</v>
       </c>
       <c r="V28" s="8" t="n">
-        <v>22.99424838315407</v>
+        <v>20.30450995140057</v>
       </c>
       <c r="W28" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="X28" s="8" t="n">
-        <v>94.24490792410714</v>
+        <v>82.70816538109631</v>
       </c>
       <c r="Y28" s="8" t="n">
-        <v>90.65471762230906</v>
+        <v>85.13626686259248</v>
       </c>
       <c r="Z28" s="8" t="n">
-        <v>1.126884609032408</v>
+        <v>-1.592371365196821</v>
       </c>
       <c r="AA28" s="8" t="n">
-        <v>0.9540779219695539</v>
+        <v>6.118935236093481</v>
       </c>
       <c r="AB28" s="8" t="n">
-        <v>7.035561008343016</v>
+        <v>16.46005932003769</v>
       </c>
       <c r="AC28" s="8" t="n">
-        <v>41.63420827017548</v>
+        <v>46.65732660045303</v>
       </c>
       <c r="AD28" s="8" t="n">
-        <v>-0.9846351666157438</v>
+        <v>-2.973322630320707</v>
       </c>
       <c r="AE28" s="8" t="n">
-        <v>-0.9846351666157438</v>
+        <v>-3.009259259259256</v>
       </c>
       <c r="AF28" s="8" t="n">
-        <v>6.424248043411529</v>
+        <v>6.078022012806694</v>
       </c>
       <c r="AG28" s="6" t="inlineStr">
         <is>
@@ -9945,62 +8167,62 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>TFCILTD</t>
+          <t>PVRINOX</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>EMA20 PULLBACK</t>
+          <t>TREND CONTINUATION</t>
         </is>
       </c>
       <c r="D29" s="5" t="n">
         <v>69</v>
       </c>
       <c r="E29" s="9" t="n">
-        <v>150.1999969482422</v>
+        <v>1417.900024414062</v>
       </c>
       <c r="F29" s="9" t="n">
-        <v>148.6034311026721</v>
+        <v>1332.309178107311</v>
       </c>
       <c r="G29" s="9" t="n">
-        <v>136.406951508431</v>
+        <v>1258.638635856032</v>
       </c>
       <c r="H29" s="9" t="n">
-        <v>99.43699802047756</v>
+        <v>1125.347867558656</v>
       </c>
       <c r="I29" s="8" t="n">
-        <v>55.55823012731431</v>
+        <v>65.6005916128039</v>
       </c>
       <c r="J29" s="9" t="n">
-        <v>5.334571853616467</v>
+        <v>47.21464310565693</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>5.185653051446711</v>
+        <v>37.6842694976652</v>
       </c>
       <c r="L29" s="9" t="n">
-        <v>0.1489188021697556</v>
+        <v>9.530373607991734</v>
       </c>
       <c r="M29" s="8" t="n">
-        <v>38.81636756382034</v>
+        <v>36.89022604213147</v>
       </c>
       <c r="N29" s="8" t="n">
-        <v>24.81263262971194</v>
+        <v>32.29790840001962</v>
       </c>
       <c r="O29" s="8" t="n">
-        <v>19.58751990156778</v>
+        <v>9.238919993142714</v>
       </c>
       <c r="P29" s="9" t="n">
-        <v>6.15627114690921</v>
+        <v>49.42990996648658</v>
       </c>
       <c r="Q29" s="8" t="n">
-        <v>4.098715893470102</v>
+        <v>3.48613506702725</v>
       </c>
       <c r="R29" s="8" t="n">
-        <v>1.014430895810536</v>
+        <v>1.120039499192308</v>
       </c>
       <c r="S29" s="6" t="inlineStr">
         <is>
@@ -10008,45 +8230,45 @@
         </is>
       </c>
       <c r="T29" s="8" t="n">
-        <v>1.97514623966385</v>
+        <v>9.052684116224988</v>
       </c>
       <c r="U29" s="8" t="n">
-        <v>0.6025489221374285</v>
+        <v>0.8425543246104154</v>
       </c>
       <c r="V29" s="8" t="n">
-        <v>20.95317723519181</v>
+        <v>22.99424838315407</v>
       </c>
       <c r="W29" s="6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X29" s="8" t="n">
-        <v>52.90580586292285</v>
+        <v>94.24490792410714</v>
       </c>
       <c r="Y29" s="8" t="n">
-        <v>68.58294904486161</v>
+        <v>90.65471762230906</v>
       </c>
       <c r="Z29" s="8" t="n">
-        <v>-3.828912798038808</v>
+        <v>1.126884609032408</v>
       </c>
       <c r="AA29" s="8" t="n">
-        <v>-5.35005694281142</v>
+        <v>0.9540779219695539</v>
       </c>
       <c r="AB29" s="8" t="n">
-        <v>7.577712506131062</v>
+        <v>7.035561008343016</v>
       </c>
       <c r="AC29" s="8" t="n">
-        <v>81.45131454641812</v>
+        <v>41.63420827017548</v>
       </c>
       <c r="AD29" s="8" t="n">
-        <v>-7.255325854532247</v>
+        <v>-0.9846351666157438</v>
       </c>
       <c r="AE29" s="8" t="n">
-        <v>-7.255325854532247</v>
+        <v>-0.9846351666157438</v>
       </c>
       <c r="AF29" s="8" t="n">
-        <v>1.074380203554659</v>
+        <v>6.424248043411529</v>
       </c>
       <c r="AG29" s="6" t="inlineStr">
         <is>
@@ -10066,1239 +8288,9 @@
       <c r="AN29" s="6" t="inlineStr"/>
       <c r="AO29" s="6" t="inlineStr"/>
     </row>
-    <row r="30">
-      <c r="A30" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>OAL</t>
-        </is>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>TREND CONTINUATION</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>68</v>
-      </c>
-      <c r="E30" s="9" t="n">
-        <v>604.5</v>
-      </c>
-      <c r="F30" s="9" t="n">
-        <v>547.1275351825357</v>
-      </c>
-      <c r="G30" s="9" t="n">
-        <v>494.7597816882591</v>
-      </c>
-      <c r="H30" s="9" t="n">
-        <v>390.2622577767484</v>
-      </c>
-      <c r="I30" s="8" t="n">
-        <v>67.66230132499675</v>
-      </c>
-      <c r="J30" s="9" t="n">
-        <v>28.61398699409699</v>
-      </c>
-      <c r="K30" s="9" t="n">
-        <v>21.9011154565658</v>
-      </c>
-      <c r="L30" s="9" t="n">
-        <v>6.712871537531189</v>
-      </c>
-      <c r="M30" s="8" t="n">
-        <v>31.56900392148759</v>
-      </c>
-      <c r="N30" s="8" t="n">
-        <v>28.39074751911908</v>
-      </c>
-      <c r="O30" s="8" t="n">
-        <v>11.10654493388937</v>
-      </c>
-      <c r="P30" s="9" t="n">
-        <v>35.1556782092246</v>
-      </c>
-      <c r="Q30" s="8" t="n">
-        <v>5.815662234776609</v>
-      </c>
-      <c r="R30" s="8" t="n">
-        <v>0.6680246302457933</v>
-      </c>
-      <c r="S30" s="6" t="inlineStr">
-        <is>
-          <t>Rising</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v>10.29090292002956</v>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v>0.899268712850063</v>
-      </c>
-      <c r="V30" s="8" t="n">
-        <v>27.27477228350401</v>
-      </c>
-      <c r="W30" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X30" s="8" t="n">
-        <v>75.97493138326867</v>
-      </c>
-      <c r="Y30" s="8" t="n">
-        <v>87.30126595423445</v>
-      </c>
-      <c r="Z30" s="8" t="n">
-        <v>-3.18706336258342</v>
-      </c>
-      <c r="AA30" s="8" t="n">
-        <v>18.3090293684274</v>
-      </c>
-      <c r="AB30" s="8" t="n">
-        <v>17.57268721107277</v>
-      </c>
-      <c r="AC30" s="8" t="n">
-        <v>73.9104507960857</v>
-      </c>
-      <c r="AD30" s="8" t="n">
-        <v>-5.39906103286385</v>
-      </c>
-      <c r="AE30" s="8" t="n">
-        <v>-5.39906103286385</v>
-      </c>
-      <c r="AF30" s="8" t="n">
-        <v>10.48612272791634</v>
-      </c>
-      <c r="AG30" s="6" t="inlineStr">
-        <is>
-          <t>BEAR</t>
-        </is>
-      </c>
-      <c r="AH30" s="8" t="n">
-        <v>-2.291791335270921</v>
-      </c>
-      <c r="AI30" s="8" t="n">
-        <v>-5.690287434648067</v>
-      </c>
-      <c r="AJ30" s="6" t="inlineStr"/>
-      <c r="AK30" s="6" t="inlineStr"/>
-      <c r="AL30" s="6" t="inlineStr"/>
-      <c r="AM30" s="6" t="inlineStr"/>
-      <c r="AN30" s="6" t="inlineStr"/>
-      <c r="AO30" s="6" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="n">
-        <v>12</v>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>BHARTIHEXA</t>
-        </is>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>MOMENTUM</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>67</v>
-      </c>
-      <c r="E31" s="9" t="n">
-        <v>1629.300048828125</v>
-      </c>
-      <c r="F31" s="9" t="n">
-        <v>1541.237088914875</v>
-      </c>
-      <c r="G31" s="9" t="n">
-        <v>1530.589955803257</v>
-      </c>
-      <c r="H31" s="9" t="n">
-        <v>1558.504794200772</v>
-      </c>
-      <c r="I31" s="8" t="n">
-        <v>64.12386080902328</v>
-      </c>
-      <c r="J31" s="9" t="n">
-        <v>29.53441963674345</v>
-      </c>
-      <c r="K31" s="9" t="n">
-        <v>6.638560219279443</v>
-      </c>
-      <c r="L31" s="9" t="n">
-        <v>22.89585941746401</v>
-      </c>
-      <c r="M31" s="8" t="n">
-        <v>22.89856761005461</v>
-      </c>
-      <c r="N31" s="8" t="n">
-        <v>31.87786112233419</v>
-      </c>
-      <c r="O31" s="8" t="n">
-        <v>16.40013732109102</v>
-      </c>
-      <c r="P31" s="9" t="n">
-        <v>52.39165733193742</v>
-      </c>
-      <c r="Q31" s="8" t="n">
-        <v>3.215592939411016</v>
-      </c>
-      <c r="R31" s="8" t="n">
-        <v>1.267479921686761</v>
-      </c>
-      <c r="S31" s="6" t="inlineStr">
-        <is>
-          <t>Rising</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v>5.21241947449266</v>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v>0.8524302958921506</v>
-      </c>
-      <c r="V31" s="8" t="n">
-        <v>22.9955973458446</v>
-      </c>
-      <c r="W31" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X31" s="8" t="n">
-        <v>84.53837172339593</v>
-      </c>
-      <c r="Y31" s="8" t="n">
-        <v>86.61634540936171</v>
-      </c>
-      <c r="Z31" s="8" t="n">
-        <v>-0.2021270860688484</v>
-      </c>
-      <c r="AA31" s="8" t="n">
-        <v>5.204371421027121</v>
-      </c>
-      <c r="AB31" s="8" t="n">
-        <v>5.791836546731388</v>
-      </c>
-      <c r="AC31" s="8" t="n">
-        <v>-0.2346057846205785</v>
-      </c>
-      <c r="AD31" s="8" t="n">
-        <v>-2.14414121152402</v>
-      </c>
-      <c r="AE31" s="8" t="n">
-        <v>-15.7687488028333</v>
-      </c>
-      <c r="AF31" s="8" t="n">
-        <v>5.713784111907882</v>
-      </c>
-      <c r="AG31" s="6" t="inlineStr">
-        <is>
-          <t>BEAR</t>
-        </is>
-      </c>
-      <c r="AH31" s="8" t="n">
-        <v>-2.291791335270921</v>
-      </c>
-      <c r="AI31" s="8" t="n">
-        <v>-5.690287434648067</v>
-      </c>
-      <c r="AJ31" s="6" t="inlineStr"/>
-      <c r="AK31" s="6" t="inlineStr"/>
-      <c r="AL31" s="6" t="inlineStr"/>
-      <c r="AM31" s="6" t="inlineStr"/>
-      <c r="AN31" s="6" t="inlineStr"/>
-      <c r="AO31" s="6" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="n">
-        <v>13</v>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>JKIPL</t>
-        </is>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>TREND CONTINUATION</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>67</v>
-      </c>
-      <c r="E32" s="9" t="n">
-        <v>117.5100021362305</v>
-      </c>
-      <c r="F32" s="9" t="n">
-        <v>109.4143986458882</v>
-      </c>
-      <c r="G32" s="9" t="n">
-        <v>103.9185543754456</v>
-      </c>
-      <c r="H32" s="9" t="n">
-        <v>97.73983542175806</v>
-      </c>
-      <c r="I32" s="8" t="n">
-        <v>60.41544032177482</v>
-      </c>
-      <c r="J32" s="9" t="n">
-        <v>5.769211414196832</v>
-      </c>
-      <c r="K32" s="9" t="n">
-        <v>3.742283919837368</v>
-      </c>
-      <c r="L32" s="9" t="n">
-        <v>2.026927494359464</v>
-      </c>
-      <c r="M32" s="8" t="n">
-        <v>32.47961144595103</v>
-      </c>
-      <c r="N32" s="8" t="n">
-        <v>31.4172278496744</v>
-      </c>
-      <c r="O32" s="8" t="n">
-        <v>16.94311471197069</v>
-      </c>
-      <c r="P32" s="9" t="n">
-        <v>8.117525100602169</v>
-      </c>
-      <c r="Q32" s="8" t="n">
-        <v>6.907943964796669</v>
-      </c>
-      <c r="R32" s="8" t="n">
-        <v>0.7222030161031204</v>
-      </c>
-      <c r="S32" s="6" t="inlineStr">
-        <is>
-          <t>Rising</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v>2.819278991964481</v>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v>0.7688724995188332</v>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v>40.63242891972244</v>
-      </c>
-      <c r="W32" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X32" s="8" t="n">
-        <v>56.019064208941</v>
-      </c>
-      <c r="Y32" s="8" t="n">
-        <v>61.99442839048649</v>
-      </c>
-      <c r="Z32" s="8" t="n">
-        <v>-1.392964721172096</v>
-      </c>
-      <c r="AA32" s="8" t="n">
-        <v>9.443977954979822</v>
-      </c>
-      <c r="AB32" s="8" t="n">
-        <v>19.17850299670396</v>
-      </c>
-      <c r="AC32" s="8" t="n">
-        <v>25.82717946698643</v>
-      </c>
-      <c r="AD32" s="8" t="n">
-        <v>-13.57017039316968</v>
-      </c>
-      <c r="AE32" s="8" t="n">
-        <v>-13.57017039316968</v>
-      </c>
-      <c r="AF32" s="8" t="n">
-        <v>7.399029369565113</v>
-      </c>
-      <c r="AG32" s="6" t="inlineStr">
-        <is>
-          <t>BEAR</t>
-        </is>
-      </c>
-      <c r="AH32" s="8" t="n">
-        <v>-2.291791335270921</v>
-      </c>
-      <c r="AI32" s="8" t="n">
-        <v>-5.690287434648067</v>
-      </c>
-      <c r="AJ32" s="6" t="inlineStr"/>
-      <c r="AK32" s="6" t="inlineStr"/>
-      <c r="AL32" s="6" t="inlineStr"/>
-      <c r="AM32" s="6" t="inlineStr"/>
-      <c r="AN32" s="6" t="inlineStr"/>
-      <c r="AO32" s="6" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="n">
-        <v>14</v>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>DHANBANK</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>TREND CONTINUATION</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="E33" s="9" t="n">
-        <v>35.52999877929688</v>
-      </c>
-      <c r="F33" s="9" t="n">
-        <v>32.67979628150144</v>
-      </c>
-      <c r="G33" s="9" t="n">
-        <v>31.93130574258955</v>
-      </c>
-      <c r="H33" s="9" t="n">
-        <v>30.3548756777462</v>
-      </c>
-      <c r="I33" s="8" t="n">
-        <v>63.06759519124925</v>
-      </c>
-      <c r="J33" s="9" t="n">
-        <v>1.377807099775744</v>
-      </c>
-      <c r="K33" s="9" t="n">
-        <v>0.6651164643908615</v>
-      </c>
-      <c r="L33" s="9" t="n">
-        <v>0.7126906353848824</v>
-      </c>
-      <c r="M33" s="8" t="n">
-        <v>27.935343580819</v>
-      </c>
-      <c r="N33" s="8" t="n">
-        <v>23.03006573203308</v>
-      </c>
-      <c r="O33" s="8" t="n">
-        <v>15.55488710262354</v>
-      </c>
-      <c r="P33" s="9" t="n">
-        <v>2.000598257581046</v>
-      </c>
-      <c r="Q33" s="8" t="n">
-        <v>5.630729879863613</v>
-      </c>
-      <c r="R33" s="8" t="n">
-        <v>0.7728284813055751</v>
-      </c>
-      <c r="S33" s="6" t="inlineStr">
-        <is>
-          <t>Rising</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v>2.322947966328475</v>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v>0.8131798868384181</v>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v>41.8022833593077</v>
-      </c>
-      <c r="W33" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X33" s="8" t="n">
-        <v>82.86955460258152</v>
-      </c>
-      <c r="Y33" s="8" t="n">
-        <v>91.80323366013108</v>
-      </c>
-      <c r="Z33" s="8" t="n">
-        <v>-4.102565422574256</v>
-      </c>
-      <c r="AA33" s="8" t="n">
-        <v>3.045241447217384</v>
-      </c>
-      <c r="AB33" s="8" t="n">
-        <v>20.56328336321427</v>
-      </c>
-      <c r="AC33" s="8" t="n">
-        <v>3.737222713275545</v>
-      </c>
-      <c r="AD33" s="8" t="n">
-        <v>-5.253336588541668</v>
-      </c>
-      <c r="AE33" s="8" t="n">
-        <v>-5.253336588541668</v>
-      </c>
-      <c r="AF33" s="8" t="n">
-        <v>8.721604239035008</v>
-      </c>
-      <c r="AG33" s="6" t="inlineStr">
-        <is>
-          <t>BEAR</t>
-        </is>
-      </c>
-      <c r="AH33" s="8" t="n">
-        <v>-2.291791335270921</v>
-      </c>
-      <c r="AI33" s="8" t="n">
-        <v>-5.690287434648067</v>
-      </c>
-      <c r="AJ33" s="6" t="inlineStr"/>
-      <c r="AK33" s="6" t="inlineStr"/>
-      <c r="AL33" s="6" t="inlineStr"/>
-      <c r="AM33" s="6" t="inlineStr"/>
-      <c r="AN33" s="6" t="inlineStr"/>
-      <c r="AO33" s="6" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="n">
-        <v>15</v>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>PETRONET</t>
-        </is>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>EMA20 PULLBACK</t>
-        </is>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>66</v>
-      </c>
-      <c r="E34" s="9" t="n">
-        <v>295</v>
-      </c>
-      <c r="F34" s="9" t="n">
-        <v>291.0425660285314</v>
-      </c>
-      <c r="G34" s="9" t="n">
-        <v>287.9625906680766</v>
-      </c>
-      <c r="H34" s="9" t="n">
-        <v>281.9380455715776</v>
-      </c>
-      <c r="I34" s="8" t="n">
-        <v>56.59393292417634</v>
-      </c>
-      <c r="J34" s="9" t="n">
-        <v>1.904759647092646</v>
-      </c>
-      <c r="K34" s="9" t="n">
-        <v>1.504080589545278</v>
-      </c>
-      <c r="L34" s="9" t="n">
-        <v>0.4006790575473687</v>
-      </c>
-      <c r="M34" s="8" t="n">
-        <v>19.45919177234353</v>
-      </c>
-      <c r="N34" s="8" t="n">
-        <v>23.34613344362123</v>
-      </c>
-      <c r="O34" s="8" t="n">
-        <v>12.67104626898336</v>
-      </c>
-      <c r="P34" s="9" t="n">
-        <v>5.848997389936769</v>
-      </c>
-      <c r="Q34" s="8" t="n">
-        <v>1.982710979639583</v>
-      </c>
-      <c r="R34" s="8" t="n">
-        <v>1.674574317541534</v>
-      </c>
-      <c r="S34" s="6" t="inlineStr">
-        <is>
-          <t>Rising</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v>1.113868589771573</v>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v>0.7762897133208089</v>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v>6.348269323231791</v>
-      </c>
-      <c r="W34" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X34" s="8" t="n">
-        <v>71.51697930661769</v>
-      </c>
-      <c r="Y34" s="8" t="n">
-        <v>67.06959250598779</v>
-      </c>
-      <c r="Z34" s="8" t="n">
-        <v>0.4597330603015592</v>
-      </c>
-      <c r="AA34" s="8" t="n">
-        <v>1.724137931034475</v>
-      </c>
-      <c r="AB34" s="8" t="n">
-        <v>0.8202302961112462</v>
-      </c>
-      <c r="AC34" s="8" t="n">
-        <v>6.632932047120077</v>
-      </c>
-      <c r="AD34" s="8" t="n">
-        <v>-1.535382513285488</v>
-      </c>
-      <c r="AE34" s="8" t="n">
-        <v>-8.577454441370547</v>
-      </c>
-      <c r="AF34" s="8" t="n">
-        <v>1.359744048944611</v>
-      </c>
-      <c r="AG34" s="6" t="inlineStr">
-        <is>
-          <t>BEAR</t>
-        </is>
-      </c>
-      <c r="AH34" s="8" t="n">
-        <v>-2.291791335270921</v>
-      </c>
-      <c r="AI34" s="8" t="n">
-        <v>-5.690287434648067</v>
-      </c>
-      <c r="AJ34" s="6" t="inlineStr"/>
-      <c r="AK34" s="6" t="inlineStr"/>
-      <c r="AL34" s="6" t="inlineStr"/>
-      <c r="AM34" s="6" t="inlineStr"/>
-      <c r="AN34" s="6" t="inlineStr"/>
-      <c r="AO34" s="6" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="n">
-        <v>16</v>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>ANANDRATHI</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>TREND CONTINUATION</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="E35" s="9" t="n">
-        <v>2200</v>
-      </c>
-      <c r="F35" s="9" t="n">
-        <v>2141.553206907429</v>
-      </c>
-      <c r="G35" s="9" t="n">
-        <v>2128.825454047934</v>
-      </c>
-      <c r="H35" s="9" t="n">
-        <v>1879.409072345837</v>
-      </c>
-      <c r="I35" s="8" t="n">
-        <v>59.56889649475414</v>
-      </c>
-      <c r="J35" s="9" t="n">
-        <v>-1.419565931341822</v>
-      </c>
-      <c r="K35" s="9" t="n">
-        <v>-10.51150287153483</v>
-      </c>
-      <c r="L35" s="9" t="n">
-        <v>9.091936940193008</v>
-      </c>
-      <c r="M35" s="8" t="n">
-        <v>29.28237029068234</v>
-      </c>
-      <c r="N35" s="8" t="n">
-        <v>20.97211379491637</v>
-      </c>
-      <c r="O35" s="8" t="n">
-        <v>21.85776835954972</v>
-      </c>
-      <c r="P35" s="9" t="n">
-        <v>50.69401700763036</v>
-      </c>
-      <c r="Q35" s="8" t="n">
-        <v>2.304273500346835</v>
-      </c>
-      <c r="R35" s="8" t="n">
-        <v>1.59729183391757</v>
-      </c>
-      <c r="S35" s="6" t="inlineStr">
-        <is>
-          <t>Rising</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v>3.150783287914778</v>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v>0.9686726084587198</v>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v>6.951881716907065</v>
-      </c>
-      <c r="W35" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X35" s="8" t="n">
-        <v>100</v>
-      </c>
-      <c r="Y35" s="8" t="n">
-        <v>96.9885877399186</v>
-      </c>
-      <c r="Z35" s="8" t="n">
-        <v>1.668288704904941</v>
-      </c>
-      <c r="AA35" s="8" t="n">
-        <v>4.960206044040838</v>
-      </c>
-      <c r="AB35" s="8" t="n">
-        <v>-1.131948779784009</v>
-      </c>
-      <c r="AC35" s="8" t="n">
-        <v>5.40189384670593</v>
-      </c>
-      <c r="AD35" s="8" t="n">
-        <v>-1.366436382514957</v>
-      </c>
-      <c r="AE35" s="8" t="n">
-        <v>-2.83176105433246</v>
-      </c>
-      <c r="AF35" s="8" t="n">
-        <v>2.72917772502943</v>
-      </c>
-      <c r="AG35" s="6" t="inlineStr">
-        <is>
-          <t>BEAR</t>
-        </is>
-      </c>
-      <c r="AH35" s="8" t="n">
-        <v>-2.291791335270921</v>
-      </c>
-      <c r="AI35" s="8" t="n">
-        <v>-5.690287434648067</v>
-      </c>
-      <c r="AJ35" s="6" t="inlineStr"/>
-      <c r="AK35" s="6" t="inlineStr"/>
-      <c r="AL35" s="6" t="inlineStr"/>
-      <c r="AM35" s="6" t="inlineStr"/>
-      <c r="AN35" s="6" t="inlineStr"/>
-      <c r="AO35" s="6" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="n">
-        <v>17</v>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>BALAJITELE</t>
-        </is>
-      </c>
-      <c r="C36" s="6" t="inlineStr">
-        <is>
-          <t>EMA20 PULLBACK</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="E36" s="9" t="n">
-        <v>93.65000152587891</v>
-      </c>
-      <c r="F36" s="9" t="n">
-        <v>91.68656006747858</v>
-      </c>
-      <c r="G36" s="9" t="n">
-        <v>91.59649341425502</v>
-      </c>
-      <c r="H36" s="9" t="n">
-        <v>93.06865785202058</v>
-      </c>
-      <c r="I36" s="8" t="n">
-        <v>56.17383484391576</v>
-      </c>
-      <c r="J36" s="9" t="n">
-        <v>-0.06757603696838999</v>
-      </c>
-      <c r="K36" s="9" t="n">
-        <v>-0.3171684617331565</v>
-      </c>
-      <c r="L36" s="9" t="n">
-        <v>0.2495924247647666</v>
-      </c>
-      <c r="M36" s="8" t="n">
-        <v>20.53393652304001</v>
-      </c>
-      <c r="N36" s="8" t="n">
-        <v>19.99401983375661</v>
-      </c>
-      <c r="O36" s="8" t="n">
-        <v>11.74523802449723</v>
-      </c>
-      <c r="P36" s="9" t="n">
-        <v>3.69086750370328</v>
-      </c>
-      <c r="Q36" s="8" t="n">
-        <v>3.941129144224689</v>
-      </c>
-      <c r="R36" s="8" t="n">
-        <v>6.947042780966337</v>
-      </c>
-      <c r="S36" s="6" t="inlineStr">
-        <is>
-          <t>Rising</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v>4.303978523829741</v>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v>0.7551579170114906</v>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v>8.607040639519148</v>
-      </c>
-      <c r="W36" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X36" s="8" t="n">
-        <v>74.80317430863202</v>
-      </c>
-      <c r="Y36" s="8" t="n">
-        <v>69.16949648693192</v>
-      </c>
-      <c r="Z36" s="8" t="n">
-        <v>1.090244109331606</v>
-      </c>
-      <c r="AA36" s="8" t="n">
-        <v>1.882075055913202</v>
-      </c>
-      <c r="AB36" s="8" t="n">
-        <v>-1.679788424274109</v>
-      </c>
-      <c r="AC36" s="8" t="n">
-        <v>8.115906899546111</v>
-      </c>
-      <c r="AD36" s="8" t="n">
-        <v>-3.938861854583842</v>
-      </c>
-      <c r="AE36" s="8" t="n">
-        <v>-29.05302914706144</v>
-      </c>
-      <c r="AF36" s="8" t="n">
-        <v>2.141471396631411</v>
-      </c>
-      <c r="AG36" s="6" t="inlineStr">
-        <is>
-          <t>BEAR</t>
-        </is>
-      </c>
-      <c r="AH36" s="8" t="n">
-        <v>-2.291791335270921</v>
-      </c>
-      <c r="AI36" s="8" t="n">
-        <v>-5.690287434648067</v>
-      </c>
-      <c r="AJ36" s="6" t="inlineStr"/>
-      <c r="AK36" s="6" t="inlineStr"/>
-      <c r="AL36" s="6" t="inlineStr"/>
-      <c r="AM36" s="6" t="inlineStr"/>
-      <c r="AN36" s="6" t="inlineStr"/>
-      <c r="AO36" s="6" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>RISHABH</t>
-        </is>
-      </c>
-      <c r="C37" s="6" t="inlineStr">
-        <is>
-          <t>EMA20 PULLBACK</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="E37" s="9" t="n">
-        <v>701.9500122070312</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <v>698.2399587691323</v>
-      </c>
-      <c r="G37" s="9" t="n">
-        <v>694.7077211466203</v>
-      </c>
-      <c r="H37" s="9" t="n">
-        <v>575.1803827581235</v>
-      </c>
-      <c r="I37" s="8" t="n">
-        <v>50.13690801943186</v>
-      </c>
-      <c r="J37" s="9" t="n">
-        <v>-9.727999355223687</v>
-      </c>
-      <c r="K37" s="9" t="n">
-        <v>-10.25294274441841</v>
-      </c>
-      <c r="L37" s="9" t="n">
-        <v>0.5249433891947195</v>
-      </c>
-      <c r="M37" s="8" t="n">
-        <v>26.01148018016203</v>
-      </c>
-      <c r="N37" s="8" t="n">
-        <v>16.13555418373964</v>
-      </c>
-      <c r="O37" s="8" t="n">
-        <v>19.91277206615639</v>
-      </c>
-      <c r="P37" s="9" t="n">
-        <v>37.66389987341809</v>
-      </c>
-      <c r="Q37" s="8" t="n">
-        <v>5.365609974846699</v>
-      </c>
-      <c r="R37" s="8" t="n">
-        <v>3.582480611672469</v>
-      </c>
-      <c r="S37" s="6" t="inlineStr">
-        <is>
-          <t>Rising</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v>6.517059317279381</v>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v>0.5676243543949326</v>
-      </c>
-      <c r="V37" s="8" t="n">
-        <v>12.94175322996476</v>
-      </c>
-      <c r="W37" s="6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X37" s="8" t="n">
-        <v>74.42396313364056</v>
-      </c>
-      <c r="Y37" s="8" t="n">
-        <v>65.70994112351003</v>
-      </c>
-      <c r="Z37" s="8" t="n">
-        <v>1.547922199932183</v>
-      </c>
-      <c r="AA37" s="8" t="n">
-        <v>1.901725642067542</v>
-      </c>
-      <c r="AB37" s="8" t="n">
-        <v>-8.205832221565512</v>
-      </c>
-      <c r="AC37" s="8" t="n">
-        <v>7.903389784710169</v>
-      </c>
-      <c r="AD37" s="8" t="n">
-        <v>-9.067944671685101</v>
-      </c>
-      <c r="AE37" s="8" t="n">
-        <v>-17.61150091466769</v>
-      </c>
-      <c r="AF37" s="8" t="n">
-        <v>0.531343614942803</v>
-      </c>
-      <c r="AG37" s="6" t="inlineStr">
-        <is>
-          <t>BEAR</t>
-        </is>
-      </c>
-      <c r="AH37" s="8" t="n">
-        <v>-2.291791335270921</v>
-      </c>
-      <c r="AI37" s="8" t="n">
-        <v>-5.690287434648067</v>
-      </c>
-      <c r="AJ37" s="6" t="inlineStr"/>
-      <c r="AK37" s="6" t="inlineStr"/>
-      <c r="AL37" s="6" t="inlineStr"/>
-      <c r="AM37" s="6" t="inlineStr"/>
-      <c r="AN37" s="6" t="inlineStr"/>
-      <c r="AO37" s="6" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="n">
-        <v>19</v>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>SEJALLTD</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
-        <is>
-          <t>TREND CONTINUATION</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="E38" s="9" t="n">
-        <v>839.2999877929688</v>
-      </c>
-      <c r="F38" s="9" t="n">
-        <v>757.6142853538457</v>
-      </c>
-      <c r="G38" s="9" t="n">
-        <v>720.6946575937801</v>
-      </c>
-      <c r="H38" s="9" t="n">
-        <v>700.793054241396</v>
-      </c>
-      <c r="I38" s="8" t="n">
-        <v>61.4453698267056</v>
-      </c>
-      <c r="J38" s="9" t="n">
-        <v>49.28501783813897</v>
-      </c>
-      <c r="K38" s="9" t="n">
-        <v>28.25929482088174</v>
-      </c>
-      <c r="L38" s="9" t="n">
-        <v>21.02572301725723</v>
-      </c>
-      <c r="M38" s="8" t="n">
-        <v>32.03034826313974</v>
-      </c>
-      <c r="N38" s="8" t="n">
-        <v>38.7376788791961</v>
-      </c>
-      <c r="O38" s="8" t="n">
-        <v>13.84786939007223</v>
-      </c>
-      <c r="P38" s="9" t="n">
-        <v>64.09791537440063</v>
-      </c>
-      <c r="Q38" s="8" t="n">
-        <v>7.637068546009766</v>
-      </c>
-      <c r="R38" s="8" t="n">
-        <v>0.7091259076412276</v>
-      </c>
-      <c r="S38" s="6" t="inlineStr">
-        <is>
-          <t>Rising</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v>3.117153571745103</v>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v>0.7906311426736885</v>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v>52.37698076015147</v>
-      </c>
-      <c r="W38" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X38" s="8" t="n">
-        <v>52.08386921445884</v>
-      </c>
-      <c r="Y38" s="8" t="n">
-        <v>56.39399139008881</v>
-      </c>
-      <c r="Z38" s="8" t="n">
-        <v>-2.202286663391828</v>
-      </c>
-      <c r="AA38" s="8" t="n">
-        <v>14.97260106752996</v>
-      </c>
-      <c r="AB38" s="8" t="n">
-        <v>17.48319696396243</v>
-      </c>
-      <c r="AC38" s="8" t="n">
-        <v>13.48026169525565</v>
-      </c>
-      <c r="AD38" s="8" t="n">
-        <v>-18.06911677173841</v>
-      </c>
-      <c r="AE38" s="8" t="n">
-        <v>-19.0411857505894</v>
-      </c>
-      <c r="AF38" s="8" t="n">
-        <v>10.78196438719097</v>
-      </c>
-      <c r="AG38" s="6" t="inlineStr">
-        <is>
-          <t>BEAR</t>
-        </is>
-      </c>
-      <c r="AH38" s="8" t="n">
-        <v>-2.291791335270921</v>
-      </c>
-      <c r="AI38" s="8" t="n">
-        <v>-5.690287434648067</v>
-      </c>
-      <c r="AJ38" s="6" t="inlineStr"/>
-      <c r="AK38" s="6" t="inlineStr"/>
-      <c r="AL38" s="6" t="inlineStr"/>
-      <c r="AM38" s="6" t="inlineStr"/>
-      <c r="AN38" s="6" t="inlineStr"/>
-      <c r="AO38" s="6" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="n">
-        <v>20</v>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>TEXINFRA</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>EMA20 PULLBACK</t>
-        </is>
-      </c>
-      <c r="D39" s="5" t="n">
-        <v>65</v>
-      </c>
-      <c r="E39" s="9" t="n">
-        <v>122.2799987792969</v>
-      </c>
-      <c r="F39" s="9" t="n">
-        <v>120.9107641533407</v>
-      </c>
-      <c r="G39" s="9" t="n">
-        <v>117.0873733418113</v>
-      </c>
-      <c r="H39" s="9" t="n">
-        <v>108.0976902905854</v>
-      </c>
-      <c r="I39" s="8" t="n">
-        <v>53.70978301135534</v>
-      </c>
-      <c r="J39" s="9" t="n">
-        <v>2.509474261656919</v>
-      </c>
-      <c r="K39" s="9" t="n">
-        <v>2.107816685193745</v>
-      </c>
-      <c r="L39" s="9" t="n">
-        <v>0.4016575764631738</v>
-      </c>
-      <c r="M39" s="8" t="n">
-        <v>27.06654697453134</v>
-      </c>
-      <c r="N39" s="8" t="n">
-        <v>28.10717828348569</v>
-      </c>
-      <c r="O39" s="8" t="n">
-        <v>19.77337912885615</v>
-      </c>
-      <c r="P39" s="9" t="n">
-        <v>5.269954091493455</v>
-      </c>
-      <c r="Q39" s="8" t="n">
-        <v>4.309743330146079</v>
-      </c>
-      <c r="R39" s="8" t="n">
-        <v>0.9185624929455689</v>
-      </c>
-      <c r="S39" s="6" t="inlineStr">
-        <is>
-          <t>Rising</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v>1.283847065813414</v>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v>0.6031232667349206</v>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v>12.91771256740989</v>
-      </c>
-      <c r="W39" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X39" s="8" t="n">
-        <v>55.79822210866514</v>
-      </c>
-      <c r="Y39" s="8" t="n">
-        <v>79.36352188592321</v>
-      </c>
-      <c r="Z39" s="8" t="n">
-        <v>-4.669841189402756</v>
-      </c>
-      <c r="AA39" s="8" t="n">
-        <v>1.066204594019293</v>
-      </c>
-      <c r="AB39" s="8" t="n">
-        <v>7.697725729518012</v>
-      </c>
-      <c r="AC39" s="8" t="n">
-        <v>7.393807168707123</v>
-      </c>
-      <c r="AD39" s="8" t="n">
-        <v>-6.499464810627897</v>
-      </c>
-      <c r="AE39" s="8" t="n">
-        <v>-6.499464810627897</v>
-      </c>
-      <c r="AF39" s="8" t="n">
-        <v>1.132434019042106</v>
-      </c>
-      <c r="AG39" s="6" t="inlineStr">
-        <is>
-          <t>BEAR</t>
-        </is>
-      </c>
-      <c r="AH39" s="8" t="n">
-        <v>-2.291791335270921</v>
-      </c>
-      <c r="AI39" s="8" t="n">
-        <v>-5.690287434648067</v>
-      </c>
-      <c r="AJ39" s="6" t="inlineStr"/>
-      <c r="AK39" s="6" t="inlineStr"/>
-      <c r="AL39" s="6" t="inlineStr"/>
-      <c r="AM39" s="6" t="inlineStr"/>
-      <c r="AN39" s="6" t="inlineStr"/>
-      <c r="AO39" s="6" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:AO39"/>
-  <conditionalFormatting sqref="D5:D39">
+  <autoFilter ref="A4:AO29"/>
+  <conditionalFormatting sqref="D5:D29">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="50"/>
@@ -11336,7 +8328,7 @@
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
         <is>
-          <t>PRIORITY sheet = the SWING PICKS where every check is OK: Action is BUY ZONE, no Risk Flags (RELAXED smallcap is only information), Fundamental is not Mixed, Hist Hit 7% is 25 or more, and only the best one from each sector. Sorted by Hist Hit 7%, at most 5 stocks (3 when NIFTY regime is BEAR). The other picks are listed under it with the check that failed. It is a way to narrow the list, not a guarantee: in a 6-month test (Apr-Oct 2026) these stocks did about the same as the full list.</t>
+          <t>PRIORITY sheet = the SWING PICKS where every check is OK: Action is BUY ZONE, no Risk Flags (RELAXED smallcap is only information), Fundamental is not Mixed, Hist Hit 7% is 25 or more, and only the best one from each sector. Sorted by Hist Hit 7%, at most 5 stocks (1 when NIFTY regime is BEAR, and SWING PICKS then has only 5). The other picks are listed under it with the check that failed. It is a way to narrow the list, not a guarantee. In a 6-month test (Apr-Oct 2026, NIFTY -7%) these rules, selling at Target 1, made about +1.1% per PRIORITY trade (Rs 1L account: about +Rs 22,000, 6 of 7 months in profit), before brokerage and taxes.</t>
         </is>
       </c>
     </row>
@@ -11357,7 +8349,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Targets are fixed at +7% and +10% from entry. Stop = tighter of 1.8 x ATR or 10-day swing low, limited to 3-6.5% below entry. Suggested approach: book half at Target 1, trail the rest.</t>
+          <t>Targets are fixed at +7% and +10% from entry. Stop = tighter of 1.8 x ATR or 10-day swing low, limited to 3-6.5% below entry. Exit plan: sell at Target 1. In the 6-month test, holding on for Target 2 (half or all, with or without a trailing stop) made less money on a Rs 1L account.</t>
         </is>
       </c>
     </row>
@@ -11752,7 +8744,7 @@
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>5. Final SWING PICKS: 15</t>
+          <t>5. Final SWING PICKS: 5</t>
         </is>
       </c>
     </row>
